--- a/RangeSayacv3_yeni_taslak.xlsx
+++ b/RangeSayacv3_yeni_taslak.xlsx
@@ -8,14 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kaank\Downloads\IpekyolRangeSayac\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9A82489-966E-47E4-87F0-80C47D10CB63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4482AD1A-E3D5-4681-92EF-EA865B7B0D40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19090" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sayfa1" sheetId="1" r:id="rId1"/>
     <sheet name="Sayfa2" sheetId="3" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sayfa1!$A$1:$I$827</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -42,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3527" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3647" uniqueCount="176">
   <si>
     <t>Tema Adı</t>
   </si>
@@ -565,12 +568,18 @@
   <si>
     <t>TRAVEL SET</t>
   </si>
+  <si>
+    <t>Mono-Weekend Edit 2</t>
+  </si>
+  <si>
+    <t>Jean SP1</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -610,6 +619,12 @@
       <name val="Arial"/>
       <family val="2"/>
       <charset val="162"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="9">
@@ -1065,7 +1080,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I827"/>
+  <dimension ref="A1:I857"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="19.125" customWidth="1"/>
@@ -1695,7 +1710,7 @@
         <v>49</v>
       </c>
       <c r="I21" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
@@ -1726,7 +1741,7 @@
         <v>13</v>
       </c>
       <c r="I22" s="1">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
@@ -1786,7 +1801,7 @@
         <v>17</v>
       </c>
       <c r="I24" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
@@ -1817,7 +1832,7 @@
         <v>14</v>
       </c>
       <c r="I25" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
@@ -1847,9 +1862,7 @@
         <f>VLOOKUP(G26,Sayfa2!M:N,2,0)</f>
         <v>52</v>
       </c>
-      <c r="I26" s="1">
-        <v>1</v>
-      </c>
+      <c r="I26" s="1"/>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
@@ -1909,7 +1922,9 @@
         <f>VLOOKUP(G28,Sayfa2!M:N,2,0)</f>
         <v>22</v>
       </c>
-      <c r="I28" s="1"/>
+      <c r="I28" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
@@ -1939,7 +1954,7 @@
         <v>23</v>
       </c>
       <c r="I29" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
@@ -1998,7 +2013,9 @@
         <f>VLOOKUP(G31,Sayfa2!M:N,2,0)</f>
         <v>50</v>
       </c>
-      <c r="I31" s="1"/>
+      <c r="I31" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
@@ -25943,7 +25960,852 @@
         <v>1</v>
       </c>
     </row>
+    <row r="828" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A828" t="s">
+        <v>40</v>
+      </c>
+      <c r="B828">
+        <v>4</v>
+      </c>
+      <c r="C828">
+        <v>10</v>
+      </c>
+      <c r="D828" t="s">
+        <v>37</v>
+      </c>
+      <c r="E828" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="F828">
+        <v>1327</v>
+      </c>
+      <c r="G828" t="s">
+        <v>4</v>
+      </c>
+      <c r="H828">
+        <f>VLOOKUP(G828,Sayfa2!M:N,2,0)</f>
+        <v>21</v>
+      </c>
+      <c r="I828" s="1"/>
+    </row>
+    <row r="829" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A829" t="s">
+        <v>40</v>
+      </c>
+      <c r="B829">
+        <v>4</v>
+      </c>
+      <c r="C829">
+        <v>10</v>
+      </c>
+      <c r="D829" t="s">
+        <v>37</v>
+      </c>
+      <c r="E829" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="F829">
+        <v>1327</v>
+      </c>
+      <c r="G829" t="s">
+        <v>5</v>
+      </c>
+      <c r="H829">
+        <f>VLOOKUP(G829,Sayfa2!M:N,2,0)</f>
+        <v>19</v>
+      </c>
+      <c r="I829" s="1"/>
+    </row>
+    <row r="830" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A830" t="s">
+        <v>40</v>
+      </c>
+      <c r="B830">
+        <v>4</v>
+      </c>
+      <c r="C830">
+        <v>10</v>
+      </c>
+      <c r="D830" t="s">
+        <v>37</v>
+      </c>
+      <c r="E830" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="F830">
+        <v>1327</v>
+      </c>
+      <c r="G830" t="s">
+        <v>6</v>
+      </c>
+      <c r="H830">
+        <f>VLOOKUP(G830,Sayfa2!M:N,2,0)</f>
+        <v>20</v>
+      </c>
+      <c r="I830" s="1"/>
+    </row>
+    <row r="831" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A831" t="s">
+        <v>40</v>
+      </c>
+      <c r="B831">
+        <v>4</v>
+      </c>
+      <c r="C831">
+        <v>10</v>
+      </c>
+      <c r="D831" t="s">
+        <v>37</v>
+      </c>
+      <c r="E831" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="F831">
+        <v>1327</v>
+      </c>
+      <c r="G831" t="s">
+        <v>7</v>
+      </c>
+      <c r="H831">
+        <f>VLOOKUP(G831,Sayfa2!M:N,2,0)</f>
+        <v>12</v>
+      </c>
+      <c r="I831" s="1"/>
+    </row>
+    <row r="832" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A832" t="s">
+        <v>40</v>
+      </c>
+      <c r="B832">
+        <v>4</v>
+      </c>
+      <c r="C832">
+        <v>10</v>
+      </c>
+      <c r="D832" t="s">
+        <v>37</v>
+      </c>
+      <c r="E832" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="F832">
+        <v>1327</v>
+      </c>
+      <c r="G832" t="s">
+        <v>8</v>
+      </c>
+      <c r="H832">
+        <f>VLOOKUP(G832,Sayfa2!M:N,2,0)</f>
+        <v>49</v>
+      </c>
+      <c r="I832" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="833" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A833" t="s">
+        <v>40</v>
+      </c>
+      <c r="B833">
+        <v>4</v>
+      </c>
+      <c r="C833">
+        <v>10</v>
+      </c>
+      <c r="D833" t="s">
+        <v>37</v>
+      </c>
+      <c r="E833" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="F833">
+        <v>1327</v>
+      </c>
+      <c r="G833" t="s">
+        <v>9</v>
+      </c>
+      <c r="H833">
+        <f>VLOOKUP(G833,Sayfa2!M:N,2,0)</f>
+        <v>13</v>
+      </c>
+      <c r="I833" s="1"/>
+    </row>
+    <row r="834" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A834" t="s">
+        <v>40</v>
+      </c>
+      <c r="B834">
+        <v>4</v>
+      </c>
+      <c r="C834">
+        <v>10</v>
+      </c>
+      <c r="D834" t="s">
+        <v>37</v>
+      </c>
+      <c r="E834" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="F834">
+        <v>1327</v>
+      </c>
+      <c r="G834" t="s">
+        <v>10</v>
+      </c>
+      <c r="H834">
+        <f>VLOOKUP(G834,Sayfa2!M:N,2,0)</f>
+        <v>16</v>
+      </c>
+      <c r="I834" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="835" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A835" t="s">
+        <v>40</v>
+      </c>
+      <c r="B835">
+        <v>4</v>
+      </c>
+      <c r="C835">
+        <v>10</v>
+      </c>
+      <c r="D835" t="s">
+        <v>37</v>
+      </c>
+      <c r="E835" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="F835">
+        <v>1327</v>
+      </c>
+      <c r="G835" t="s">
+        <v>11</v>
+      </c>
+      <c r="H835">
+        <f>VLOOKUP(G835,Sayfa2!M:N,2,0)</f>
+        <v>17</v>
+      </c>
+      <c r="I835" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="836" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A836" t="s">
+        <v>40</v>
+      </c>
+      <c r="B836">
+        <v>4</v>
+      </c>
+      <c r="C836">
+        <v>10</v>
+      </c>
+      <c r="D836" t="s">
+        <v>37</v>
+      </c>
+      <c r="E836" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="F836">
+        <v>1327</v>
+      </c>
+      <c r="G836" t="s">
+        <v>12</v>
+      </c>
+      <c r="H836">
+        <f>VLOOKUP(G836,Sayfa2!M:N,2,0)</f>
+        <v>14</v>
+      </c>
+      <c r="I836" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="837" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A837" t="s">
+        <v>40</v>
+      </c>
+      <c r="B837">
+        <v>4</v>
+      </c>
+      <c r="C837">
+        <v>10</v>
+      </c>
+      <c r="D837" t="s">
+        <v>37</v>
+      </c>
+      <c r="E837" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="F837">
+        <v>1327</v>
+      </c>
+      <c r="G837" t="s">
+        <v>13</v>
+      </c>
+      <c r="H837">
+        <f>VLOOKUP(G837,Sayfa2!M:N,2,0)</f>
+        <v>52</v>
+      </c>
+      <c r="I837" s="1"/>
+    </row>
+    <row r="838" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A838" t="s">
+        <v>40</v>
+      </c>
+      <c r="B838">
+        <v>4</v>
+      </c>
+      <c r="C838">
+        <v>10</v>
+      </c>
+      <c r="D838" t="s">
+        <v>37</v>
+      </c>
+      <c r="E838" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="F838">
+        <v>1327</v>
+      </c>
+      <c r="G838" t="s">
+        <v>14</v>
+      </c>
+      <c r="H838">
+        <f>VLOOKUP(G838,Sayfa2!M:N,2,0)</f>
+        <v>27</v>
+      </c>
+      <c r="I838" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="839" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A839" t="s">
+        <v>40</v>
+      </c>
+      <c r="B839">
+        <v>4</v>
+      </c>
+      <c r="C839">
+        <v>10</v>
+      </c>
+      <c r="D839" t="s">
+        <v>37</v>
+      </c>
+      <c r="E839" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="F839">
+        <v>1327</v>
+      </c>
+      <c r="G839" t="s">
+        <v>15</v>
+      </c>
+      <c r="H839">
+        <f>VLOOKUP(G839,Sayfa2!M:N,2,0)</f>
+        <v>22</v>
+      </c>
+      <c r="I839" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="840" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A840" t="s">
+        <v>40</v>
+      </c>
+      <c r="B840">
+        <v>4</v>
+      </c>
+      <c r="C840">
+        <v>10</v>
+      </c>
+      <c r="D840" t="s">
+        <v>37</v>
+      </c>
+      <c r="E840" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="F840">
+        <v>1327</v>
+      </c>
+      <c r="G840" t="s">
+        <v>16</v>
+      </c>
+      <c r="H840">
+        <f>VLOOKUP(G840,Sayfa2!M:N,2,0)</f>
+        <v>23</v>
+      </c>
+      <c r="I840" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="841" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A841" t="s">
+        <v>40</v>
+      </c>
+      <c r="B841">
+        <v>4</v>
+      </c>
+      <c r="C841">
+        <v>10</v>
+      </c>
+      <c r="D841" t="s">
+        <v>37</v>
+      </c>
+      <c r="E841" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="F841">
+        <v>1327</v>
+      </c>
+      <c r="G841" t="s">
+        <v>17</v>
+      </c>
+      <c r="H841">
+        <f>VLOOKUP(G841,Sayfa2!M:N,2,0)</f>
+        <v>25</v>
+      </c>
+      <c r="I841" s="1"/>
+    </row>
+    <row r="842" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A842" t="s">
+        <v>40</v>
+      </c>
+      <c r="B842">
+        <v>4</v>
+      </c>
+      <c r="C842">
+        <v>10</v>
+      </c>
+      <c r="D842" t="s">
+        <v>37</v>
+      </c>
+      <c r="E842" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="F842">
+        <v>1327</v>
+      </c>
+      <c r="G842" t="s">
+        <v>18</v>
+      </c>
+      <c r="H842">
+        <f>VLOOKUP(G842,Sayfa2!M:N,2,0)</f>
+        <v>50</v>
+      </c>
+      <c r="I842" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="843" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A843" t="s">
+        <v>40</v>
+      </c>
+      <c r="B843">
+        <v>4</v>
+      </c>
+      <c r="C843">
+        <v>10</v>
+      </c>
+      <c r="D843" t="s">
+        <v>37</v>
+      </c>
+      <c r="E843" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="F843">
+        <v>1228</v>
+      </c>
+      <c r="G843" t="s">
+        <v>4</v>
+      </c>
+      <c r="H843">
+        <f>VLOOKUP(G843,Sayfa2!M:N,2,0)</f>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="844" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A844" t="s">
+        <v>40</v>
+      </c>
+      <c r="B844">
+        <v>4</v>
+      </c>
+      <c r="C844">
+        <v>10</v>
+      </c>
+      <c r="D844" t="s">
+        <v>37</v>
+      </c>
+      <c r="E844" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="F844">
+        <v>1228</v>
+      </c>
+      <c r="G844" t="s">
+        <v>5</v>
+      </c>
+      <c r="H844">
+        <f>VLOOKUP(G844,Sayfa2!M:N,2,0)</f>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="845" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A845" t="s">
+        <v>40</v>
+      </c>
+      <c r="B845">
+        <v>4</v>
+      </c>
+      <c r="C845">
+        <v>10</v>
+      </c>
+      <c r="D845" t="s">
+        <v>37</v>
+      </c>
+      <c r="E845" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="F845">
+        <v>1228</v>
+      </c>
+      <c r="G845" t="s">
+        <v>6</v>
+      </c>
+      <c r="H845">
+        <f>VLOOKUP(G845,Sayfa2!M:N,2,0)</f>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="846" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A846" t="s">
+        <v>40</v>
+      </c>
+      <c r="B846">
+        <v>4</v>
+      </c>
+      <c r="C846">
+        <v>10</v>
+      </c>
+      <c r="D846" t="s">
+        <v>37</v>
+      </c>
+      <c r="E846" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="F846">
+        <v>1228</v>
+      </c>
+      <c r="G846" t="s">
+        <v>7</v>
+      </c>
+      <c r="H846">
+        <f>VLOOKUP(G846,Sayfa2!M:N,2,0)</f>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="847" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A847" t="s">
+        <v>40</v>
+      </c>
+      <c r="B847">
+        <v>4</v>
+      </c>
+      <c r="C847">
+        <v>10</v>
+      </c>
+      <c r="D847" t="s">
+        <v>37</v>
+      </c>
+      <c r="E847" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="F847">
+        <v>1228</v>
+      </c>
+      <c r="G847" t="s">
+        <v>8</v>
+      </c>
+      <c r="H847">
+        <f>VLOOKUP(G847,Sayfa2!M:N,2,0)</f>
+        <v>49</v>
+      </c>
+    </row>
+    <row r="848" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A848" t="s">
+        <v>40</v>
+      </c>
+      <c r="B848">
+        <v>4</v>
+      </c>
+      <c r="C848">
+        <v>10</v>
+      </c>
+      <c r="D848" t="s">
+        <v>37</v>
+      </c>
+      <c r="E848" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="F848">
+        <v>1228</v>
+      </c>
+      <c r="G848" t="s">
+        <v>9</v>
+      </c>
+      <c r="H848">
+        <f>VLOOKUP(G848,Sayfa2!M:N,2,0)</f>
+        <v>13</v>
+      </c>
+      <c r="I848">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="849" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A849" t="s">
+        <v>40</v>
+      </c>
+      <c r="B849">
+        <v>4</v>
+      </c>
+      <c r="C849">
+        <v>10</v>
+      </c>
+      <c r="D849" t="s">
+        <v>37</v>
+      </c>
+      <c r="E849" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="F849">
+        <v>1228</v>
+      </c>
+      <c r="G849" t="s">
+        <v>10</v>
+      </c>
+      <c r="H849">
+        <f>VLOOKUP(G849,Sayfa2!M:N,2,0)</f>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="850" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A850" t="s">
+        <v>40</v>
+      </c>
+      <c r="B850">
+        <v>4</v>
+      </c>
+      <c r="C850">
+        <v>10</v>
+      </c>
+      <c r="D850" t="s">
+        <v>37</v>
+      </c>
+      <c r="E850" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="F850">
+        <v>1228</v>
+      </c>
+      <c r="G850" t="s">
+        <v>11</v>
+      </c>
+      <c r="H850">
+        <f>VLOOKUP(G850,Sayfa2!M:N,2,0)</f>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="851" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A851" t="s">
+        <v>40</v>
+      </c>
+      <c r="B851">
+        <v>4</v>
+      </c>
+      <c r="C851">
+        <v>10</v>
+      </c>
+      <c r="D851" t="s">
+        <v>37</v>
+      </c>
+      <c r="E851" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="F851">
+        <v>1228</v>
+      </c>
+      <c r="G851" t="s">
+        <v>12</v>
+      </c>
+      <c r="H851">
+        <f>VLOOKUP(G851,Sayfa2!M:N,2,0)</f>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="852" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A852" t="s">
+        <v>40</v>
+      </c>
+      <c r="B852">
+        <v>4</v>
+      </c>
+      <c r="C852">
+        <v>10</v>
+      </c>
+      <c r="D852" t="s">
+        <v>37</v>
+      </c>
+      <c r="E852" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="F852">
+        <v>1228</v>
+      </c>
+      <c r="G852" t="s">
+        <v>13</v>
+      </c>
+      <c r="H852">
+        <f>VLOOKUP(G852,Sayfa2!M:N,2,0)</f>
+        <v>52</v>
+      </c>
+    </row>
+    <row r="853" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A853" t="s">
+        <v>40</v>
+      </c>
+      <c r="B853">
+        <v>4</v>
+      </c>
+      <c r="C853">
+        <v>10</v>
+      </c>
+      <c r="D853" t="s">
+        <v>37</v>
+      </c>
+      <c r="E853" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="F853">
+        <v>1228</v>
+      </c>
+      <c r="G853" t="s">
+        <v>14</v>
+      </c>
+      <c r="H853">
+        <f>VLOOKUP(G853,Sayfa2!M:N,2,0)</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="854" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A854" t="s">
+        <v>40</v>
+      </c>
+      <c r="B854">
+        <v>4</v>
+      </c>
+      <c r="C854">
+        <v>10</v>
+      </c>
+      <c r="D854" t="s">
+        <v>37</v>
+      </c>
+      <c r="E854" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="F854">
+        <v>1228</v>
+      </c>
+      <c r="G854" t="s">
+        <v>15</v>
+      </c>
+      <c r="H854">
+        <f>VLOOKUP(G854,Sayfa2!M:N,2,0)</f>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="855" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A855" t="s">
+        <v>40</v>
+      </c>
+      <c r="B855">
+        <v>4</v>
+      </c>
+      <c r="C855">
+        <v>10</v>
+      </c>
+      <c r="D855" t="s">
+        <v>37</v>
+      </c>
+      <c r="E855" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="F855">
+        <v>1228</v>
+      </c>
+      <c r="G855" t="s">
+        <v>16</v>
+      </c>
+      <c r="H855">
+        <f>VLOOKUP(G855,Sayfa2!M:N,2,0)</f>
+        <v>23</v>
+      </c>
+    </row>
+    <row r="856" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A856" t="s">
+        <v>40</v>
+      </c>
+      <c r="B856">
+        <v>4</v>
+      </c>
+      <c r="C856">
+        <v>10</v>
+      </c>
+      <c r="D856" t="s">
+        <v>37</v>
+      </c>
+      <c r="E856" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="F856">
+        <v>1228</v>
+      </c>
+      <c r="G856" t="s">
+        <v>17</v>
+      </c>
+      <c r="H856">
+        <f>VLOOKUP(G856,Sayfa2!M:N,2,0)</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="857" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A857" t="s">
+        <v>40</v>
+      </c>
+      <c r="B857">
+        <v>4</v>
+      </c>
+      <c r="C857">
+        <v>10</v>
+      </c>
+      <c r="D857" t="s">
+        <v>37</v>
+      </c>
+      <c r="E857" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="F857">
+        <v>1228</v>
+      </c>
+      <c r="G857" t="s">
+        <v>18</v>
+      </c>
+      <c r="H857">
+        <f>VLOOKUP(G857,Sayfa2!M:N,2,0)</f>
+        <v>50</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/RangeSayacv3_yeni_taslak.xlsx
+++ b/RangeSayacv3_yeni_taslak.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kaank\Downloads\IpekyolRangeSayac\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4482AD1A-E3D5-4681-92EF-EA865B7B0D40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22F85DA9-8425-4515-9146-21F931DDF2AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19090" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sayfa1" sheetId="1" r:id="rId1"/>
@@ -1740,9 +1740,7 @@
         <f>VLOOKUP(G22,Sayfa2!M:N,2,0)</f>
         <v>13</v>
       </c>
-      <c r="I22" s="1">
-        <v>2</v>
-      </c>
+      <c r="I22" s="1"/>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
@@ -1771,7 +1769,9 @@
         <f>VLOOKUP(G23,Sayfa2!M:N,2,0)</f>
         <v>16</v>
       </c>
-      <c r="I23" s="1"/>
+      <c r="I23" s="1">
+        <v>2</v>
+      </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" t="s">

--- a/RangeSayacv3_yeni_taslak.xlsx
+++ b/RangeSayacv3_yeni_taslak.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kaank\Downloads\IpekyolRangeSayac\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kaankaraca/Desktop/RangeSayac/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22F85DA9-8425-4515-9146-21F931DDF2AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AB8A78E-1588-DD43-81F3-3355821ECCA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19090" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="34200" windowHeight="20860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sayfa1" sheetId="1" r:id="rId1"/>
     <sheet name="Sayfa2" sheetId="3" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sayfa1!$A$1:$I$827</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sayfa1!$A$1:$I$866</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3647" uniqueCount="176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3683" uniqueCount="177">
   <si>
     <t>Tema Adı</t>
   </si>
@@ -574,12 +574,15 @@
   <si>
     <t>Jean SP1</t>
   </si>
+  <si>
+    <t>ACTIVE</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -625,6 +628,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="9">
@@ -677,7 +686,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -709,12 +718,27 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -740,6 +764,10 @@
     <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1080,17 +1108,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I857"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:I866"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="3" max="3" width="19.125" customWidth="1"/>
-    <col min="4" max="4" width="17.125" customWidth="1"/>
-    <col min="5" max="6" width="22.875" customWidth="1"/>
-    <col min="7" max="8" width="18.875" customWidth="1"/>
-    <col min="9" max="9" width="10.875" customWidth="1"/>
+    <col min="3" max="3" width="19.1640625" customWidth="1"/>
+    <col min="4" max="4" width="17.1640625" customWidth="1"/>
+    <col min="5" max="6" width="22.83203125" customWidth="1"/>
+    <col min="7" max="8" width="18.83203125" customWidth="1"/>
+    <col min="9" max="9" width="10.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>39</v>
       </c>
@@ -1119,7 +1147,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>40</v>
       </c>
@@ -1150,7 +1178,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>40</v>
       </c>
@@ -1181,7 +1209,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>40</v>
       </c>
@@ -1212,7 +1240,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>40</v>
       </c>
@@ -1243,7 +1271,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>40</v>
       </c>
@@ -1274,7 +1302,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>40</v>
       </c>
@@ -1302,7 +1330,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>40</v>
       </c>
@@ -1333,7 +1361,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>40</v>
       </c>
@@ -1361,7 +1389,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>40</v>
       </c>
@@ -1392,7 +1420,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>40</v>
       </c>
@@ -1420,7 +1448,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>40</v>
       </c>
@@ -1448,7 +1476,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>40</v>
       </c>
@@ -1479,7 +1507,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>40</v>
       </c>
@@ -1510,7 +1538,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>40</v>
       </c>
@@ -1538,7 +1566,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>40</v>
       </c>
@@ -1566,7 +1594,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>40</v>
       </c>
@@ -1595,7 +1623,7 @@
       </c>
       <c r="I17" s="1"/>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>40</v>
       </c>
@@ -1624,7 +1652,7 @@
       </c>
       <c r="I18" s="1"/>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>40</v>
       </c>
@@ -1653,7 +1681,7 @@
       </c>
       <c r="I19" s="1"/>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>40</v>
       </c>
@@ -1682,7 +1710,7 @@
       </c>
       <c r="I20" s="1"/>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>40</v>
       </c>
@@ -1713,7 +1741,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>40</v>
       </c>
@@ -1742,7 +1770,7 @@
       </c>
       <c r="I22" s="1"/>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>40</v>
       </c>
@@ -1773,7 +1801,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>40</v>
       </c>
@@ -1804,7 +1832,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>40</v>
       </c>
@@ -1835,7 +1863,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>40</v>
       </c>
@@ -1864,7 +1892,7 @@
       </c>
       <c r="I26" s="1"/>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>40</v>
       </c>
@@ -1895,7 +1923,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>40</v>
       </c>
@@ -1926,7 +1954,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>40</v>
       </c>
@@ -1957,7 +1985,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>40</v>
       </c>
@@ -1986,7 +2014,7 @@
       </c>
       <c r="I30" s="1"/>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>40</v>
       </c>
@@ -2017,7 +2045,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>40</v>
       </c>
@@ -2048,7 +2076,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>40</v>
       </c>
@@ -2079,7 +2107,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>40</v>
       </c>
@@ -2110,7 +2138,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>40</v>
       </c>
@@ -2141,7 +2169,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>40</v>
       </c>
@@ -2172,7 +2200,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>40</v>
       </c>
@@ -2200,7 +2228,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>40</v>
       </c>
@@ -2228,7 +2256,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>40</v>
       </c>
@@ -2256,7 +2284,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>40</v>
       </c>
@@ -2287,7 +2315,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>40</v>
       </c>
@@ -2318,7 +2346,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>40</v>
       </c>
@@ -2346,7 +2374,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>40</v>
       </c>
@@ -2377,7 +2405,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>40</v>
       </c>
@@ -2408,7 +2436,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>40</v>
       </c>
@@ -2436,7 +2464,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>40</v>
       </c>
@@ -2464,7 +2492,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>40</v>
       </c>
@@ -2493,7 +2521,7 @@
       </c>
       <c r="I47" s="1"/>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>40</v>
       </c>
@@ -2522,7 +2550,7 @@
       </c>
       <c r="I48" s="1"/>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>40</v>
       </c>
@@ -2551,7 +2579,7 @@
       </c>
       <c r="I49" s="1"/>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>40</v>
       </c>
@@ -2580,7 +2608,7 @@
       </c>
       <c r="I50" s="1"/>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>40</v>
       </c>
@@ -2611,7 +2639,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>40</v>
       </c>
@@ -2640,7 +2668,7 @@
       </c>
       <c r="I52" s="1"/>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>40</v>
       </c>
@@ -2671,7 +2699,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>40</v>
       </c>
@@ -2699,10 +2727,10 @@
         <v>17</v>
       </c>
       <c r="I54" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>40</v>
       </c>
@@ -2730,10 +2758,10 @@
         <v>14</v>
       </c>
       <c r="I55" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>40</v>
       </c>
@@ -2760,9 +2788,11 @@
         <f>VLOOKUP(G56,Sayfa2!M:N,2,0)</f>
         <v>52</v>
       </c>
-      <c r="I56" s="1"/>
-    </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I56" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>40</v>
       </c>
@@ -2791,7 +2821,7 @@
       </c>
       <c r="I57" s="1"/>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>40</v>
       </c>
@@ -2822,7 +2852,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>40</v>
       </c>
@@ -2853,7 +2883,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>40</v>
       </c>
@@ -2882,7 +2912,7 @@
       </c>
       <c r="I60" s="1"/>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>40</v>
       </c>
@@ -2911,7 +2941,7 @@
       </c>
       <c r="I61" s="1"/>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>40</v>
       </c>
@@ -2942,7 +2972,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>40</v>
       </c>
@@ -2973,7 +3003,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>40</v>
       </c>
@@ -3004,7 +3034,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>40</v>
       </c>
@@ -3035,7 +3065,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>40</v>
       </c>
@@ -3066,7 +3096,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>40</v>
       </c>
@@ -3094,7 +3124,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>40</v>
       </c>
@@ -3125,7 +3155,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>40</v>
       </c>
@@ -3156,7 +3186,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>40</v>
       </c>
@@ -3187,7 +3217,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>40</v>
       </c>
@@ -3218,7 +3248,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>40</v>
       </c>
@@ -3249,7 +3279,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>40</v>
       </c>
@@ -3280,7 +3310,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>40</v>
       </c>
@@ -3311,7 +3341,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>40</v>
       </c>
@@ -3339,7 +3369,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>40</v>
       </c>
@@ -3370,7 +3400,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>40</v>
       </c>
@@ -3399,7 +3429,7 @@
       </c>
       <c r="I77" s="1"/>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>40</v>
       </c>
@@ -3428,7 +3458,7 @@
       </c>
       <c r="I78" s="1"/>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>40</v>
       </c>
@@ -3457,7 +3487,7 @@
       </c>
       <c r="I79" s="1"/>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>40</v>
       </c>
@@ -3486,7 +3516,7 @@
       </c>
       <c r="I80" s="1"/>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>40</v>
       </c>
@@ -3517,7 +3547,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>40</v>
       </c>
@@ -3546,7 +3576,7 @@
       </c>
       <c r="I82" s="1"/>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
         <v>40</v>
       </c>
@@ -3577,7 +3607,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
         <v>40</v>
       </c>
@@ -3608,7 +3638,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
         <v>40</v>
       </c>
@@ -3636,10 +3666,10 @@
         <v>14</v>
       </c>
       <c r="I85" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
         <v>40</v>
       </c>
@@ -3670,7 +3700,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
         <v>40</v>
       </c>
@@ -3701,7 +3731,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
         <v>40</v>
       </c>
@@ -3732,7 +3762,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
         <v>40</v>
       </c>
@@ -3763,7 +3793,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
         <v>40</v>
       </c>
@@ -3792,7 +3822,7 @@
       </c>
       <c r="I90" s="1"/>
     </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
         <v>40</v>
       </c>
@@ -3823,7 +3853,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
         <v>40</v>
       </c>
@@ -3854,7 +3884,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
         <v>40</v>
       </c>
@@ -3885,7 +3915,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
         <v>40</v>
       </c>
@@ -3916,7 +3946,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
         <v>40</v>
       </c>
@@ -3947,7 +3977,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
         <v>40</v>
       </c>
@@ -3978,7 +4008,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
         <v>40</v>
       </c>
@@ -4006,7 +4036,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
         <v>40</v>
       </c>
@@ -4037,7 +4067,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
         <v>40</v>
       </c>
@@ -4065,7 +4095,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
         <v>40</v>
       </c>
@@ -4096,7 +4126,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
         <v>40</v>
       </c>
@@ -4124,7 +4154,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
         <v>40</v>
       </c>
@@ -4152,7 +4182,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
         <v>40</v>
       </c>
@@ -4183,7 +4213,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
         <v>40</v>
       </c>
@@ -4214,7 +4244,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
         <v>40</v>
       </c>
@@ -4245,7 +4275,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
         <v>40</v>
       </c>
@@ -4273,7 +4303,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
         <v>40</v>
       </c>
@@ -4302,7 +4332,7 @@
       </c>
       <c r="I107" s="1"/>
     </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
         <v>40</v>
       </c>
@@ -4331,7 +4361,7 @@
       </c>
       <c r="I108" s="1"/>
     </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
         <v>40</v>
       </c>
@@ -4360,7 +4390,7 @@
       </c>
       <c r="I109" s="1"/>
     </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
         <v>40</v>
       </c>
@@ -4389,7 +4419,7 @@
       </c>
       <c r="I110" s="1"/>
     </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
         <v>40</v>
       </c>
@@ -4418,7 +4448,7 @@
       </c>
       <c r="I111" s="1"/>
     </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
         <v>40</v>
       </c>
@@ -4447,7 +4477,7 @@
       </c>
       <c r="I112" s="1"/>
     </row>
-    <row r="113" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
         <v>40</v>
       </c>
@@ -4478,7 +4508,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
         <v>40</v>
       </c>
@@ -4509,7 +4539,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="115" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
         <v>40</v>
       </c>
@@ -4540,7 +4570,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="116" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
         <v>40</v>
       </c>
@@ -4569,7 +4599,7 @@
       </c>
       <c r="I116" s="1"/>
     </row>
-    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
         <v>40</v>
       </c>
@@ -4598,7 +4628,7 @@
       </c>
       <c r="I117" s="1"/>
     </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
         <v>40</v>
       </c>
@@ -4625,11 +4655,9 @@
         <f>VLOOKUP(G118,Sayfa2!M:N,2,0)</f>
         <v>22</v>
       </c>
-      <c r="I118" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="119" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I118" s="1"/>
+    </row>
+    <row r="119" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
         <v>40</v>
       </c>
@@ -4660,7 +4688,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="120" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
         <v>40</v>
       </c>
@@ -4689,7 +4717,7 @@
       </c>
       <c r="I120" s="1"/>
     </row>
-    <row r="121" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
         <v>40</v>
       </c>
@@ -4720,7 +4748,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="122" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
         <v>40</v>
       </c>
@@ -4751,7 +4779,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="123" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
         <v>40</v>
       </c>
@@ -4782,7 +4810,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="124" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
         <v>40</v>
       </c>
@@ -4813,7 +4841,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="125" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
         <v>40</v>
       </c>
@@ -4844,7 +4872,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="126" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
         <v>40</v>
       </c>
@@ -4875,7 +4903,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="127" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
         <v>40</v>
       </c>
@@ -4903,7 +4931,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="128" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
         <v>40</v>
       </c>
@@ -4934,7 +4962,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="129" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
         <v>40</v>
       </c>
@@ -4965,7 +4993,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="130" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
         <v>40</v>
       </c>
@@ -4996,7 +5024,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="131" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
         <v>40</v>
       </c>
@@ -5027,7 +5055,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="132" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
         <v>40</v>
       </c>
@@ -5058,7 +5086,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="133" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
         <v>40</v>
       </c>
@@ -5089,7 +5117,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="134" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
         <v>40</v>
       </c>
@@ -5120,7 +5148,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="135" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
         <v>40</v>
       </c>
@@ -5148,7 +5176,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="136" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
         <v>40</v>
       </c>
@@ -5179,7 +5207,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="137" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
         <v>40</v>
       </c>
@@ -5208,7 +5236,7 @@
       </c>
       <c r="I137" s="1"/>
     </row>
-    <row r="138" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
         <v>40</v>
       </c>
@@ -5237,7 +5265,7 @@
       </c>
       <c r="I138" s="1"/>
     </row>
-    <row r="139" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
         <v>40</v>
       </c>
@@ -5266,7 +5294,7 @@
       </c>
       <c r="I139" s="1"/>
     </row>
-    <row r="140" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
         <v>40</v>
       </c>
@@ -5295,7 +5323,7 @@
       </c>
       <c r="I140" s="1"/>
     </row>
-    <row r="141" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A141" t="s">
         <v>40</v>
       </c>
@@ -5324,7 +5352,7 @@
       </c>
       <c r="I141" s="1"/>
     </row>
-    <row r="142" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
         <v>40</v>
       </c>
@@ -5353,7 +5381,7 @@
       </c>
       <c r="I142" s="1"/>
     </row>
-    <row r="143" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
         <v>40</v>
       </c>
@@ -5381,10 +5409,10 @@
         <v>16</v>
       </c>
       <c r="I143" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="144" spans="1:9" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="144" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A144" t="s">
         <v>40</v>
       </c>
@@ -5412,10 +5440,10 @@
         <v>17</v>
       </c>
       <c r="I144" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="145" spans="1:9" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="145" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A145" t="s">
         <v>40</v>
       </c>
@@ -5446,7 +5474,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="146" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A146" t="s">
         <v>40</v>
       </c>
@@ -5477,7 +5505,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="147" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A147" t="s">
         <v>40</v>
       </c>
@@ -5506,7 +5534,7 @@
       </c>
       <c r="I147" s="1"/>
     </row>
-    <row r="148" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A148" t="s">
         <v>40</v>
       </c>
@@ -5535,7 +5563,7 @@
       </c>
       <c r="I148" s="1"/>
     </row>
-    <row r="149" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A149" t="s">
         <v>40</v>
       </c>
@@ -5566,7 +5594,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="150" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A150" t="s">
         <v>40</v>
       </c>
@@ -5595,7 +5623,7 @@
       </c>
       <c r="I150" s="1"/>
     </row>
-    <row r="151" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A151" t="s">
         <v>40</v>
       </c>
@@ -5622,11 +5650,9 @@
         <f>VLOOKUP(G151,Sayfa2!M:N,2,0)</f>
         <v>50</v>
       </c>
-      <c r="I151" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="152" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I151" s="1"/>
+    </row>
+    <row r="152" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A152" t="s">
         <v>40</v>
       </c>
@@ -5657,7 +5683,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="153" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A153" t="s">
         <v>40</v>
       </c>
@@ -5688,7 +5714,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="154" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A154" t="s">
         <v>40</v>
       </c>
@@ -5719,7 +5745,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="155" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A155" t="s">
         <v>40</v>
       </c>
@@ -5750,7 +5776,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="156" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A156" t="s">
         <v>40</v>
       </c>
@@ -5781,7 +5807,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="157" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A157" t="s">
         <v>40</v>
       </c>
@@ -5809,7 +5835,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="158" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A158" t="s">
         <v>40</v>
       </c>
@@ -5840,7 +5866,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="159" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A159" t="s">
         <v>40</v>
       </c>
@@ -5871,7 +5897,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="160" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A160" t="s">
         <v>40</v>
       </c>
@@ -5902,7 +5928,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="161" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A161" t="s">
         <v>40</v>
       </c>
@@ -5933,7 +5959,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="162" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A162" t="s">
         <v>40</v>
       </c>
@@ -5964,7 +5990,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="163" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A163" t="s">
         <v>40</v>
       </c>
@@ -5992,7 +6018,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="164" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A164" t="s">
         <v>40</v>
       </c>
@@ -6023,7 +6049,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="165" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A165" t="s">
         <v>40</v>
       </c>
@@ -6051,7 +6077,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="166" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A166" t="s">
         <v>40</v>
       </c>
@@ -6079,7 +6105,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="167" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A167" t="s">
         <v>40</v>
       </c>
@@ -6108,7 +6134,7 @@
       </c>
       <c r="I167" s="1"/>
     </row>
-    <row r="168" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A168" t="s">
         <v>40</v>
       </c>
@@ -6137,7 +6163,7 @@
       </c>
       <c r="I168" s="1"/>
     </row>
-    <row r="169" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A169" t="s">
         <v>40</v>
       </c>
@@ -6168,7 +6194,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="170" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A170" t="s">
         <v>40</v>
       </c>
@@ -6197,7 +6223,7 @@
       </c>
       <c r="I170" s="1"/>
     </row>
-    <row r="171" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A171" t="s">
         <v>40</v>
       </c>
@@ -6228,7 +6254,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="172" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A172" t="s">
         <v>40</v>
       </c>
@@ -6257,7 +6283,7 @@
       </c>
       <c r="I172" s="1"/>
     </row>
-    <row r="173" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A173" t="s">
         <v>40</v>
       </c>
@@ -6285,10 +6311,10 @@
         <v>16</v>
       </c>
       <c r="I173" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="174" spans="1:9" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="174" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A174" t="s">
         <v>40</v>
       </c>
@@ -6319,7 +6345,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="175" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A175" t="s">
         <v>40</v>
       </c>
@@ -6347,10 +6373,10 @@
         <v>14</v>
       </c>
       <c r="I175" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="176" spans="1:9" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="176" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A176" t="s">
         <v>40</v>
       </c>
@@ -6379,7 +6405,7 @@
       </c>
       <c r="I176" s="1"/>
     </row>
-    <row r="177" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A177" t="s">
         <v>40</v>
       </c>
@@ -6407,10 +6433,10 @@
         <v>27</v>
       </c>
       <c r="I177" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="178" spans="1:9" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="178" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A178" t="s">
         <v>40</v>
       </c>
@@ -6439,7 +6465,7 @@
       </c>
       <c r="I178" s="1"/>
     </row>
-    <row r="179" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A179" t="s">
         <v>40</v>
       </c>
@@ -6470,7 +6496,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="180" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A180" t="s">
         <v>40</v>
       </c>
@@ -6499,7 +6525,7 @@
       </c>
       <c r="I180" s="1"/>
     </row>
-    <row r="181" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A181" t="s">
         <v>40</v>
       </c>
@@ -6527,10 +6553,10 @@
         <v>50</v>
       </c>
       <c r="I181" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="182" spans="1:9" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="182" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A182" t="s">
         <v>40</v>
       </c>
@@ -6561,7 +6587,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="183" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A183" t="s">
         <v>40</v>
       </c>
@@ -6592,7 +6618,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="184" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A184" t="s">
         <v>40</v>
       </c>
@@ -6623,7 +6649,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="185" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A185" t="s">
         <v>40</v>
       </c>
@@ -6654,7 +6680,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="186" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A186" t="s">
         <v>40</v>
       </c>
@@ -6685,7 +6711,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="187" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A187" t="s">
         <v>40</v>
       </c>
@@ -6713,7 +6739,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="188" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A188" t="s">
         <v>40</v>
       </c>
@@ -6744,7 +6770,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="189" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A189" t="s">
         <v>40</v>
       </c>
@@ -6775,7 +6801,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="190" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A190" t="s">
         <v>40</v>
       </c>
@@ -6806,7 +6832,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="191" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A191" t="s">
         <v>40</v>
       </c>
@@ -6834,7 +6860,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="192" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A192" t="s">
         <v>40</v>
       </c>
@@ -6865,7 +6891,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="193" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A193" t="s">
         <v>40</v>
       </c>
@@ -6893,7 +6919,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="194" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A194" t="s">
         <v>40</v>
       </c>
@@ -6924,7 +6950,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="195" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A195" t="s">
         <v>40</v>
       </c>
@@ -6952,7 +6978,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="196" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A196" t="s">
         <v>40</v>
       </c>
@@ -6983,7 +7009,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="197" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A197" t="s">
         <v>40</v>
       </c>
@@ -7012,7 +7038,7 @@
       </c>
       <c r="I197" s="1"/>
     </row>
-    <row r="198" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A198" t="s">
         <v>40</v>
       </c>
@@ -7041,7 +7067,7 @@
       </c>
       <c r="I198" s="1"/>
     </row>
-    <row r="199" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A199" t="s">
         <v>40</v>
       </c>
@@ -7070,7 +7096,7 @@
       </c>
       <c r="I199" s="1"/>
     </row>
-    <row r="200" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A200" t="s">
         <v>40</v>
       </c>
@@ -7099,7 +7125,7 @@
       </c>
       <c r="I200" s="1"/>
     </row>
-    <row r="201" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A201" t="s">
         <v>40</v>
       </c>
@@ -7130,7 +7156,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="202" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A202" t="s">
         <v>40</v>
       </c>
@@ -7159,7 +7185,7 @@
       </c>
       <c r="I202" s="1"/>
     </row>
-    <row r="203" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A203" t="s">
         <v>40</v>
       </c>
@@ -7187,10 +7213,10 @@
         <v>16</v>
       </c>
       <c r="I203" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="204" spans="1:9" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="204" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A204" t="s">
         <v>40</v>
       </c>
@@ -7221,7 +7247,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="205" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A205" t="s">
         <v>40</v>
       </c>
@@ -7252,7 +7278,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="206" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A206" t="s">
         <v>40</v>
       </c>
@@ -7283,7 +7309,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="207" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A207" t="s">
         <v>40</v>
       </c>
@@ -7310,11 +7336,9 @@
         <f>VLOOKUP(G207,Sayfa2!M:N,2,0)</f>
         <v>27</v>
       </c>
-      <c r="I207" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="208" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I207" s="1"/>
+    </row>
+    <row r="208" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A208" t="s">
         <v>40</v>
       </c>
@@ -7343,7 +7367,7 @@
       </c>
       <c r="I208" s="1"/>
     </row>
-    <row r="209" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A209" t="s">
         <v>40</v>
       </c>
@@ -7374,7 +7398,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="210" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A210" t="s">
         <v>40</v>
       </c>
@@ -7403,7 +7427,7 @@
       </c>
       <c r="I210" s="1"/>
     </row>
-    <row r="211" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A211" t="s">
         <v>40</v>
       </c>
@@ -7434,7 +7458,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="212" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A212" t="s">
         <v>40</v>
       </c>
@@ -7462,7 +7486,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="213" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A213" t="s">
         <v>40</v>
       </c>
@@ -7493,7 +7517,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="214" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A214" t="s">
         <v>40</v>
       </c>
@@ -7524,7 +7548,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="215" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A215" t="s">
         <v>40</v>
       </c>
@@ -7555,7 +7579,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="216" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A216" t="s">
         <v>40</v>
       </c>
@@ -7586,7 +7610,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="217" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A217" t="s">
         <v>40</v>
       </c>
@@ -7614,7 +7638,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="218" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A218" t="s">
         <v>40</v>
       </c>
@@ -7645,7 +7669,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="219" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A219" t="s">
         <v>40</v>
       </c>
@@ -7676,7 +7700,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="220" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A220" t="s">
         <v>40</v>
       </c>
@@ -7707,7 +7731,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="221" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A221" t="s">
         <v>40</v>
       </c>
@@ -7738,7 +7762,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="222" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A222" t="s">
         <v>40</v>
       </c>
@@ -7769,7 +7793,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="223" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A223" t="s">
         <v>40</v>
       </c>
@@ -7800,7 +7824,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="224" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A224" t="s">
         <v>40</v>
       </c>
@@ -7831,7 +7855,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="225" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A225" t="s">
         <v>40</v>
       </c>
@@ -7859,7 +7883,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="226" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A226" t="s">
         <v>40</v>
       </c>
@@ -7887,7 +7911,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="227" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A227" t="s">
         <v>40</v>
       </c>
@@ -7916,7 +7940,7 @@
       </c>
       <c r="I227" s="1"/>
     </row>
-    <row r="228" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A228" t="s">
         <v>40</v>
       </c>
@@ -7945,7 +7969,7 @@
       </c>
       <c r="I228" s="1"/>
     </row>
-    <row r="229" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A229" t="s">
         <v>40</v>
       </c>
@@ -7974,7 +7998,7 @@
       </c>
       <c r="I229" s="1"/>
     </row>
-    <row r="230" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A230" t="s">
         <v>40</v>
       </c>
@@ -8003,7 +8027,7 @@
       </c>
       <c r="I230" s="1"/>
     </row>
-    <row r="231" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A231" t="s">
         <v>40</v>
       </c>
@@ -8034,7 +8058,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="232" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A232" t="s">
         <v>40</v>
       </c>
@@ -8063,7 +8087,7 @@
       </c>
       <c r="I232" s="1"/>
     </row>
-    <row r="233" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A233" t="s">
         <v>40</v>
       </c>
@@ -8094,7 +8118,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="234" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A234" t="s">
         <v>40</v>
       </c>
@@ -8125,7 +8149,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="235" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A235" t="s">
         <v>40</v>
       </c>
@@ -8153,10 +8177,10 @@
         <v>14</v>
       </c>
       <c r="I235" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="236" spans="1:9" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="236" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A236" t="s">
         <v>40</v>
       </c>
@@ -8187,7 +8211,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="237" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A237" t="s">
         <v>40</v>
       </c>
@@ -8216,7 +8240,7 @@
       </c>
       <c r="I237" s="1"/>
     </row>
-    <row r="238" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A238" t="s">
         <v>40</v>
       </c>
@@ -8245,7 +8269,7 @@
       </c>
       <c r="I238" s="1"/>
     </row>
-    <row r="239" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A239" t="s">
         <v>40</v>
       </c>
@@ -8276,7 +8300,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="240" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A240" t="s">
         <v>40</v>
       </c>
@@ -8305,7 +8329,7 @@
       </c>
       <c r="I240" s="1"/>
     </row>
-    <row r="241" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A241" t="s">
         <v>40</v>
       </c>
@@ -8334,7 +8358,7 @@
       </c>
       <c r="I241" s="1"/>
     </row>
-    <row r="242" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A242" t="s">
         <v>40</v>
       </c>
@@ -8365,7 +8389,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="243" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A243" t="s">
         <v>40</v>
       </c>
@@ -8396,7 +8420,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="244" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A244" t="s">
         <v>40</v>
       </c>
@@ -8427,7 +8451,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="245" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A245" t="s">
         <v>40</v>
       </c>
@@ -8458,7 +8482,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="246" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A246" t="s">
         <v>40</v>
       </c>
@@ -8486,7 +8510,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="247" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A247" t="s">
         <v>40</v>
       </c>
@@ -8514,7 +8538,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="248" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A248" t="s">
         <v>40</v>
       </c>
@@ -8545,7 +8569,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="249" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A249" t="s">
         <v>40</v>
       </c>
@@ -8573,7 +8597,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="250" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A250" t="s">
         <v>40</v>
       </c>
@@ -8604,7 +8628,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="251" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A251" t="s">
         <v>40</v>
       </c>
@@ -8635,7 +8659,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="252" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A252" t="s">
         <v>40</v>
       </c>
@@ -8663,7 +8687,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="253" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A253" t="s">
         <v>40</v>
       </c>
@@ -8691,7 +8715,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="254" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A254" t="s">
         <v>40</v>
       </c>
@@ -8722,7 +8746,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="255" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A255" t="s">
         <v>40</v>
       </c>
@@ -8753,7 +8777,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="256" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A256" t="s">
         <v>40</v>
       </c>
@@ -8781,7 +8805,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="257" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A257" t="s">
         <v>41</v>
       </c>
@@ -8809,7 +8833,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="258" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A258" t="s">
         <v>41</v>
       </c>
@@ -8837,7 +8861,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="259" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A259" t="s">
         <v>41</v>
       </c>
@@ -8865,7 +8889,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="260" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A260" t="s">
         <v>41</v>
       </c>
@@ -8893,7 +8917,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="261" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A261" t="s">
         <v>41</v>
       </c>
@@ -8921,7 +8945,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="262" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A262" t="s">
         <v>41</v>
       </c>
@@ -8952,7 +8976,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="263" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A263" t="s">
         <v>41</v>
       </c>
@@ -8980,7 +9004,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="264" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A264" t="s">
         <v>41</v>
       </c>
@@ -9008,7 +9032,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="265" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A265" t="s">
         <v>41</v>
       </c>
@@ -9036,7 +9060,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="266" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A266" t="s">
         <v>41</v>
       </c>
@@ -9064,7 +9088,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="267" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A267" t="s">
         <v>41</v>
       </c>
@@ -9092,7 +9116,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="268" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A268" t="s">
         <v>41</v>
       </c>
@@ -9120,7 +9144,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="269" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A269" t="s">
         <v>41</v>
       </c>
@@ -9148,7 +9172,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="270" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A270" t="s">
         <v>41</v>
       </c>
@@ -9176,7 +9200,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="271" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A271" t="s">
         <v>41</v>
       </c>
@@ -9204,7 +9228,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="272" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A272" t="s">
         <v>41</v>
       </c>
@@ -9235,7 +9259,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="273" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A273" t="s">
         <v>41</v>
       </c>
@@ -9266,7 +9290,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="274" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A274" t="s">
         <v>41</v>
       </c>
@@ -9297,7 +9321,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="275" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A275" t="s">
         <v>41</v>
       </c>
@@ -9328,7 +9352,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="276" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A276" t="s">
         <v>41</v>
       </c>
@@ -9359,7 +9383,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="277" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A277" t="s">
         <v>41</v>
       </c>
@@ -9387,7 +9411,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="278" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A278" t="s">
         <v>41</v>
       </c>
@@ -9418,7 +9442,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="279" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A279" t="s">
         <v>41</v>
       </c>
@@ -9449,7 +9473,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="280" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A280" t="s">
         <v>41</v>
       </c>
@@ -9480,7 +9504,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="281" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A281" t="s">
         <v>41</v>
       </c>
@@ -9508,7 +9532,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="282" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A282" t="s">
         <v>41</v>
       </c>
@@ -9536,7 +9560,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="283" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A283" t="s">
         <v>41</v>
       </c>
@@ -9564,7 +9588,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="284" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A284" t="s">
         <v>41</v>
       </c>
@@ -9595,7 +9619,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="285" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A285" t="s">
         <v>41</v>
       </c>
@@ -9626,7 +9650,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="286" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A286" t="s">
         <v>41</v>
       </c>
@@ -9657,7 +9681,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="287" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A287" t="s">
         <v>41</v>
       </c>
@@ -9685,7 +9709,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="288" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A288" t="s">
         <v>41</v>
       </c>
@@ -9713,7 +9737,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="289" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A289" t="s">
         <v>41</v>
       </c>
@@ -9741,7 +9765,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="290" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A290" t="s">
         <v>41</v>
       </c>
@@ -9769,7 +9793,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="291" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A291" t="s">
         <v>41</v>
       </c>
@@ -9800,7 +9824,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="292" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A292" t="s">
         <v>41</v>
       </c>
@@ -9828,7 +9852,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="293" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A293" t="s">
         <v>41</v>
       </c>
@@ -9859,7 +9883,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="294" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A294" t="s">
         <v>41</v>
       </c>
@@ -9890,7 +9914,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="295" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A295" t="s">
         <v>41</v>
       </c>
@@ -9921,7 +9945,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="296" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A296" t="s">
         <v>41</v>
       </c>
@@ -9949,7 +9973,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="297" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A297" t="s">
         <v>41</v>
       </c>
@@ -9977,7 +10001,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="298" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A298" t="s">
         <v>41</v>
       </c>
@@ -10008,7 +10032,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="299" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A299" t="s">
         <v>41</v>
       </c>
@@ -10039,7 +10063,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="300" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A300" t="s">
         <v>41</v>
       </c>
@@ -10070,7 +10094,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="301" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A301" t="s">
         <v>41</v>
       </c>
@@ -10101,7 +10125,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="302" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A302" t="s">
         <v>41</v>
       </c>
@@ -10129,7 +10153,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="303" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A303" t="s">
         <v>41</v>
       </c>
@@ -10160,7 +10184,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="304" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A304" t="s">
         <v>41</v>
       </c>
@@ -10191,7 +10215,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="305" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A305" t="s">
         <v>41</v>
       </c>
@@ -10222,7 +10246,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="306" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A306" t="s">
         <v>41</v>
       </c>
@@ -10253,7 +10277,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="307" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A307" t="s">
         <v>41</v>
       </c>
@@ -10281,7 +10305,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="308" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A308" t="s">
         <v>41</v>
       </c>
@@ -10309,7 +10333,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="309" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A309" t="s">
         <v>41</v>
       </c>
@@ -10340,7 +10364,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="310" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A310" t="s">
         <v>41</v>
       </c>
@@ -10371,7 +10395,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="311" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A311" t="s">
         <v>41</v>
       </c>
@@ -10399,7 +10423,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="312" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A312" t="s">
         <v>41</v>
       </c>
@@ -10427,7 +10451,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="313" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A313" t="s">
         <v>41</v>
       </c>
@@ -10455,7 +10479,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="314" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A314" t="s">
         <v>41</v>
       </c>
@@ -10486,7 +10510,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="315" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A315" t="s">
         <v>41</v>
       </c>
@@ -10517,7 +10541,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="316" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A316" t="s">
         <v>41</v>
       </c>
@@ -10545,7 +10569,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="317" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A317" t="s">
         <v>41</v>
       </c>
@@ -10576,7 +10600,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="318" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A318" t="s">
         <v>41</v>
       </c>
@@ -10607,7 +10631,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="319" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A319" t="s">
         <v>41</v>
       </c>
@@ -10638,7 +10662,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="320" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A320" t="s">
         <v>41</v>
       </c>
@@ -10669,7 +10693,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="321" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A321" t="s">
         <v>41</v>
       </c>
@@ -10700,7 +10724,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="322" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A322" t="s">
         <v>41</v>
       </c>
@@ -10728,7 +10752,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="323" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A323" t="s">
         <v>41</v>
       </c>
@@ -10756,7 +10780,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="324" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A324" t="s">
         <v>41</v>
       </c>
@@ -10787,7 +10811,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="325" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A325" t="s">
         <v>41</v>
       </c>
@@ -10818,7 +10842,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="326" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A326" t="s">
         <v>41</v>
       </c>
@@ -10846,7 +10870,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="327" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A327" t="s">
         <v>41</v>
       </c>
@@ -10874,7 +10898,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="328" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A328" t="s">
         <v>41</v>
       </c>
@@ -10905,7 +10929,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="329" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A329" t="s">
         <v>41</v>
       </c>
@@ -10936,7 +10960,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="330" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A330" t="s">
         <v>41</v>
       </c>
@@ -10967,7 +10991,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="331" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A331" t="s">
         <v>41</v>
       </c>
@@ -10998,7 +11022,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="332" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A332" t="s">
         <v>41</v>
       </c>
@@ -11026,7 +11050,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="333" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A333" t="s">
         <v>41</v>
       </c>
@@ -11057,7 +11081,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="334" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A334" t="s">
         <v>41</v>
       </c>
@@ -11085,7 +11109,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="335" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A335" t="s">
         <v>41</v>
       </c>
@@ -11113,7 +11137,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="336" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A336" t="s">
         <v>41</v>
       </c>
@@ -11144,7 +11168,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="337" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A337" t="s">
         <v>41</v>
       </c>
@@ -11172,7 +11196,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="338" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A338" t="s">
         <v>41</v>
       </c>
@@ -11203,7 +11227,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="339" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A339" t="s">
         <v>41</v>
       </c>
@@ -11234,7 +11258,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="340" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A340" t="s">
         <v>41</v>
       </c>
@@ -11265,7 +11289,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="341" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A341" t="s">
         <v>41</v>
       </c>
@@ -11293,7 +11317,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="342" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A342" t="s">
         <v>41</v>
       </c>
@@ -11321,7 +11345,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="343" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A343" t="s">
         <v>41</v>
       </c>
@@ -11352,7 +11376,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="344" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A344" t="s">
         <v>41</v>
       </c>
@@ -11383,7 +11407,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="345" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A345" t="s">
         <v>41</v>
       </c>
@@ -11414,7 +11438,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="346" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A346" t="s">
         <v>41</v>
       </c>
@@ -11442,7 +11466,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="347" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A347" t="s">
         <v>41</v>
       </c>
@@ -11473,7 +11497,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="348" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A348" t="s">
         <v>41</v>
       </c>
@@ -11504,7 +11528,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="349" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A349" t="s">
         <v>41</v>
       </c>
@@ -11535,7 +11559,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="350" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A350" t="s">
         <v>41</v>
       </c>
@@ -11566,7 +11590,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="351" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A351" t="s">
         <v>41</v>
       </c>
@@ -11597,7 +11621,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="352" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A352" t="s">
         <v>41</v>
       </c>
@@ -11628,7 +11652,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="353" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A353" t="s">
         <v>41</v>
       </c>
@@ -11659,7 +11683,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="354" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A354" t="s">
         <v>41</v>
       </c>
@@ -11690,7 +11714,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="355" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A355" t="s">
         <v>41</v>
       </c>
@@ -11721,7 +11745,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="356" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A356" t="s">
         <v>41</v>
       </c>
@@ -11749,7 +11773,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="357" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A357" t="s">
         <v>41</v>
       </c>
@@ -11780,7 +11804,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="358" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A358" t="s">
         <v>41</v>
       </c>
@@ -11811,7 +11835,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="359" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A359" t="s">
         <v>41</v>
       </c>
@@ -11842,7 +11866,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="360" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A360" t="s">
         <v>41</v>
       </c>
@@ -11873,7 +11897,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="361" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A361" t="s">
         <v>41</v>
       </c>
@@ -11901,7 +11925,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="362" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A362" t="s">
         <v>41</v>
       </c>
@@ -11929,7 +11953,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="363" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A363" t="s">
         <v>41</v>
       </c>
@@ -11960,7 +11984,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="364" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A364" t="s">
         <v>41</v>
       </c>
@@ -11991,7 +12015,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="365" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A365" t="s">
         <v>41</v>
       </c>
@@ -12022,7 +12046,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="366" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A366" t="s">
         <v>41</v>
       </c>
@@ -12053,7 +12077,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="367" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A367" t="s">
         <v>41</v>
       </c>
@@ -12081,7 +12105,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="368" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A368" t="s">
         <v>41</v>
       </c>
@@ -12112,7 +12136,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="369" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A369" t="s">
         <v>41</v>
       </c>
@@ -12143,7 +12167,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="370" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A370" t="s">
         <v>41</v>
       </c>
@@ -12174,7 +12198,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="371" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A371" t="s">
         <v>41</v>
       </c>
@@ -12205,7 +12229,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="372" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A372" t="s">
         <v>41</v>
       </c>
@@ -12236,7 +12260,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="373" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A373" t="s">
         <v>41</v>
       </c>
@@ -12267,7 +12291,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="374" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A374" t="s">
         <v>41</v>
       </c>
@@ -12298,7 +12322,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="375" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A375" t="s">
         <v>41</v>
       </c>
@@ -12329,7 +12353,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="376" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A376" t="s">
         <v>41</v>
       </c>
@@ -12357,7 +12381,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="377" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A377" t="s">
         <v>41</v>
       </c>
@@ -12388,7 +12412,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="378" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A378" t="s">
         <v>41</v>
       </c>
@@ -12419,7 +12443,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="379" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A379" t="s">
         <v>41</v>
       </c>
@@ -12450,7 +12474,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="380" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A380" t="s">
         <v>41</v>
       </c>
@@ -12481,7 +12505,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="381" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A381" t="s">
         <v>41</v>
       </c>
@@ -12512,7 +12536,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="382" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A382" t="s">
         <v>41</v>
       </c>
@@ -12540,7 +12564,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="383" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A383" t="s">
         <v>41</v>
       </c>
@@ -12571,7 +12595,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="384" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A384" t="s">
         <v>41</v>
       </c>
@@ -12602,7 +12626,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="385" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A385" t="s">
         <v>41</v>
       </c>
@@ -12633,7 +12657,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="386" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A386" t="s">
         <v>41</v>
       </c>
@@ -12661,7 +12685,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="387" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A387" t="s">
         <v>41</v>
       </c>
@@ -12692,7 +12716,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="388" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A388" t="s">
         <v>41</v>
       </c>
@@ -12723,7 +12747,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="389" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A389" t="s">
         <v>41</v>
       </c>
@@ -12754,7 +12778,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="390" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A390" t="s">
         <v>41</v>
       </c>
@@ -12785,7 +12809,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="391" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A391" t="s">
         <v>41</v>
       </c>
@@ -12816,7 +12840,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="392" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A392" t="s">
         <v>41</v>
       </c>
@@ -12844,7 +12868,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="393" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A393" t="s">
         <v>41</v>
       </c>
@@ -12872,7 +12896,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="394" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A394" t="s">
         <v>41</v>
       </c>
@@ -12900,7 +12924,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="395" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A395" t="s">
         <v>41</v>
       </c>
@@ -12928,7 +12952,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="396" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A396" t="s">
         <v>41</v>
       </c>
@@ -12959,7 +12983,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="397" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A397" t="s">
         <v>41</v>
       </c>
@@ -12987,7 +13011,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="398" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A398" t="s">
         <v>41</v>
       </c>
@@ -13018,7 +13042,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="399" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A399" t="s">
         <v>41</v>
       </c>
@@ -13049,7 +13073,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="400" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A400" t="s">
         <v>41</v>
       </c>
@@ -13080,7 +13104,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="401" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A401" t="s">
         <v>41</v>
       </c>
@@ -13108,7 +13132,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="402" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A402" t="s">
         <v>41</v>
       </c>
@@ -13136,7 +13160,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="403" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A403" t="s">
         <v>41</v>
       </c>
@@ -13164,7 +13188,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="404" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A404" t="s">
         <v>41</v>
       </c>
@@ -13195,7 +13219,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="405" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A405" t="s">
         <v>41</v>
       </c>
@@ -13226,7 +13250,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="406" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A406" t="s">
         <v>41</v>
       </c>
@@ -13254,7 +13278,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="407" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A407" t="s">
         <v>41</v>
       </c>
@@ -13282,7 +13306,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="408" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A408" t="s">
         <v>41</v>
       </c>
@@ -13313,7 +13337,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="409" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A409" t="s">
         <v>41</v>
       </c>
@@ -13344,7 +13368,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="410" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A410" t="s">
         <v>41</v>
       </c>
@@ -13375,7 +13399,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="411" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A411" t="s">
         <v>41</v>
       </c>
@@ -13406,7 +13430,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="412" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A412" t="s">
         <v>41</v>
       </c>
@@ -13434,7 +13458,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="413" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A413" t="s">
         <v>41</v>
       </c>
@@ -13462,7 +13486,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="414" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A414" t="s">
         <v>41</v>
       </c>
@@ -13493,7 +13517,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="415" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A415" t="s">
         <v>41</v>
       </c>
@@ -13524,7 +13548,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="416" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A416" t="s">
         <v>41</v>
       </c>
@@ -13555,7 +13579,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="417" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A417" t="s">
         <v>41</v>
       </c>
@@ -13586,7 +13610,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="418" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A418" t="s">
         <v>41</v>
       </c>
@@ -13614,7 +13638,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="419" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A419" t="s">
         <v>41</v>
       </c>
@@ -13645,7 +13669,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="420" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A420" t="s">
         <v>41</v>
       </c>
@@ -13676,7 +13700,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="421" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A421" t="s">
         <v>41</v>
       </c>
@@ -13707,7 +13731,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="422" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A422" t="s">
         <v>41</v>
       </c>
@@ -13735,7 +13759,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="423" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A423" t="s">
         <v>41</v>
       </c>
@@ -13766,7 +13790,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="424" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A424" t="s">
         <v>41</v>
       </c>
@@ -13797,7 +13821,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="425" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A425" t="s">
         <v>41</v>
       </c>
@@ -13828,7 +13852,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="426" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A426" t="s">
         <v>41</v>
       </c>
@@ -13859,7 +13883,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="427" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A427" t="s">
         <v>41</v>
       </c>
@@ -13887,7 +13911,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="428" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A428" t="s">
         <v>41</v>
       </c>
@@ -13915,7 +13939,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="429" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A429" t="s">
         <v>41</v>
       </c>
@@ -13946,7 +13970,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="430" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A430" t="s">
         <v>41</v>
       </c>
@@ -13977,7 +14001,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="431" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A431" t="s">
         <v>41</v>
       </c>
@@ -14005,7 +14029,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="432" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A432" t="s">
         <v>41</v>
       </c>
@@ -14036,7 +14060,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="433" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A433" t="s">
         <v>41</v>
       </c>
@@ -14064,7 +14088,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="434" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A434" t="s">
         <v>41</v>
       </c>
@@ -14095,7 +14119,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="435" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A435" t="s">
         <v>41</v>
       </c>
@@ -14126,7 +14150,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="436" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A436" t="s">
         <v>41</v>
       </c>
@@ -14154,7 +14178,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="437" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A437" t="s">
         <v>41</v>
       </c>
@@ -14185,7 +14209,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="438" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A438" t="s">
         <v>41</v>
       </c>
@@ -14213,7 +14237,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="439" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A439" t="s">
         <v>41</v>
       </c>
@@ -14244,7 +14268,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="440" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A440" t="s">
         <v>41</v>
       </c>
@@ -14275,7 +14299,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="441" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A441" t="s">
         <v>41</v>
       </c>
@@ -14303,7 +14327,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="442" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A442" t="s">
         <v>41</v>
       </c>
@@ -14331,7 +14355,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="443" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A443" t="s">
         <v>41</v>
       </c>
@@ -14359,7 +14383,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="444" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A444" t="s">
         <v>41</v>
       </c>
@@ -14390,7 +14414,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="445" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A445" t="s">
         <v>41</v>
       </c>
@@ -14421,7 +14445,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="446" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A446" t="s">
         <v>41</v>
       </c>
@@ -14449,7 +14473,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="447" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A447" t="s">
         <v>41</v>
       </c>
@@ -14480,7 +14504,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="448" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A448" t="s">
         <v>41</v>
       </c>
@@ -14508,7 +14532,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="449" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A449" t="s">
         <v>41</v>
       </c>
@@ -14536,7 +14560,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="450" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A450" t="s">
         <v>41</v>
       </c>
@@ -14567,7 +14591,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="451" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A451" t="s">
         <v>41</v>
       </c>
@@ -14595,7 +14619,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="452" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A452" t="s">
         <v>40</v>
       </c>
@@ -14626,7 +14650,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="453" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A453" t="s">
         <v>40</v>
       </c>
@@ -14655,7 +14679,7 @@
       </c>
       <c r="I453" s="6"/>
     </row>
-    <row r="454" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A454" t="s">
         <v>40</v>
       </c>
@@ -14686,7 +14710,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="455" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A455" t="s">
         <v>40</v>
       </c>
@@ -14717,7 +14741,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="456" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A456" t="s">
         <v>40</v>
       </c>
@@ -14748,7 +14772,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="457" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A457" t="s">
         <v>40</v>
       </c>
@@ -14777,7 +14801,7 @@
       </c>
       <c r="I457" s="6"/>
     </row>
-    <row r="458" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A458" t="s">
         <v>40</v>
       </c>
@@ -14806,7 +14830,7 @@
       </c>
       <c r="I458" s="6"/>
     </row>
-    <row r="459" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A459" t="s">
         <v>40</v>
       </c>
@@ -14837,7 +14861,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="460" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A460" t="s">
         <v>40</v>
       </c>
@@ -14866,7 +14890,7 @@
       </c>
       <c r="I460" s="6"/>
     </row>
-    <row r="461" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A461" t="s">
         <v>40</v>
       </c>
@@ -14895,7 +14919,7 @@
       </c>
       <c r="I461" s="6"/>
     </row>
-    <row r="462" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A462" t="s">
         <v>40</v>
       </c>
@@ -14926,7 +14950,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="463" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A463" t="s">
         <v>40</v>
       </c>
@@ -14957,7 +14981,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="464" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A464" t="s">
         <v>40</v>
       </c>
@@ -14986,7 +15010,7 @@
       </c>
       <c r="I464" s="6"/>
     </row>
-    <row r="465" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A465" t="s">
         <v>40</v>
       </c>
@@ -15015,7 +15039,7 @@
       </c>
       <c r="I465" s="6"/>
     </row>
-    <row r="466" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A466" t="s">
         <v>40</v>
       </c>
@@ -15046,7 +15070,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="467" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A467" t="s">
         <v>40</v>
       </c>
@@ -15077,7 +15101,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="468" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A468" t="s">
         <v>40</v>
       </c>
@@ -15108,7 +15132,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="469" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A469" t="s">
         <v>40</v>
       </c>
@@ -15139,7 +15163,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="470" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A470" t="s">
         <v>40</v>
       </c>
@@ -15170,7 +15194,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="471" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A471" t="s">
         <v>40</v>
       </c>
@@ -15199,7 +15223,7 @@
       </c>
       <c r="I471" s="6"/>
     </row>
-    <row r="472" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A472" t="s">
         <v>40</v>
       </c>
@@ -15228,7 +15252,7 @@
       </c>
       <c r="I472" s="6"/>
     </row>
-    <row r="473" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A473" t="s">
         <v>40</v>
       </c>
@@ -15259,7 +15283,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="474" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A474" t="s">
         <v>40</v>
       </c>
@@ -15288,7 +15312,7 @@
       </c>
       <c r="I474" s="6"/>
     </row>
-    <row r="475" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A475" t="s">
         <v>40</v>
       </c>
@@ -15317,7 +15341,7 @@
       </c>
       <c r="I475" s="6"/>
     </row>
-    <row r="476" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A476" t="s">
         <v>40</v>
       </c>
@@ -15348,7 +15372,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="477" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A477" t="s">
         <v>40</v>
       </c>
@@ -15377,7 +15401,7 @@
       </c>
       <c r="I477" s="6"/>
     </row>
-    <row r="478" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A478" t="s">
         <v>40</v>
       </c>
@@ -15408,7 +15432,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="479" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A479" t="s">
         <v>40</v>
       </c>
@@ -15437,7 +15461,7 @@
       </c>
       <c r="I479" s="6"/>
     </row>
-    <row r="480" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A480" t="s">
         <v>40</v>
       </c>
@@ -15468,7 +15492,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="481" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A481" t="s">
         <v>40</v>
       </c>
@@ -15499,7 +15523,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="482" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A482" t="s">
         <v>40</v>
       </c>
@@ -15530,7 +15554,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="483" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A483" t="s">
         <v>40</v>
       </c>
@@ -15561,7 +15585,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="484" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A484" t="s">
         <v>40</v>
       </c>
@@ -15592,7 +15616,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="485" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A485" t="s">
         <v>40</v>
       </c>
@@ -15621,7 +15645,7 @@
       </c>
       <c r="I485" s="6"/>
     </row>
-    <row r="486" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A486" t="s">
         <v>40</v>
       </c>
@@ -15652,7 +15676,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="487" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A487" t="s">
         <v>40</v>
       </c>
@@ -15683,7 +15707,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="488" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A488" t="s">
         <v>40</v>
       </c>
@@ -15712,7 +15736,7 @@
       </c>
       <c r="I488" s="6"/>
     </row>
-    <row r="489" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A489" t="s">
         <v>40</v>
       </c>
@@ -15743,7 +15767,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="490" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A490" t="s">
         <v>40</v>
       </c>
@@ -15774,7 +15798,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="491" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A491" t="s">
         <v>40</v>
       </c>
@@ -15805,7 +15829,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="492" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A492" t="s">
         <v>40</v>
       </c>
@@ -15834,7 +15858,7 @@
       </c>
       <c r="I492" s="6"/>
     </row>
-    <row r="493" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A493" t="s">
         <v>40</v>
       </c>
@@ -15863,7 +15887,7 @@
       </c>
       <c r="I493" s="6"/>
     </row>
-    <row r="494" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A494" t="s">
         <v>40</v>
       </c>
@@ -15894,7 +15918,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="495" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A495" t="s">
         <v>40</v>
       </c>
@@ -15925,7 +15949,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="496" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A496" t="s">
         <v>40</v>
       </c>
@@ -15956,7 +15980,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="497" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A497" t="s">
         <v>40</v>
       </c>
@@ -15987,7 +16011,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="498" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A498" t="s">
         <v>40</v>
       </c>
@@ -16016,7 +16040,7 @@
       </c>
       <c r="I498" s="6"/>
     </row>
-    <row r="499" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A499" t="s">
         <v>40</v>
       </c>
@@ -16045,7 +16069,7 @@
       </c>
       <c r="I499" s="6"/>
     </row>
-    <row r="500" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A500" t="s">
         <v>40</v>
       </c>
@@ -16076,7 +16100,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="501" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A501" t="s">
         <v>40</v>
       </c>
@@ -16107,7 +16131,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="502" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A502" t="s">
         <v>40</v>
       </c>
@@ -16138,7 +16162,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="503" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A503" t="s">
         <v>40</v>
       </c>
@@ -16169,7 +16193,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="504" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A504" t="s">
         <v>40</v>
       </c>
@@ -16198,7 +16222,7 @@
       </c>
       <c r="I504" s="6"/>
     </row>
-    <row r="505" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A505" t="s">
         <v>40</v>
       </c>
@@ -16229,7 +16253,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="506" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A506" t="s">
         <v>40</v>
       </c>
@@ -16260,7 +16284,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="507" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A507" t="s">
         <v>40</v>
       </c>
@@ -16289,7 +16313,7 @@
       </c>
       <c r="I507" s="6"/>
     </row>
-    <row r="508" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A508" t="s">
         <v>40</v>
       </c>
@@ -16320,7 +16344,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="509" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A509" t="s">
         <v>40</v>
       </c>
@@ -16349,7 +16373,7 @@
       </c>
       <c r="I509" s="6"/>
     </row>
-    <row r="510" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A510" t="s">
         <v>40</v>
       </c>
@@ -16380,7 +16404,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="511" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A511" t="s">
         <v>40</v>
       </c>
@@ -16411,7 +16435,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="512" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A512" t="s">
         <v>40</v>
       </c>
@@ -16442,7 +16466,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="513" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A513" t="s">
         <v>40</v>
       </c>
@@ -16471,7 +16495,7 @@
       </c>
       <c r="I513" s="6"/>
     </row>
-    <row r="514" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A514" t="s">
         <v>40</v>
       </c>
@@ -16502,7 +16526,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="515" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A515" t="s">
         <v>40</v>
       </c>
@@ -16533,7 +16557,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="516" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A516" t="s">
         <v>40</v>
       </c>
@@ -16562,7 +16586,7 @@
       </c>
       <c r="I516" s="6"/>
     </row>
-    <row r="517" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A517" t="s">
         <v>40</v>
       </c>
@@ -16593,7 +16617,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="518" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A518" t="s">
         <v>40</v>
       </c>
@@ -16624,7 +16648,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="519" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A519" t="s">
         <v>40</v>
       </c>
@@ -16655,7 +16679,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="520" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A520" t="s">
         <v>40</v>
       </c>
@@ -16686,7 +16710,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="521" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A521" t="s">
         <v>40</v>
       </c>
@@ -16717,7 +16741,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="522" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A522" t="s">
         <v>40</v>
       </c>
@@ -16748,7 +16772,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="523" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A523" t="s">
         <v>40</v>
       </c>
@@ -16779,7 +16803,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="524" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A524" t="s">
         <v>40</v>
       </c>
@@ -16810,7 +16834,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="525" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A525" t="s">
         <v>40</v>
       </c>
@@ -16841,7 +16865,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="526" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A526" t="s">
         <v>40</v>
       </c>
@@ -16872,7 +16896,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="527" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A527" t="s">
         <v>40</v>
       </c>
@@ -16901,7 +16925,7 @@
       </c>
       <c r="I527" s="6"/>
     </row>
-    <row r="528" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A528" t="s">
         <v>40</v>
       </c>
@@ -16930,7 +16954,7 @@
       </c>
       <c r="I528" s="6"/>
     </row>
-    <row r="529" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="529" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A529" t="s">
         <v>40</v>
       </c>
@@ -16961,7 +16985,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="530" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="530" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A530" t="s">
         <v>40</v>
       </c>
@@ -16992,7 +17016,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="531" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="531" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A531" t="s">
         <v>40</v>
       </c>
@@ -17021,7 +17045,7 @@
       </c>
       <c r="I531" s="6"/>
     </row>
-    <row r="532" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A532" t="s">
         <v>40</v>
       </c>
@@ -17050,7 +17074,7 @@
       </c>
       <c r="I532" s="6"/>
     </row>
-    <row r="533" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="533" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A533" t="s">
         <v>40</v>
       </c>
@@ -17081,7 +17105,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="534" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="534" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A534" t="s">
         <v>40</v>
       </c>
@@ -17110,7 +17134,7 @@
       </c>
       <c r="I534" s="6"/>
     </row>
-    <row r="535" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="535" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A535" t="s">
         <v>40</v>
       </c>
@@ -17139,7 +17163,7 @@
       </c>
       <c r="I535" s="6"/>
     </row>
-    <row r="536" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="536" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A536" t="s">
         <v>40</v>
       </c>
@@ -17170,7 +17194,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="537" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A537" t="s">
         <v>40</v>
       </c>
@@ -17199,7 +17223,7 @@
       </c>
       <c r="I537" s="6"/>
     </row>
-    <row r="538" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="538" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A538" t="s">
         <v>40</v>
       </c>
@@ -17230,7 +17254,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="539" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="539" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A539" t="s">
         <v>40</v>
       </c>
@@ -17261,7 +17285,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="540" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="540" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A540" t="s">
         <v>40</v>
       </c>
@@ -17292,7 +17316,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="541" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="541" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A541" t="s">
         <v>40</v>
       </c>
@@ -17321,7 +17345,7 @@
       </c>
       <c r="I541" s="6"/>
     </row>
-    <row r="542" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="542" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A542" t="s">
         <v>40</v>
       </c>
@@ -17352,7 +17376,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="543" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="543" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A543" t="s">
         <v>40</v>
       </c>
@@ -17383,7 +17407,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="544" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="544" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A544" t="s">
         <v>40</v>
       </c>
@@ -17414,7 +17438,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="545" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="545" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A545" t="s">
         <v>40</v>
       </c>
@@ -17445,7 +17469,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="546" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A546" t="s">
         <v>40</v>
       </c>
@@ -17476,7 +17500,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="547" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="547" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A547" t="s">
         <v>40</v>
       </c>
@@ -17507,7 +17531,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="548" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A548" t="s">
         <v>40</v>
       </c>
@@ -17536,7 +17560,7 @@
       </c>
       <c r="I548" s="6"/>
     </row>
-    <row r="549" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A549" t="s">
         <v>40</v>
       </c>
@@ -17567,7 +17591,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="550" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A550" t="s">
         <v>40</v>
       </c>
@@ -17598,7 +17622,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="551" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="551" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A551" t="s">
         <v>40</v>
       </c>
@@ -17627,7 +17651,7 @@
       </c>
       <c r="I551" s="6"/>
     </row>
-    <row r="552" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="552" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A552" t="s">
         <v>40</v>
       </c>
@@ -17656,7 +17680,7 @@
       </c>
       <c r="I552" s="6"/>
     </row>
-    <row r="553" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="553" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A553" t="s">
         <v>40</v>
       </c>
@@ -17685,7 +17709,7 @@
       </c>
       <c r="I553" s="6"/>
     </row>
-    <row r="554" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="554" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A554" t="s">
         <v>40</v>
       </c>
@@ -17716,7 +17740,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="555" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="555" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A555" t="s">
         <v>40</v>
       </c>
@@ -17745,7 +17769,7 @@
       </c>
       <c r="I555" s="6"/>
     </row>
-    <row r="556" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="556" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A556" t="s">
         <v>40</v>
       </c>
@@ -17774,7 +17798,7 @@
       </c>
       <c r="I556" s="6"/>
     </row>
-    <row r="557" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A557" t="s">
         <v>40</v>
       </c>
@@ -17805,7 +17829,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="558" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="558" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A558" t="s">
         <v>40</v>
       </c>
@@ -17836,7 +17860,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="559" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="559" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A559" t="s">
         <v>40</v>
       </c>
@@ -17865,7 +17889,7 @@
       </c>
       <c r="I559" s="6"/>
     </row>
-    <row r="560" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A560" t="s">
         <v>40</v>
       </c>
@@ -17896,7 +17920,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="561" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A561" t="s">
         <v>40</v>
       </c>
@@ -17927,7 +17951,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="562" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A562" t="s">
         <v>40</v>
       </c>
@@ -17956,7 +17980,7 @@
       </c>
       <c r="I562" s="6"/>
     </row>
-    <row r="563" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A563" t="s">
         <v>40</v>
       </c>
@@ -17985,7 +18009,7 @@
       </c>
       <c r="I563" s="6"/>
     </row>
-    <row r="564" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A564" t="s">
         <v>40</v>
       </c>
@@ -18014,7 +18038,7 @@
       </c>
       <c r="I564" s="6"/>
     </row>
-    <row r="565" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="565" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A565" t="s">
         <v>40</v>
       </c>
@@ -18043,7 +18067,7 @@
       </c>
       <c r="I565" s="6"/>
     </row>
-    <row r="566" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="566" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A566" t="s">
         <v>40</v>
       </c>
@@ -18072,7 +18096,7 @@
       </c>
       <c r="I566" s="6"/>
     </row>
-    <row r="567" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="567" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A567" t="s">
         <v>40</v>
       </c>
@@ -18101,7 +18125,7 @@
       </c>
       <c r="I567" s="6"/>
     </row>
-    <row r="568" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="568" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A568" t="s">
         <v>40</v>
       </c>
@@ -18132,7 +18156,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="569" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="569" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A569" t="s">
         <v>40</v>
       </c>
@@ -18161,7 +18185,7 @@
       </c>
       <c r="I569" s="6"/>
     </row>
-    <row r="570" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="570" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A570" t="s">
         <v>40</v>
       </c>
@@ -18192,7 +18216,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="571" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="571" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A571" t="s">
         <v>40</v>
       </c>
@@ -18223,7 +18247,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="572" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="572" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A572" t="s">
         <v>40</v>
       </c>
@@ -18254,7 +18278,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="573" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="573" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A573" t="s">
         <v>40</v>
       </c>
@@ -18285,7 +18309,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="574" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="574" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A574" t="s">
         <v>40</v>
       </c>
@@ -18316,7 +18340,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="575" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="575" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A575" t="s">
         <v>40</v>
       </c>
@@ -18347,7 +18371,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="576" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="576" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A576" t="s">
         <v>40</v>
       </c>
@@ -18376,7 +18400,7 @@
       </c>
       <c r="I576" s="6"/>
     </row>
-    <row r="577" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="577" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A577" t="s">
         <v>40</v>
       </c>
@@ -18405,7 +18429,7 @@
       </c>
       <c r="I577" s="6"/>
     </row>
-    <row r="578" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="578" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A578" t="s">
         <v>40</v>
       </c>
@@ -18436,7 +18460,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="579" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="579" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A579" t="s">
         <v>40</v>
       </c>
@@ -18465,7 +18489,7 @@
       </c>
       <c r="I579" s="6"/>
     </row>
-    <row r="580" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="580" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A580" t="s">
         <v>40</v>
       </c>
@@ -18496,7 +18520,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="581" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="581" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A581" t="s">
         <v>40</v>
       </c>
@@ -18525,7 +18549,7 @@
       </c>
       <c r="I581" s="6"/>
     </row>
-    <row r="582" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="582" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A582" t="s">
         <v>40</v>
       </c>
@@ -18556,7 +18580,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="583" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="583" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A583" t="s">
         <v>40</v>
       </c>
@@ -18585,7 +18609,7 @@
       </c>
       <c r="I583" s="6"/>
     </row>
-    <row r="584" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="584" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A584" t="s">
         <v>40</v>
       </c>
@@ -18616,7 +18640,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="585" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="585" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A585" t="s">
         <v>40</v>
       </c>
@@ -18647,7 +18671,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="586" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="586" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A586" t="s">
         <v>40</v>
       </c>
@@ -18678,7 +18702,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="587" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="587" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A587" t="s">
         <v>40</v>
       </c>
@@ -18709,7 +18733,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="588" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="588" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A588" t="s">
         <v>40</v>
       </c>
@@ -18740,7 +18764,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="589" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="589" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A589" t="s">
         <v>40</v>
       </c>
@@ -18771,7 +18795,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="590" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="590" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A590" t="s">
         <v>40</v>
       </c>
@@ -18800,7 +18824,7 @@
       </c>
       <c r="I590" s="6"/>
     </row>
-    <row r="591" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="591" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A591" t="s">
         <v>40</v>
       </c>
@@ -18829,7 +18853,7 @@
       </c>
       <c r="I591" s="6"/>
     </row>
-    <row r="592" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="592" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A592" t="s">
         <v>40</v>
       </c>
@@ -18857,7 +18881,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="593" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="593" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A593" t="s">
         <v>40</v>
       </c>
@@ -18885,7 +18909,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="594" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="594" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A594" t="s">
         <v>40</v>
       </c>
@@ -18913,7 +18937,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="595" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="595" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A595" t="s">
         <v>40</v>
       </c>
@@ -18941,7 +18965,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="596" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="596" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A596" t="s">
         <v>40</v>
       </c>
@@ -18969,7 +18993,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="597" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="597" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A597" t="s">
         <v>40</v>
       </c>
@@ -19000,7 +19024,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="598" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="598" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A598" t="s">
         <v>40</v>
       </c>
@@ -19028,7 +19052,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="599" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="599" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A599" t="s">
         <v>40</v>
       </c>
@@ -19056,7 +19080,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="600" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="600" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A600" t="s">
         <v>40</v>
       </c>
@@ -19084,7 +19108,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="601" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="601" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A601" t="s">
         <v>40</v>
       </c>
@@ -19112,7 +19136,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="602" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="602" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A602" t="s">
         <v>40</v>
       </c>
@@ -19140,7 +19164,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="603" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="603" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A603" t="s">
         <v>40</v>
       </c>
@@ -19168,7 +19192,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="604" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="604" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A604" t="s">
         <v>40</v>
       </c>
@@ -19196,7 +19220,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="605" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="605" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A605" t="s">
         <v>40</v>
       </c>
@@ -19224,7 +19248,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="606" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="606" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A606" t="s">
         <v>40</v>
       </c>
@@ -19255,7 +19279,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="607" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="607" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A607" t="s">
         <v>40</v>
       </c>
@@ -19284,7 +19308,7 @@
       </c>
       <c r="I607" s="6"/>
     </row>
-    <row r="608" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="608" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A608" t="s">
         <v>40</v>
       </c>
@@ -19315,7 +19339,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="609" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="609" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A609" t="s">
         <v>40</v>
       </c>
@@ -19344,7 +19368,7 @@
       </c>
       <c r="I609" s="6"/>
     </row>
-    <row r="610" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="610" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A610" t="s">
         <v>40</v>
       </c>
@@ -19375,7 +19399,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="611" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="611" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A611" t="s">
         <v>40</v>
       </c>
@@ -19404,7 +19428,7 @@
       </c>
       <c r="I611" s="6"/>
     </row>
-    <row r="612" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="612" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A612" t="s">
         <v>40</v>
       </c>
@@ -19435,7 +19459,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="613" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="613" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A613" t="s">
         <v>40</v>
       </c>
@@ -19466,7 +19490,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="614" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="614" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A614" t="s">
         <v>40</v>
       </c>
@@ -19497,7 +19521,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="615" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="615" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A615" t="s">
         <v>40</v>
       </c>
@@ -19528,7 +19552,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="616" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="616" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A616" t="s">
         <v>40</v>
       </c>
@@ -19559,7 +19583,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="617" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="617" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A617" t="s">
         <v>40</v>
       </c>
@@ -19590,7 +19614,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="618" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="618" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A618" t="s">
         <v>40</v>
       </c>
@@ -19619,7 +19643,7 @@
       </c>
       <c r="I618" s="6"/>
     </row>
-    <row r="619" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="619" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A619" t="s">
         <v>40</v>
       </c>
@@ -19648,7 +19672,7 @@
       </c>
       <c r="I619" s="6"/>
     </row>
-    <row r="620" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="620" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A620" t="s">
         <v>40</v>
       </c>
@@ -19677,7 +19701,7 @@
       </c>
       <c r="I620" s="6"/>
     </row>
-    <row r="621" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="621" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A621" t="s">
         <v>40</v>
       </c>
@@ -19708,7 +19732,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="622" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="622" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A622" t="s">
         <v>40</v>
       </c>
@@ -19737,7 +19761,7 @@
       </c>
       <c r="I622" s="6"/>
     </row>
-    <row r="623" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="623" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A623" t="s">
         <v>40</v>
       </c>
@@ -19766,7 +19790,7 @@
       </c>
       <c r="I623" s="6"/>
     </row>
-    <row r="624" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="624" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A624" t="s">
         <v>40</v>
       </c>
@@ -19797,7 +19821,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="625" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="625" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A625" t="s">
         <v>40</v>
       </c>
@@ -19826,7 +19850,7 @@
       </c>
       <c r="I625" s="6"/>
     </row>
-    <row r="626" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="626" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A626" t="s">
         <v>40</v>
       </c>
@@ -19857,7 +19881,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="627" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="627" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A627" t="s">
         <v>40</v>
       </c>
@@ -19888,7 +19912,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="628" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="628" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A628" t="s">
         <v>40</v>
       </c>
@@ -19917,7 +19941,7 @@
       </c>
       <c r="I628" s="6"/>
     </row>
-    <row r="629" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="629" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A629" t="s">
         <v>40</v>
       </c>
@@ -19948,7 +19972,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="630" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="630" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A630" t="s">
         <v>40</v>
       </c>
@@ -19979,7 +20003,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="631" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="631" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A631" t="s">
         <v>40</v>
       </c>
@@ -20010,7 +20034,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="632" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="632" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A632" t="s">
         <v>40</v>
       </c>
@@ -20039,7 +20063,7 @@
       </c>
       <c r="I632" s="6"/>
     </row>
-    <row r="633" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="633" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A633" t="s">
         <v>40</v>
       </c>
@@ -20070,7 +20094,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="634" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="634" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A634" t="s">
         <v>40</v>
       </c>
@@ -20099,7 +20123,7 @@
       </c>
       <c r="I634" s="6"/>
     </row>
-    <row r="635" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="635" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A635" t="s">
         <v>40</v>
       </c>
@@ -20130,7 +20154,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="636" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="636" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A636" t="s">
         <v>40</v>
       </c>
@@ -20159,7 +20183,7 @@
       </c>
       <c r="I636" s="6"/>
     </row>
-    <row r="637" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="637" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A637" t="s">
         <v>40</v>
       </c>
@@ -20188,7 +20212,7 @@
       </c>
       <c r="I637" s="6"/>
     </row>
-    <row r="638" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="638" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A638" t="s">
         <v>40</v>
       </c>
@@ -20219,7 +20243,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="639" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="639" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A639" t="s">
         <v>40</v>
       </c>
@@ -20248,7 +20272,7 @@
       </c>
       <c r="I639" s="6"/>
     </row>
-    <row r="640" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="640" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A640" t="s">
         <v>40</v>
       </c>
@@ -20279,7 +20303,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="641" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="641" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A641" t="s">
         <v>40</v>
       </c>
@@ -20310,7 +20334,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="642" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="642" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A642" t="s">
         <v>40</v>
       </c>
@@ -20341,7 +20365,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="643" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="643" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A643" t="s">
         <v>40</v>
       </c>
@@ -20372,7 +20396,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="644" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="644" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A644" t="s">
         <v>40</v>
       </c>
@@ -20403,7 +20427,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="645" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="645" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A645" t="s">
         <v>40</v>
       </c>
@@ -20434,7 +20458,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="646" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="646" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A646" t="s">
         <v>40</v>
       </c>
@@ -20463,7 +20487,7 @@
       </c>
       <c r="I646" s="6"/>
     </row>
-    <row r="647" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="647" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A647" t="s">
         <v>40</v>
       </c>
@@ -20494,7 +20518,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="648" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="648" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A648" t="s">
         <v>41</v>
       </c>
@@ -20525,7 +20549,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="649" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="649" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A649" t="s">
         <v>41</v>
       </c>
@@ -20554,7 +20578,7 @@
       </c>
       <c r="I649" s="6"/>
     </row>
-    <row r="650" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="650" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A650" t="s">
         <v>41</v>
       </c>
@@ -20585,7 +20609,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="651" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="651" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A651" t="s">
         <v>41</v>
       </c>
@@ -20616,7 +20640,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="652" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="652" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A652" t="s">
         <v>41</v>
       </c>
@@ -20647,7 +20671,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="653" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="653" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A653" t="s">
         <v>41</v>
       </c>
@@ -20678,7 +20702,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="654" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="654" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A654" t="s">
         <v>41</v>
       </c>
@@ -20707,7 +20731,7 @@
       </c>
       <c r="I654" s="6"/>
     </row>
-    <row r="655" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="655" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A655" t="s">
         <v>41</v>
       </c>
@@ -20738,7 +20762,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="656" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="656" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A656" t="s">
         <v>41</v>
       </c>
@@ -20769,7 +20793,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="657" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="657" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A657" t="s">
         <v>41</v>
       </c>
@@ -20798,7 +20822,7 @@
       </c>
       <c r="I657" s="6"/>
     </row>
-    <row r="658" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="658" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A658" t="s">
         <v>41</v>
       </c>
@@ -20827,7 +20851,7 @@
       </c>
       <c r="I658" s="6"/>
     </row>
-    <row r="659" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="659" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A659" t="s">
         <v>41</v>
       </c>
@@ -20858,7 +20882,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="660" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="660" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A660" t="s">
         <v>41</v>
       </c>
@@ -20889,7 +20913,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="661" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="661" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A661" t="s">
         <v>41</v>
       </c>
@@ -20920,7 +20944,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="662" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="662" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A662" t="s">
         <v>41</v>
       </c>
@@ -20951,7 +20975,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="663" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="663" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A663" t="s">
         <v>41</v>
       </c>
@@ -20980,7 +21004,7 @@
       </c>
       <c r="I663" s="6"/>
     </row>
-    <row r="664" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="664" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A664" t="s">
         <v>41</v>
       </c>
@@ -21009,7 +21033,7 @@
       </c>
       <c r="I664" s="6"/>
     </row>
-    <row r="665" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="665" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A665" t="s">
         <v>41</v>
       </c>
@@ -21040,7 +21064,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="666" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="666" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A666" t="s">
         <v>41</v>
       </c>
@@ -21071,7 +21095,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="667" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="667" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A667" t="s">
         <v>41</v>
       </c>
@@ -21102,7 +21126,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="668" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="668" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A668" t="s">
         <v>41</v>
       </c>
@@ -21131,7 +21155,7 @@
       </c>
       <c r="I668" s="6"/>
     </row>
-    <row r="669" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="669" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A669" t="s">
         <v>41</v>
       </c>
@@ -21160,7 +21184,7 @@
       </c>
       <c r="I669" s="6"/>
     </row>
-    <row r="670" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="670" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A670" t="s">
         <v>41</v>
       </c>
@@ -21191,7 +21215,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="671" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="671" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A671" t="s">
         <v>41</v>
       </c>
@@ -21222,7 +21246,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="672" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="672" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A672" t="s">
         <v>41</v>
       </c>
@@ -21253,7 +21277,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="673" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="673" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A673" t="s">
         <v>41</v>
       </c>
@@ -21284,7 +21308,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="674" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="674" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A674" t="s">
         <v>41</v>
       </c>
@@ -21315,7 +21339,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="675" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="675" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A675" t="s">
         <v>41</v>
       </c>
@@ -21346,7 +21370,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="676" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="676" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A676" t="s">
         <v>41</v>
       </c>
@@ -21377,7 +21401,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="677" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="677" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A677" t="s">
         <v>41</v>
       </c>
@@ -21408,7 +21432,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="678" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="678" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A678" t="s">
         <v>41</v>
       </c>
@@ -21437,7 +21461,7 @@
       </c>
       <c r="I678" s="6"/>
     </row>
-    <row r="679" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="679" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A679" t="s">
         <v>41</v>
       </c>
@@ -21468,7 +21492,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="680" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="680" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A680" t="s">
         <v>41</v>
       </c>
@@ -21499,7 +21523,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="681" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="681" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A681" t="s">
         <v>41</v>
       </c>
@@ -21530,7 +21554,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="682" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="682" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A682" t="s">
         <v>41</v>
       </c>
@@ -21561,7 +21585,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="683" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="683" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A683" t="s">
         <v>41</v>
       </c>
@@ -21590,7 +21614,7 @@
       </c>
       <c r="I683" s="6"/>
     </row>
-    <row r="684" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="684" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A684" t="s">
         <v>41</v>
       </c>
@@ -21619,7 +21643,7 @@
       </c>
       <c r="I684" s="6"/>
     </row>
-    <row r="685" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="685" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A685" t="s">
         <v>41</v>
       </c>
@@ -21648,7 +21672,7 @@
       </c>
       <c r="I685" s="6"/>
     </row>
-    <row r="686" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="686" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A686" t="s">
         <v>41</v>
       </c>
@@ -21679,7 +21703,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="687" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="687" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A687" t="s">
         <v>41</v>
       </c>
@@ -21708,7 +21732,7 @@
       </c>
       <c r="I687" s="6"/>
     </row>
-    <row r="688" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="688" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A688" t="s">
         <v>41</v>
       </c>
@@ -21739,7 +21763,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="689" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="689" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A689" t="s">
         <v>41</v>
       </c>
@@ -21770,7 +21794,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="690" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="690" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A690" t="s">
         <v>41</v>
       </c>
@@ -21801,7 +21825,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="691" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="691" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A691" t="s">
         <v>41</v>
       </c>
@@ -21830,7 +21854,7 @@
       </c>
       <c r="I691" s="6"/>
     </row>
-    <row r="692" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="692" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A692" t="s">
         <v>41</v>
       </c>
@@ -21861,7 +21885,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="693" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="693" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A693" t="s">
         <v>41</v>
       </c>
@@ -21892,7 +21916,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="694" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="694" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A694" t="s">
         <v>41</v>
       </c>
@@ -21923,7 +21947,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="695" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="695" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A695" t="s">
         <v>41</v>
       </c>
@@ -21954,7 +21978,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="696" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="696" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A696" t="s">
         <v>41</v>
       </c>
@@ -21985,7 +22009,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="697" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="697" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A697" t="s">
         <v>41</v>
       </c>
@@ -22016,7 +22040,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="698" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="698" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A698" t="s">
         <v>41</v>
       </c>
@@ -22045,7 +22069,7 @@
       </c>
       <c r="I698" s="6"/>
     </row>
-    <row r="699" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="699" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A699" t="s">
         <v>41</v>
       </c>
@@ -22074,7 +22098,7 @@
       </c>
       <c r="I699" s="6"/>
     </row>
-    <row r="700" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="700" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A700" t="s">
         <v>41</v>
       </c>
@@ -22105,7 +22129,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="701" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="701" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A701" t="s">
         <v>41</v>
       </c>
@@ -22136,7 +22160,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="702" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="702" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A702" t="s">
         <v>41</v>
       </c>
@@ -22167,7 +22191,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="703" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="703" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A703" t="s">
         <v>41</v>
       </c>
@@ -22198,7 +22222,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="704" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="704" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A704" t="s">
         <v>41</v>
       </c>
@@ -22229,7 +22253,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="705" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="705" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A705" t="s">
         <v>41</v>
       </c>
@@ -22260,7 +22284,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="706" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="706" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A706" t="s">
         <v>41</v>
       </c>
@@ -22289,7 +22313,7 @@
       </c>
       <c r="I706" s="6"/>
     </row>
-    <row r="707" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="707" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A707" t="s">
         <v>41</v>
       </c>
@@ -22318,7 +22342,7 @@
       </c>
       <c r="I707" s="6"/>
     </row>
-    <row r="708" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="708" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A708" t="s">
         <v>41</v>
       </c>
@@ -22349,7 +22373,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="709" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="709" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A709" t="s">
         <v>41</v>
       </c>
@@ -22378,7 +22402,7 @@
       </c>
       <c r="I709" s="6"/>
     </row>
-    <row r="710" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="710" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A710" t="s">
         <v>41</v>
       </c>
@@ -22409,7 +22433,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="711" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="711" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A711" t="s">
         <v>41</v>
       </c>
@@ -22440,7 +22464,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="712" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="712" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A712" t="s">
         <v>41</v>
       </c>
@@ -22471,7 +22495,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="713" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="713" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A713" t="s">
         <v>41</v>
       </c>
@@ -22502,7 +22526,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="714" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="714" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A714" t="s">
         <v>41</v>
       </c>
@@ -22531,7 +22555,7 @@
       </c>
       <c r="I714" s="6"/>
     </row>
-    <row r="715" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="715" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A715" t="s">
         <v>41</v>
       </c>
@@ -22562,7 +22586,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="716" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="716" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A716" t="s">
         <v>41</v>
       </c>
@@ -22593,7 +22617,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="717" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="717" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A717" t="s">
         <v>41</v>
       </c>
@@ -22624,7 +22648,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="718" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="718" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A718" t="s">
         <v>41</v>
       </c>
@@ -22653,7 +22677,7 @@
       </c>
       <c r="I718" s="6"/>
     </row>
-    <row r="719" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="719" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A719" t="s">
         <v>41</v>
       </c>
@@ -22684,7 +22708,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="720" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="720" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A720" t="s">
         <v>41</v>
       </c>
@@ -22715,7 +22739,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="721" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="721" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A721" t="s">
         <v>41</v>
       </c>
@@ -22744,7 +22768,7 @@
       </c>
       <c r="I721" s="6"/>
     </row>
-    <row r="722" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="722" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A722" t="s">
         <v>41</v>
       </c>
@@ -22775,7 +22799,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="723" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="723" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A723" t="s">
         <v>41</v>
       </c>
@@ -22804,7 +22828,7 @@
       </c>
       <c r="I723" s="6"/>
     </row>
-    <row r="724" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="724" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A724" t="s">
         <v>41</v>
       </c>
@@ -22835,7 +22859,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="725" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="725" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A725" t="s">
         <v>41</v>
       </c>
@@ -22866,7 +22890,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="726" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="726" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A726" t="s">
         <v>41</v>
       </c>
@@ -22897,7 +22921,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="727" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="727" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A727" t="s">
         <v>41</v>
       </c>
@@ -22928,7 +22952,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="728" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="728" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A728" t="s">
         <v>41</v>
       </c>
@@ -22959,7 +22983,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="729" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="729" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A729" t="s">
         <v>41</v>
       </c>
@@ -22988,7 +23012,7 @@
       </c>
       <c r="I729" s="6"/>
     </row>
-    <row r="730" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="730" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A730" t="s">
         <v>41</v>
       </c>
@@ -23019,7 +23043,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="731" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="731" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A731" t="s">
         <v>41</v>
       </c>
@@ -23050,7 +23074,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="732" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="732" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A732" t="s">
         <v>41</v>
       </c>
@@ -23081,7 +23105,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="733" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="733" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A733" t="s">
         <v>41</v>
       </c>
@@ -23112,7 +23136,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="734" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="734" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A734" t="s">
         <v>41</v>
       </c>
@@ -23143,7 +23167,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="735" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="735" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A735" t="s">
         <v>41</v>
       </c>
@@ -23174,7 +23198,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="736" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="736" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A736" t="s">
         <v>41</v>
       </c>
@@ -23203,7 +23227,7 @@
       </c>
       <c r="I736" s="6"/>
     </row>
-    <row r="737" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="737" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A737" t="s">
         <v>41</v>
       </c>
@@ -23234,7 +23258,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="738" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="738" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A738" t="s">
         <v>41</v>
       </c>
@@ -23265,7 +23289,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="739" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="739" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A739" t="s">
         <v>41</v>
       </c>
@@ -23296,7 +23320,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="740" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="740" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A740" t="s">
         <v>41</v>
       </c>
@@ -23327,7 +23351,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="741" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="741" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A741" t="s">
         <v>41</v>
       </c>
@@ -23358,7 +23382,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="742" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="742" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A742" t="s">
         <v>41</v>
       </c>
@@ -23389,7 +23413,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="743" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="743" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A743" t="s">
         <v>41</v>
       </c>
@@ -23420,7 +23444,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="744" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="744" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A744" t="s">
         <v>41</v>
       </c>
@@ -23451,7 +23475,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="745" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="745" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A745" t="s">
         <v>41</v>
       </c>
@@ -23482,7 +23506,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="746" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="746" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A746" t="s">
         <v>41</v>
       </c>
@@ -23513,7 +23537,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="747" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="747" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A747" t="s">
         <v>41</v>
       </c>
@@ -23544,7 +23568,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="748" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="748" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A748" t="s">
         <v>41</v>
       </c>
@@ -23573,7 +23597,7 @@
       </c>
       <c r="I748" s="6"/>
     </row>
-    <row r="749" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="749" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A749" t="s">
         <v>41</v>
       </c>
@@ -23604,7 +23628,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="750" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="750" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A750" t="s">
         <v>41</v>
       </c>
@@ -23635,7 +23659,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="751" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="751" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A751" t="s">
         <v>41</v>
       </c>
@@ -23664,7 +23688,7 @@
       </c>
       <c r="I751" s="6"/>
     </row>
-    <row r="752" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="752" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A752" t="s">
         <v>41</v>
       </c>
@@ -23695,7 +23719,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="753" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="753" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A753" t="s">
         <v>41</v>
       </c>
@@ -23726,7 +23750,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="754" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="754" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A754" t="s">
         <v>41</v>
       </c>
@@ -23757,7 +23781,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="755" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="755" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A755" t="s">
         <v>41</v>
       </c>
@@ -23788,7 +23812,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="756" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="756" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A756" t="s">
         <v>41</v>
       </c>
@@ -23819,7 +23843,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="757" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="757" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A757" t="s">
         <v>41</v>
       </c>
@@ -23850,7 +23874,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="758" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="758" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A758" t="s">
         <v>41</v>
       </c>
@@ -23879,7 +23903,7 @@
       </c>
       <c r="I758" s="6"/>
     </row>
-    <row r="759" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="759" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A759" t="s">
         <v>41</v>
       </c>
@@ -23908,7 +23932,7 @@
       </c>
       <c r="I759" s="6"/>
     </row>
-    <row r="760" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="760" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A760" t="s">
         <v>41</v>
       </c>
@@ -23939,7 +23963,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="761" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="761" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A761" t="s">
         <v>41</v>
       </c>
@@ -23970,7 +23994,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="762" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="762" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A762" t="s">
         <v>41</v>
       </c>
@@ -24001,7 +24025,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="763" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="763" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A763" t="s">
         <v>41</v>
       </c>
@@ -24032,7 +24056,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="764" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="764" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A764" t="s">
         <v>41</v>
       </c>
@@ -24063,7 +24087,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="765" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="765" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A765" t="s">
         <v>41</v>
       </c>
@@ -24094,7 +24118,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="766" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="766" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A766" t="s">
         <v>41</v>
       </c>
@@ -24123,7 +24147,7 @@
       </c>
       <c r="I766" s="6"/>
     </row>
-    <row r="767" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="767" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A767" t="s">
         <v>41</v>
       </c>
@@ -24154,7 +24178,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="768" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="768" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A768" t="s">
         <v>41</v>
       </c>
@@ -24185,7 +24209,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="769" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="769" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A769" t="s">
         <v>41</v>
       </c>
@@ -24216,7 +24240,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="770" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="770" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A770" t="s">
         <v>41</v>
       </c>
@@ -24247,7 +24271,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="771" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="771" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A771" t="s">
         <v>41</v>
       </c>
@@ -24278,7 +24302,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="772" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="772" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A772" t="s">
         <v>41</v>
       </c>
@@ -24309,7 +24333,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="773" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="773" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A773" t="s">
         <v>41</v>
       </c>
@@ -24340,7 +24364,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="774" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="774" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A774" t="s">
         <v>41</v>
       </c>
@@ -24371,7 +24395,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="775" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="775" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A775" t="s">
         <v>41</v>
       </c>
@@ -24402,7 +24426,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="776" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="776" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A776" t="s">
         <v>41</v>
       </c>
@@ -24433,7 +24457,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="777" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="777" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A777" t="s">
         <v>41</v>
       </c>
@@ -24464,7 +24488,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="778" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="778" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A778" t="s">
         <v>41</v>
       </c>
@@ -24493,7 +24517,7 @@
       </c>
       <c r="I778" s="6"/>
     </row>
-    <row r="779" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="779" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A779" t="s">
         <v>41</v>
       </c>
@@ -24524,7 +24548,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="780" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="780" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A780" t="s">
         <v>41</v>
       </c>
@@ -24555,7 +24579,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="781" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="781" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A781" t="s">
         <v>41</v>
       </c>
@@ -24584,7 +24608,7 @@
       </c>
       <c r="I781" s="6"/>
     </row>
-    <row r="782" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="782" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A782" t="s">
         <v>41</v>
       </c>
@@ -24613,7 +24637,7 @@
       </c>
       <c r="I782" s="6"/>
     </row>
-    <row r="783" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="783" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A783" t="s">
         <v>41</v>
       </c>
@@ -24642,7 +24666,7 @@
       </c>
       <c r="I783" s="6"/>
     </row>
-    <row r="784" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="784" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A784" t="s">
         <v>41</v>
       </c>
@@ -24671,7 +24695,7 @@
       </c>
       <c r="I784" s="6"/>
     </row>
-    <row r="785" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="785" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A785" t="s">
         <v>41</v>
       </c>
@@ -24702,7 +24726,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="786" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="786" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A786" t="s">
         <v>41</v>
       </c>
@@ -24731,7 +24755,7 @@
       </c>
       <c r="I786" s="6"/>
     </row>
-    <row r="787" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="787" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A787" t="s">
         <v>41</v>
       </c>
@@ -24762,7 +24786,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="788" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="788" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A788" t="s">
         <v>41</v>
       </c>
@@ -24791,7 +24815,7 @@
       </c>
       <c r="I788" s="6"/>
     </row>
-    <row r="789" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="789" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A789" t="s">
         <v>41</v>
       </c>
@@ -24820,7 +24844,7 @@
       </c>
       <c r="I789" s="6"/>
     </row>
-    <row r="790" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="790" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A790" t="s">
         <v>41</v>
       </c>
@@ -24849,7 +24873,7 @@
       </c>
       <c r="I790" s="6"/>
     </row>
-    <row r="791" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="791" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A791" t="s">
         <v>41</v>
       </c>
@@ -24880,7 +24904,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="792" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="792" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A792" t="s">
         <v>41</v>
       </c>
@@ -24909,7 +24933,7 @@
       </c>
       <c r="I792" s="6"/>
     </row>
-    <row r="793" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="793" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A793" t="s">
         <v>41</v>
       </c>
@@ -24938,7 +24962,7 @@
       </c>
       <c r="I793" s="6"/>
     </row>
-    <row r="794" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="794" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A794" t="s">
         <v>41</v>
       </c>
@@ -24969,7 +24993,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="795" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="795" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A795" t="s">
         <v>41</v>
       </c>
@@ -25000,7 +25024,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="796" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="796" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A796" t="s">
         <v>41</v>
       </c>
@@ -25029,7 +25053,7 @@
       </c>
       <c r="I796" s="6"/>
     </row>
-    <row r="797" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="797" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A797" t="s">
         <v>41</v>
       </c>
@@ -25058,7 +25082,7 @@
       </c>
       <c r="I797" s="6"/>
     </row>
-    <row r="798" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="798" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A798" t="s">
         <v>41</v>
       </c>
@@ -25087,7 +25111,7 @@
       </c>
       <c r="I798" s="6"/>
     </row>
-    <row r="799" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="799" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A799" t="s">
         <v>41</v>
       </c>
@@ -25116,7 +25140,7 @@
       </c>
       <c r="I799" s="6"/>
     </row>
-    <row r="800" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="800" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A800" t="s">
         <v>41</v>
       </c>
@@ -25145,7 +25169,7 @@
       </c>
       <c r="I800" s="6"/>
     </row>
-    <row r="801" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="801" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A801" t="s">
         <v>41</v>
       </c>
@@ -25174,7 +25198,7 @@
       </c>
       <c r="I801" s="6"/>
     </row>
-    <row r="802" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="802" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A802" t="s">
         <v>41</v>
       </c>
@@ -25205,7 +25229,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="803" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="803" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A803" t="s">
         <v>41</v>
       </c>
@@ -25234,7 +25258,7 @@
       </c>
       <c r="I803" s="6"/>
     </row>
-    <row r="804" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="804" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A804" t="s">
         <v>41</v>
       </c>
@@ -25263,7 +25287,7 @@
       </c>
       <c r="I804" s="6"/>
     </row>
-    <row r="805" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="805" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A805" t="s">
         <v>41</v>
       </c>
@@ -25294,7 +25318,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="806" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="806" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A806" t="s">
         <v>41</v>
       </c>
@@ -25325,7 +25349,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="807" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="807" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A807" t="s">
         <v>41</v>
       </c>
@@ -25354,7 +25378,7 @@
       </c>
       <c r="I807" s="6"/>
     </row>
-    <row r="808" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="808" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A808" t="s">
         <v>41</v>
       </c>
@@ -25385,7 +25409,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="809" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="809" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A809" t="s">
         <v>41</v>
       </c>
@@ -25416,7 +25440,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="810" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="810" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A810" t="s">
         <v>41</v>
       </c>
@@ -25447,7 +25471,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="811" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="811" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A811" t="s">
         <v>41</v>
       </c>
@@ -25476,7 +25500,7 @@
       </c>
       <c r="I811" s="6"/>
     </row>
-    <row r="812" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="812" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A812" t="s">
         <v>41</v>
       </c>
@@ -25507,7 +25531,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="813" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="813" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A813" t="s">
         <v>41</v>
       </c>
@@ -25536,7 +25560,7 @@
       </c>
       <c r="I813" s="6"/>
     </row>
-    <row r="814" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="814" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A814" t="s">
         <v>41</v>
       </c>
@@ -25567,7 +25591,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="815" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="815" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A815" t="s">
         <v>41</v>
       </c>
@@ -25598,7 +25622,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="816" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="816" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A816" t="s">
         <v>41</v>
       </c>
@@ -25627,7 +25651,7 @@
       </c>
       <c r="I816" s="6"/>
     </row>
-    <row r="817" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="817" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A817" t="s">
         <v>41</v>
       </c>
@@ -25658,7 +25682,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="818" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="818" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A818" t="s">
         <v>41</v>
       </c>
@@ -25687,7 +25711,7 @@
       </c>
       <c r="I818" s="6"/>
     </row>
-    <row r="819" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="819" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A819" t="s">
         <v>41</v>
       </c>
@@ -25716,7 +25740,7 @@
       </c>
       <c r="I819" s="6"/>
     </row>
-    <row r="820" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="820" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A820" t="s">
         <v>41</v>
       </c>
@@ -25747,7 +25771,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="821" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="821" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A821" t="s">
         <v>41</v>
       </c>
@@ -25778,7 +25802,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="822" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="822" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A822" t="s">
         <v>41</v>
       </c>
@@ -25807,7 +25831,7 @@
       </c>
       <c r="I822" s="6"/>
     </row>
-    <row r="823" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="823" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A823" t="s">
         <v>41</v>
       </c>
@@ -25838,7 +25862,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="824" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="824" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A824" t="s">
         <v>41</v>
       </c>
@@ -25869,7 +25893,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="825" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="825" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A825" t="s">
         <v>41</v>
       </c>
@@ -25900,7 +25924,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="826" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="826" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A826" t="s">
         <v>41</v>
       </c>
@@ -25929,7 +25953,7 @@
       </c>
       <c r="I826" s="6"/>
     </row>
-    <row r="827" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="827" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A827" t="s">
         <v>41</v>
       </c>
@@ -25960,7 +25984,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="828" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="828" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A828" t="s">
         <v>40</v>
       </c>
@@ -25988,7 +26012,7 @@
       </c>
       <c r="I828" s="1"/>
     </row>
-    <row r="829" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="829" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A829" t="s">
         <v>40</v>
       </c>
@@ -26016,7 +26040,7 @@
       </c>
       <c r="I829" s="1"/>
     </row>
-    <row r="830" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="830" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A830" t="s">
         <v>40</v>
       </c>
@@ -26044,7 +26068,7 @@
       </c>
       <c r="I830" s="1"/>
     </row>
-    <row r="831" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="831" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A831" t="s">
         <v>40</v>
       </c>
@@ -26072,7 +26096,7 @@
       </c>
       <c r="I831" s="1"/>
     </row>
-    <row r="832" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="832" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A832" t="s">
         <v>40</v>
       </c>
@@ -26102,7 +26126,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="833" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="833" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A833" t="s">
         <v>40</v>
       </c>
@@ -26130,7 +26154,7 @@
       </c>
       <c r="I833" s="1"/>
     </row>
-    <row r="834" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="834" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A834" t="s">
         <v>40</v>
       </c>
@@ -26160,7 +26184,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="835" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="835" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A835" t="s">
         <v>40</v>
       </c>
@@ -26190,7 +26214,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="836" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="836" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A836" t="s">
         <v>40</v>
       </c>
@@ -26220,7 +26244,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="837" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="837" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A837" t="s">
         <v>40</v>
       </c>
@@ -26248,7 +26272,7 @@
       </c>
       <c r="I837" s="1"/>
     </row>
-    <row r="838" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="838" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A838" t="s">
         <v>40</v>
       </c>
@@ -26278,7 +26302,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="839" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="839" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A839" t="s">
         <v>40</v>
       </c>
@@ -26308,7 +26332,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="840" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="840" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A840" t="s">
         <v>40</v>
       </c>
@@ -26338,7 +26362,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="841" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="841" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A841" t="s">
         <v>40</v>
       </c>
@@ -26366,7 +26390,7 @@
       </c>
       <c r="I841" s="1"/>
     </row>
-    <row r="842" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="842" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A842" t="s">
         <v>40</v>
       </c>
@@ -26396,7 +26420,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="843" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="843" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A843" t="s">
         <v>40</v>
       </c>
@@ -26423,7 +26447,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="844" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="844" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A844" t="s">
         <v>40</v>
       </c>
@@ -26450,7 +26474,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="845" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="845" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A845" t="s">
         <v>40</v>
       </c>
@@ -26477,7 +26501,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="846" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="846" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A846" t="s">
         <v>40</v>
       </c>
@@ -26504,7 +26528,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="847" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="847" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A847" t="s">
         <v>40</v>
       </c>
@@ -26531,7 +26555,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="848" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="848" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A848" t="s">
         <v>40</v>
       </c>
@@ -26561,7 +26585,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="849" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="849" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A849" t="s">
         <v>40</v>
       </c>
@@ -26588,7 +26612,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="850" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="850" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A850" t="s">
         <v>40</v>
       </c>
@@ -26615,7 +26639,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="851" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="851" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A851" t="s">
         <v>40</v>
       </c>
@@ -26642,7 +26666,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="852" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="852" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A852" t="s">
         <v>40</v>
       </c>
@@ -26669,7 +26693,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="853" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="853" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A853" t="s">
         <v>40</v>
       </c>
@@ -26696,7 +26720,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="854" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="854" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A854" t="s">
         <v>40</v>
       </c>
@@ -26723,7 +26747,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="855" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="855" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A855" t="s">
         <v>40</v>
       </c>
@@ -26750,7 +26774,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="856" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="856" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A856" t="s">
         <v>40</v>
       </c>
@@ -26777,7 +26801,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="857" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="857" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A857" t="s">
         <v>40</v>
       </c>
@@ -26804,7 +26828,278 @@
         <v>50</v>
       </c>
     </row>
+    <row r="858" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A858" t="s">
+        <v>41</v>
+      </c>
+      <c r="B858">
+        <v>8</v>
+      </c>
+      <c r="C858">
+        <v>10</v>
+      </c>
+      <c r="D858" t="s">
+        <v>37</v>
+      </c>
+      <c r="E858" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="F858">
+        <v>1276</v>
+      </c>
+      <c r="G858" s="15" t="s">
+        <v>145</v>
+      </c>
+      <c r="H858">
+        <f>VLOOKUP(G858,Sayfa2!M:N,2,0)</f>
+        <v>46</v>
+      </c>
+      <c r="I858" s="16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="859" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A859" t="s">
+        <v>41</v>
+      </c>
+      <c r="B859">
+        <v>8</v>
+      </c>
+      <c r="C859">
+        <v>10</v>
+      </c>
+      <c r="D859" t="s">
+        <v>37</v>
+      </c>
+      <c r="E859" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="F859">
+        <v>1276</v>
+      </c>
+      <c r="G859" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="H859">
+        <f>VLOOKUP(G859,Sayfa2!M:N,2,0)</f>
+        <v>19</v>
+      </c>
+      <c r="I859" s="16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="860" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A860" t="s">
+        <v>41</v>
+      </c>
+      <c r="B860">
+        <v>8</v>
+      </c>
+      <c r="C860">
+        <v>10</v>
+      </c>
+      <c r="D860" t="s">
+        <v>37</v>
+      </c>
+      <c r="E860" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="F860">
+        <v>1276</v>
+      </c>
+      <c r="G860" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="H860">
+        <f>VLOOKUP(G860,Sayfa2!M:N,2,0)</f>
+        <v>17</v>
+      </c>
+      <c r="I860" s="16">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="861" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A861" t="s">
+        <v>41</v>
+      </c>
+      <c r="B861">
+        <v>8</v>
+      </c>
+      <c r="C861">
+        <v>10</v>
+      </c>
+      <c r="D861" t="s">
+        <v>37</v>
+      </c>
+      <c r="E861" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="F861">
+        <v>1276</v>
+      </c>
+      <c r="G861" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="H861">
+        <f>VLOOKUP(G861,Sayfa2!M:N,2,0)</f>
+        <v>14</v>
+      </c>
+      <c r="I861" s="16">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="862" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A862" t="s">
+        <v>41</v>
+      </c>
+      <c r="B862">
+        <v>8</v>
+      </c>
+      <c r="C862">
+        <v>10</v>
+      </c>
+      <c r="D862" t="s">
+        <v>37</v>
+      </c>
+      <c r="E862" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="F862">
+        <v>1276</v>
+      </c>
+      <c r="G862" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H862">
+        <f>VLOOKUP(G862,Sayfa2!M:N,2,0)</f>
+        <v>27</v>
+      </c>
+      <c r="I862" s="16">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="863" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A863" t="s">
+        <v>41</v>
+      </c>
+      <c r="B863">
+        <v>8</v>
+      </c>
+      <c r="C863">
+        <v>10</v>
+      </c>
+      <c r="D863" t="s">
+        <v>37</v>
+      </c>
+      <c r="E863" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="F863">
+        <v>1276</v>
+      </c>
+      <c r="G863" s="15" t="s">
+        <v>170</v>
+      </c>
+      <c r="H863">
+        <f>VLOOKUP(G863,Sayfa2!M:N,2,0)</f>
+        <v>45</v>
+      </c>
+      <c r="I863" s="16">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="864" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A864" t="s">
+        <v>41</v>
+      </c>
+      <c r="B864">
+        <v>8</v>
+      </c>
+      <c r="C864">
+        <v>10</v>
+      </c>
+      <c r="D864" t="s">
+        <v>37</v>
+      </c>
+      <c r="E864" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="F864">
+        <v>1276</v>
+      </c>
+      <c r="G864" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="H864">
+        <f>VLOOKUP(G864,Sayfa2!M:N,2,0)</f>
+        <v>22</v>
+      </c>
+      <c r="I864" s="16">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="865" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A865" t="s">
+        <v>41</v>
+      </c>
+      <c r="B865">
+        <v>8</v>
+      </c>
+      <c r="C865">
+        <v>10</v>
+      </c>
+      <c r="D865" t="s">
+        <v>37</v>
+      </c>
+      <c r="E865" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="F865">
+        <v>1276</v>
+      </c>
+      <c r="G865" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="H865">
+        <f>VLOOKUP(G865,Sayfa2!M:N,2,0)</f>
+        <v>25</v>
+      </c>
+      <c r="I865" s="16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="866" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A866" t="s">
+        <v>41</v>
+      </c>
+      <c r="B866">
+        <v>8</v>
+      </c>
+      <c r="C866">
+        <v>10</v>
+      </c>
+      <c r="D866" t="s">
+        <v>37</v>
+      </c>
+      <c r="E866" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="F866">
+        <v>1276</v>
+      </c>
+      <c r="G866" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="H866">
+        <f>VLOOKUP(G866,Sayfa2!M:N,2,0)</f>
+        <v>50</v>
+      </c>
+      <c r="I866" s="16">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
+  <autoFilter ref="A1:I866" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -26813,12 +27108,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B9A5482-841C-4FB2-932F-F0C84C0CE835}">
   <dimension ref="A1:O57"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="22.875" customWidth="1"/>
+    <col min="1" max="1" width="22.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -26832,7 +27127,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -26849,7 +27144,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>19</v>
       </c>
@@ -26866,7 +27161,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>20</v>
       </c>
@@ -26883,7 +27178,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>21</v>
       </c>
@@ -26900,7 +27195,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>22</v>
       </c>
@@ -26917,7 +27212,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>23</v>
       </c>
@@ -26934,7 +27229,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>24</v>
       </c>
@@ -26951,7 +27246,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>25</v>
       </c>
@@ -26968,7 +27263,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>26</v>
       </c>
@@ -26985,7 +27280,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>27</v>
       </c>
@@ -27002,7 +27297,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>28</v>
       </c>
@@ -27019,7 +27314,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>29</v>
       </c>
@@ -27036,7 +27331,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>30</v>
       </c>
@@ -27053,7 +27348,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>31</v>
       </c>
@@ -27070,7 +27365,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>32</v>
       </c>
@@ -27087,7 +27382,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>33</v>
       </c>
@@ -27104,7 +27399,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>34</v>
       </c>
@@ -27121,7 +27416,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
         <v>42</v>
       </c>
@@ -27138,7 +27433,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A20" s="3" t="s">
         <v>43</v>
       </c>
@@ -27155,7 +27450,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
         <v>44</v>
       </c>
@@ -27172,7 +27467,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
         <v>45</v>
       </c>
@@ -27189,7 +27484,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
         <v>46</v>
       </c>
@@ -27206,7 +27501,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
         <v>47</v>
       </c>
@@ -27223,7 +27518,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
         <v>48</v>
       </c>
@@ -27240,7 +27535,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A26" s="3" t="s">
         <v>49</v>
       </c>
@@ -27257,7 +27552,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A27" s="3" t="s">
         <v>50</v>
       </c>
@@ -27274,7 +27569,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
         <v>51</v>
       </c>
@@ -27291,7 +27586,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A29" s="3" t="s">
         <v>52</v>
       </c>
@@ -27308,7 +27603,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A30" s="3" t="s">
         <v>53</v>
       </c>
@@ -27325,7 +27620,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A31" s="3" t="s">
         <v>54</v>
       </c>
@@ -27342,7 +27637,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A32" s="4" t="s">
         <v>55</v>
       </c>
@@ -27368,7 +27663,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A33" s="4" t="s">
         <v>57</v>
       </c>
@@ -27394,7 +27689,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A34" s="4" t="s">
         <v>58</v>
       </c>
@@ -27420,7 +27715,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A35" s="4" t="s">
         <v>59</v>
       </c>
@@ -27446,7 +27741,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A36" s="4" t="s">
         <v>60</v>
       </c>
@@ -27472,7 +27767,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A37" s="7" t="s">
         <v>61</v>
       </c>
@@ -27498,7 +27793,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A38" s="4" t="s">
         <v>62</v>
       </c>
@@ -27524,7 +27819,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A39" s="8" t="s">
         <v>63</v>
       </c>
@@ -27550,7 +27845,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A40" s="8" t="s">
         <v>64</v>
       </c>
@@ -27576,7 +27871,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A41" s="8" t="s">
         <v>65</v>
       </c>
@@ -27602,7 +27897,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A42" s="8" t="s">
         <v>66</v>
       </c>
@@ -27628,7 +27923,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A43" s="8" t="s">
         <v>67</v>
       </c>
@@ -27654,7 +27949,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A44" s="8" t="s">
         <v>68</v>
       </c>
@@ -27680,7 +27975,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A45" s="8" t="s">
         <v>69</v>
       </c>
@@ -27706,7 +28001,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A46" s="9" t="s">
         <v>71</v>
       </c>
@@ -27732,7 +28027,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A47" s="9" t="s">
         <v>72</v>
       </c>
@@ -27758,7 +28053,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A48" s="9" t="s">
         <v>73</v>
       </c>
@@ -27784,7 +28079,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A49" s="9" t="s">
         <v>74</v>
       </c>
@@ -27810,7 +28105,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A50" s="9" t="s">
         <v>75</v>
       </c>
@@ -27836,7 +28131,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A51" s="9" t="s">
         <v>76</v>
       </c>
@@ -27862,7 +28157,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A52" s="9" t="s">
         <v>77</v>
       </c>
@@ -27888,7 +28183,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="53" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A53" s="9" t="s">
         <v>78</v>
       </c>
@@ -27905,7 +28200,7 @@
         <v>1090</v>
       </c>
     </row>
-    <row r="54" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A54" s="9" t="s">
         <v>79</v>
       </c>
@@ -27922,7 +28217,7 @@
         <v>1094</v>
       </c>
     </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A55" s="8" t="s">
         <v>80</v>
       </c>
@@ -27939,7 +28234,7 @@
         <v>1096</v>
       </c>
     </row>
-    <row r="56" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A56" s="8" t="s">
         <v>81</v>
       </c>
@@ -27956,7 +28251,7 @@
         <v>1103</v>
       </c>
     </row>
-    <row r="57" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A57" s="8" t="s">
         <v>82</v>
       </c>

--- a/RangeSayacv3_yeni_taslak.xlsx
+++ b/RangeSayacv3_yeni_taslak.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kaankaraca/Desktop/RangeSayac/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AB8A78E-1588-DD43-81F3-3355821ECCA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEE3DCCB-26EB-2D45-8B01-F4385F05B020}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="34200" windowHeight="20860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1108,6 +1108,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:I866"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
@@ -1147,7 +1148,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>40</v>
       </c>
@@ -1178,7 +1179,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>40</v>
       </c>
@@ -1209,7 +1210,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>40</v>
       </c>
@@ -1240,7 +1241,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>40</v>
       </c>
@@ -1271,7 +1272,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>40</v>
       </c>
@@ -1302,7 +1303,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>40</v>
       </c>
@@ -1330,7 +1331,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>40</v>
       </c>
@@ -1361,7 +1362,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>40</v>
       </c>
@@ -1389,7 +1390,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>40</v>
       </c>
@@ -1420,7 +1421,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>40</v>
       </c>
@@ -1448,7 +1449,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>40</v>
       </c>
@@ -1476,7 +1477,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>40</v>
       </c>
@@ -1507,7 +1508,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>40</v>
       </c>
@@ -1538,7 +1539,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>40</v>
       </c>
@@ -1566,7 +1567,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>40</v>
       </c>
@@ -1594,7 +1595,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>40</v>
       </c>
@@ -1623,7 +1624,7 @@
       </c>
       <c r="I17" s="1"/>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>40</v>
       </c>
@@ -1652,7 +1653,7 @@
       </c>
       <c r="I18" s="1"/>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>40</v>
       </c>
@@ -1681,7 +1682,7 @@
       </c>
       <c r="I19" s="1"/>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>40</v>
       </c>
@@ -1710,7 +1711,7 @@
       </c>
       <c r="I20" s="1"/>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>40</v>
       </c>
@@ -1741,7 +1742,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>40</v>
       </c>
@@ -1770,7 +1771,7 @@
       </c>
       <c r="I22" s="1"/>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>40</v>
       </c>
@@ -1801,7 +1802,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>40</v>
       </c>
@@ -1832,7 +1833,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>40</v>
       </c>
@@ -1863,7 +1864,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>40</v>
       </c>
@@ -1892,7 +1893,7 @@
       </c>
       <c r="I26" s="1"/>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>40</v>
       </c>
@@ -1923,7 +1924,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>40</v>
       </c>
@@ -1954,7 +1955,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>40</v>
       </c>
@@ -1985,7 +1986,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>40</v>
       </c>
@@ -2014,7 +2015,7 @@
       </c>
       <c r="I30" s="1"/>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>40</v>
       </c>
@@ -2045,7 +2046,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>40</v>
       </c>
@@ -2076,7 +2077,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>40</v>
       </c>
@@ -2107,7 +2108,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>40</v>
       </c>
@@ -2138,7 +2139,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>40</v>
       </c>
@@ -2169,7 +2170,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>40</v>
       </c>
@@ -2200,7 +2201,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>40</v>
       </c>
@@ -2228,7 +2229,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>40</v>
       </c>
@@ -2256,7 +2257,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>40</v>
       </c>
@@ -2284,7 +2285,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>40</v>
       </c>
@@ -2315,7 +2316,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>40</v>
       </c>
@@ -2346,7 +2347,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>40</v>
       </c>
@@ -2374,7 +2375,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>40</v>
       </c>
@@ -2405,7 +2406,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>40</v>
       </c>
@@ -2436,7 +2437,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>40</v>
       </c>
@@ -2464,7 +2465,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>40</v>
       </c>
@@ -2492,7 +2493,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>40</v>
       </c>
@@ -2521,7 +2522,7 @@
       </c>
       <c r="I47" s="1"/>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>40</v>
       </c>
@@ -2550,7 +2551,7 @@
       </c>
       <c r="I48" s="1"/>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>40</v>
       </c>
@@ -2579,7 +2580,7 @@
       </c>
       <c r="I49" s="1"/>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>40</v>
       </c>
@@ -2608,7 +2609,7 @@
       </c>
       <c r="I50" s="1"/>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>40</v>
       </c>
@@ -2639,7 +2640,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>40</v>
       </c>
@@ -2668,7 +2669,7 @@
       </c>
       <c r="I52" s="1"/>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>40</v>
       </c>
@@ -2699,7 +2700,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>40</v>
       </c>
@@ -2730,7 +2731,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>40</v>
       </c>
@@ -2761,7 +2762,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>40</v>
       </c>
@@ -2792,7 +2793,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>40</v>
       </c>
@@ -2821,7 +2822,7 @@
       </c>
       <c r="I57" s="1"/>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>40</v>
       </c>
@@ -2852,7 +2853,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>40</v>
       </c>
@@ -2883,7 +2884,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>40</v>
       </c>
@@ -2912,7 +2913,7 @@
       </c>
       <c r="I60" s="1"/>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>40</v>
       </c>
@@ -2941,7 +2942,7 @@
       </c>
       <c r="I61" s="1"/>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>40</v>
       </c>
@@ -2972,7 +2973,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>40</v>
       </c>
@@ -3003,7 +3004,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>40</v>
       </c>
@@ -3034,7 +3035,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>40</v>
       </c>
@@ -3065,7 +3066,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>40</v>
       </c>
@@ -3096,7 +3097,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>40</v>
       </c>
@@ -3124,7 +3125,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>40</v>
       </c>
@@ -3155,7 +3156,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>40</v>
       </c>
@@ -3186,7 +3187,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>40</v>
       </c>
@@ -3217,7 +3218,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>40</v>
       </c>
@@ -3248,7 +3249,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>40</v>
       </c>
@@ -3279,7 +3280,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>40</v>
       </c>
@@ -3306,11 +3307,8 @@
         <f>VLOOKUP(G73,Sayfa2!M:N,2,0)</f>
         <v>22</v>
       </c>
-      <c r="I73">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="74" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>40</v>
       </c>
@@ -3341,7 +3339,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>40</v>
       </c>
@@ -3369,7 +3367,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>40</v>
       </c>
@@ -3400,7 +3398,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>40</v>
       </c>
@@ -3429,7 +3427,7 @@
       </c>
       <c r="I77" s="1"/>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>40</v>
       </c>
@@ -3458,7 +3456,7 @@
       </c>
       <c r="I78" s="1"/>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>40</v>
       </c>
@@ -3487,7 +3485,7 @@
       </c>
       <c r="I79" s="1"/>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>40</v>
       </c>
@@ -3516,7 +3514,7 @@
       </c>
       <c r="I80" s="1"/>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>40</v>
       </c>
@@ -3547,7 +3545,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>40</v>
       </c>
@@ -3576,7 +3574,7 @@
       </c>
       <c r="I82" s="1"/>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
         <v>40</v>
       </c>
@@ -3607,7 +3605,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
         <v>40</v>
       </c>
@@ -3638,7 +3636,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
         <v>40</v>
       </c>
@@ -3669,7 +3667,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
         <v>40</v>
       </c>
@@ -3700,7 +3698,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
         <v>40</v>
       </c>
@@ -3731,7 +3729,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
         <v>40</v>
       </c>
@@ -3762,7 +3760,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
         <v>40</v>
       </c>
@@ -3793,7 +3791,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
         <v>40</v>
       </c>
@@ -3822,7 +3820,7 @@
       </c>
       <c r="I90" s="1"/>
     </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
         <v>40</v>
       </c>
@@ -3853,7 +3851,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
         <v>40</v>
       </c>
@@ -3884,7 +3882,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
         <v>40</v>
       </c>
@@ -3915,7 +3913,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
         <v>40</v>
       </c>
@@ -3946,7 +3944,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
         <v>40</v>
       </c>
@@ -3977,7 +3975,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
         <v>40</v>
       </c>
@@ -4008,7 +4006,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
         <v>40</v>
       </c>
@@ -4036,7 +4034,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
         <v>40</v>
       </c>
@@ -4067,7 +4065,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
         <v>40</v>
       </c>
@@ -4095,7 +4093,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
         <v>40</v>
       </c>
@@ -4126,7 +4124,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
         <v>40</v>
       </c>
@@ -4154,7 +4152,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
         <v>40</v>
       </c>
@@ -4182,7 +4180,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
         <v>40</v>
       </c>
@@ -4213,7 +4211,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
         <v>40</v>
       </c>
@@ -4244,7 +4242,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
         <v>40</v>
       </c>
@@ -4275,7 +4273,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
         <v>40</v>
       </c>
@@ -4303,7 +4301,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
         <v>40</v>
       </c>
@@ -4332,7 +4330,7 @@
       </c>
       <c r="I107" s="1"/>
     </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
         <v>40</v>
       </c>
@@ -4361,7 +4359,7 @@
       </c>
       <c r="I108" s="1"/>
     </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
         <v>40</v>
       </c>
@@ -4390,7 +4388,7 @@
       </c>
       <c r="I109" s="1"/>
     </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
         <v>40</v>
       </c>
@@ -4419,7 +4417,7 @@
       </c>
       <c r="I110" s="1"/>
     </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
         <v>40</v>
       </c>
@@ -4448,7 +4446,7 @@
       </c>
       <c r="I111" s="1"/>
     </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
         <v>40</v>
       </c>
@@ -4477,7 +4475,7 @@
       </c>
       <c r="I112" s="1"/>
     </row>
-    <row r="113" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
         <v>40</v>
       </c>
@@ -4508,7 +4506,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
         <v>40</v>
       </c>
@@ -4539,7 +4537,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="115" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
         <v>40</v>
       </c>
@@ -4570,7 +4568,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="116" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
         <v>40</v>
       </c>
@@ -4599,7 +4597,7 @@
       </c>
       <c r="I116" s="1"/>
     </row>
-    <row r="117" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
         <v>40</v>
       </c>
@@ -4628,7 +4626,7 @@
       </c>
       <c r="I117" s="1"/>
     </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
         <v>40</v>
       </c>
@@ -4657,7 +4655,7 @@
       </c>
       <c r="I118" s="1"/>
     </row>
-    <row r="119" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
         <v>40</v>
       </c>
@@ -4688,7 +4686,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="120" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
         <v>40</v>
       </c>
@@ -4717,7 +4715,7 @@
       </c>
       <c r="I120" s="1"/>
     </row>
-    <row r="121" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
         <v>40</v>
       </c>
@@ -4748,7 +4746,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="122" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
         <v>40</v>
       </c>
@@ -4779,7 +4777,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="123" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
         <v>40</v>
       </c>
@@ -4810,7 +4808,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="124" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
         <v>40</v>
       </c>
@@ -4841,7 +4839,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="125" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
         <v>40</v>
       </c>
@@ -4872,7 +4870,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="126" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
         <v>40</v>
       </c>
@@ -4903,7 +4901,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="127" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
         <v>40</v>
       </c>
@@ -4931,7 +4929,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="128" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
         <v>40</v>
       </c>
@@ -4962,7 +4960,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="129" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
         <v>40</v>
       </c>
@@ -4993,7 +4991,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="130" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
         <v>40</v>
       </c>
@@ -5024,7 +5022,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="131" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
         <v>40</v>
       </c>
@@ -5055,7 +5053,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="132" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
         <v>40</v>
       </c>
@@ -5086,7 +5084,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="133" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
         <v>40</v>
       </c>
@@ -5117,7 +5115,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="134" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
         <v>40</v>
       </c>
@@ -5148,7 +5146,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="135" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
         <v>40</v>
       </c>
@@ -5176,7 +5174,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="136" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
         <v>40</v>
       </c>
@@ -5207,7 +5205,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="137" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
         <v>40</v>
       </c>
@@ -5236,7 +5234,7 @@
       </c>
       <c r="I137" s="1"/>
     </row>
-    <row r="138" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
         <v>40</v>
       </c>
@@ -5265,7 +5263,7 @@
       </c>
       <c r="I138" s="1"/>
     </row>
-    <row r="139" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
         <v>40</v>
       </c>
@@ -5294,7 +5292,7 @@
       </c>
       <c r="I139" s="1"/>
     </row>
-    <row r="140" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
         <v>40</v>
       </c>
@@ -5323,7 +5321,7 @@
       </c>
       <c r="I140" s="1"/>
     </row>
-    <row r="141" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A141" t="s">
         <v>40</v>
       </c>
@@ -5352,7 +5350,7 @@
       </c>
       <c r="I141" s="1"/>
     </row>
-    <row r="142" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
         <v>40</v>
       </c>
@@ -5381,7 +5379,7 @@
       </c>
       <c r="I142" s="1"/>
     </row>
-    <row r="143" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
         <v>40</v>
       </c>
@@ -5412,7 +5410,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="144" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A144" t="s">
         <v>40</v>
       </c>
@@ -5443,7 +5441,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="145" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A145" t="s">
         <v>40</v>
       </c>
@@ -5474,7 +5472,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="146" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A146" t="s">
         <v>40</v>
       </c>
@@ -5505,7 +5503,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="147" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A147" t="s">
         <v>40</v>
       </c>
@@ -5534,7 +5532,7 @@
       </c>
       <c r="I147" s="1"/>
     </row>
-    <row r="148" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A148" t="s">
         <v>40</v>
       </c>
@@ -5563,7 +5561,7 @@
       </c>
       <c r="I148" s="1"/>
     </row>
-    <row r="149" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A149" t="s">
         <v>40</v>
       </c>
@@ -5594,7 +5592,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="150" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A150" t="s">
         <v>40</v>
       </c>
@@ -5623,7 +5621,7 @@
       </c>
       <c r="I150" s="1"/>
     </row>
-    <row r="151" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A151" t="s">
         <v>40</v>
       </c>
@@ -5652,7 +5650,7 @@
       </c>
       <c r="I151" s="1"/>
     </row>
-    <row r="152" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A152" t="s">
         <v>40</v>
       </c>
@@ -5683,7 +5681,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="153" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A153" t="s">
         <v>40</v>
       </c>
@@ -5714,7 +5712,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="154" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A154" t="s">
         <v>40</v>
       </c>
@@ -5745,7 +5743,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="155" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A155" t="s">
         <v>40</v>
       </c>
@@ -5776,7 +5774,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="156" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A156" t="s">
         <v>40</v>
       </c>
@@ -5807,7 +5805,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="157" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A157" t="s">
         <v>40</v>
       </c>
@@ -5835,7 +5833,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="158" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A158" t="s">
         <v>40</v>
       </c>
@@ -5866,7 +5864,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="159" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A159" t="s">
         <v>40</v>
       </c>
@@ -5897,7 +5895,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="160" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A160" t="s">
         <v>40</v>
       </c>
@@ -5928,7 +5926,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="161" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A161" t="s">
         <v>40</v>
       </c>
@@ -5959,7 +5957,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="162" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A162" t="s">
         <v>40</v>
       </c>
@@ -5990,7 +5988,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="163" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A163" t="s">
         <v>40</v>
       </c>
@@ -6018,7 +6016,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="164" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A164" t="s">
         <v>40</v>
       </c>
@@ -6049,7 +6047,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="165" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A165" t="s">
         <v>40</v>
       </c>
@@ -6077,7 +6075,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="166" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A166" t="s">
         <v>40</v>
       </c>
@@ -6105,7 +6103,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="167" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A167" t="s">
         <v>40</v>
       </c>
@@ -6134,7 +6132,7 @@
       </c>
       <c r="I167" s="1"/>
     </row>
-    <row r="168" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A168" t="s">
         <v>40</v>
       </c>
@@ -6163,7 +6161,7 @@
       </c>
       <c r="I168" s="1"/>
     </row>
-    <row r="169" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A169" t="s">
         <v>40</v>
       </c>
@@ -6194,7 +6192,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="170" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A170" t="s">
         <v>40</v>
       </c>
@@ -6223,7 +6221,7 @@
       </c>
       <c r="I170" s="1"/>
     </row>
-    <row r="171" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A171" t="s">
         <v>40</v>
       </c>
@@ -6254,7 +6252,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="172" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A172" t="s">
         <v>40</v>
       </c>
@@ -6283,7 +6281,7 @@
       </c>
       <c r="I172" s="1"/>
     </row>
-    <row r="173" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A173" t="s">
         <v>40</v>
       </c>
@@ -6314,7 +6312,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="174" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A174" t="s">
         <v>40</v>
       </c>
@@ -6345,7 +6343,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="175" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A175" t="s">
         <v>40</v>
       </c>
@@ -6376,7 +6374,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="176" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A176" t="s">
         <v>40</v>
       </c>
@@ -6405,7 +6403,7 @@
       </c>
       <c r="I176" s="1"/>
     </row>
-    <row r="177" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A177" t="s">
         <v>40</v>
       </c>
@@ -6436,7 +6434,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="178" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A178" t="s">
         <v>40</v>
       </c>
@@ -6465,7 +6463,7 @@
       </c>
       <c r="I178" s="1"/>
     </row>
-    <row r="179" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A179" t="s">
         <v>40</v>
       </c>
@@ -6496,7 +6494,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="180" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A180" t="s">
         <v>40</v>
       </c>
@@ -6525,7 +6523,7 @@
       </c>
       <c r="I180" s="1"/>
     </row>
-    <row r="181" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A181" t="s">
         <v>40</v>
       </c>
@@ -6556,7 +6554,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="182" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A182" t="s">
         <v>40</v>
       </c>
@@ -6587,7 +6585,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="183" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A183" t="s">
         <v>40</v>
       </c>
@@ -6618,7 +6616,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="184" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A184" t="s">
         <v>40</v>
       </c>
@@ -6649,7 +6647,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="185" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A185" t="s">
         <v>40</v>
       </c>
@@ -6680,7 +6678,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="186" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A186" t="s">
         <v>40</v>
       </c>
@@ -6711,7 +6709,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="187" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A187" t="s">
         <v>40</v>
       </c>
@@ -6739,7 +6737,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="188" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A188" t="s">
         <v>40</v>
       </c>
@@ -6770,7 +6768,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="189" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A189" t="s">
         <v>40</v>
       </c>
@@ -6801,7 +6799,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="190" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A190" t="s">
         <v>40</v>
       </c>
@@ -6832,7 +6830,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="191" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A191" t="s">
         <v>40</v>
       </c>
@@ -6860,7 +6858,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="192" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A192" t="s">
         <v>40</v>
       </c>
@@ -6891,7 +6889,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="193" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A193" t="s">
         <v>40</v>
       </c>
@@ -6919,7 +6917,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="194" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A194" t="s">
         <v>40</v>
       </c>
@@ -6950,7 +6948,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="195" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A195" t="s">
         <v>40</v>
       </c>
@@ -6978,7 +6976,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="196" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A196" t="s">
         <v>40</v>
       </c>
@@ -7009,7 +7007,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="197" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A197" t="s">
         <v>40</v>
       </c>
@@ -7038,7 +7036,7 @@
       </c>
       <c r="I197" s="1"/>
     </row>
-    <row r="198" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A198" t="s">
         <v>40</v>
       </c>
@@ -7067,7 +7065,7 @@
       </c>
       <c r="I198" s="1"/>
     </row>
-    <row r="199" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A199" t="s">
         <v>40</v>
       </c>
@@ -7096,7 +7094,7 @@
       </c>
       <c r="I199" s="1"/>
     </row>
-    <row r="200" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A200" t="s">
         <v>40</v>
       </c>
@@ -7125,7 +7123,7 @@
       </c>
       <c r="I200" s="1"/>
     </row>
-    <row r="201" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A201" t="s">
         <v>40</v>
       </c>
@@ -7156,7 +7154,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="202" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A202" t="s">
         <v>40</v>
       </c>
@@ -7185,7 +7183,7 @@
       </c>
       <c r="I202" s="1"/>
     </row>
-    <row r="203" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A203" t="s">
         <v>40</v>
       </c>
@@ -7216,7 +7214,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="204" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A204" t="s">
         <v>40</v>
       </c>
@@ -7247,7 +7245,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="205" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A205" t="s">
         <v>40</v>
       </c>
@@ -7278,7 +7276,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="206" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A206" t="s">
         <v>40</v>
       </c>
@@ -7309,7 +7307,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="207" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A207" t="s">
         <v>40</v>
       </c>
@@ -7338,7 +7336,7 @@
       </c>
       <c r="I207" s="1"/>
     </row>
-    <row r="208" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A208" t="s">
         <v>40</v>
       </c>
@@ -7367,7 +7365,7 @@
       </c>
       <c r="I208" s="1"/>
     </row>
-    <row r="209" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A209" t="s">
         <v>40</v>
       </c>
@@ -7398,7 +7396,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="210" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A210" t="s">
         <v>40</v>
       </c>
@@ -7427,7 +7425,7 @@
       </c>
       <c r="I210" s="1"/>
     </row>
-    <row r="211" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A211" t="s">
         <v>40</v>
       </c>
@@ -7820,9 +7818,6 @@
         <f>VLOOKUP(G223,Sayfa2!M:N,2,0)</f>
         <v>22</v>
       </c>
-      <c r="I223">
-        <v>1</v>
-      </c>
     </row>
     <row r="224" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A224" t="s">
@@ -7911,7 +7906,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="227" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A227" t="s">
         <v>40</v>
       </c>
@@ -7940,7 +7935,7 @@
       </c>
       <c r="I227" s="1"/>
     </row>
-    <row r="228" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A228" t="s">
         <v>40</v>
       </c>
@@ -7969,7 +7964,7 @@
       </c>
       <c r="I228" s="1"/>
     </row>
-    <row r="229" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A229" t="s">
         <v>40</v>
       </c>
@@ -7998,7 +7993,7 @@
       </c>
       <c r="I229" s="1"/>
     </row>
-    <row r="230" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A230" t="s">
         <v>40</v>
       </c>
@@ -8027,7 +8022,7 @@
       </c>
       <c r="I230" s="1"/>
     </row>
-    <row r="231" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A231" t="s">
         <v>40</v>
       </c>
@@ -8058,7 +8053,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="232" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A232" t="s">
         <v>40</v>
       </c>
@@ -8087,7 +8082,7 @@
       </c>
       <c r="I232" s="1"/>
     </row>
-    <row r="233" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A233" t="s">
         <v>40</v>
       </c>
@@ -8118,7 +8113,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="234" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A234" t="s">
         <v>40</v>
       </c>
@@ -8149,7 +8144,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="235" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A235" t="s">
         <v>40</v>
       </c>
@@ -8180,7 +8175,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="236" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A236" t="s">
         <v>40</v>
       </c>
@@ -8211,7 +8206,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="237" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A237" t="s">
         <v>40</v>
       </c>
@@ -8240,7 +8235,7 @@
       </c>
       <c r="I237" s="1"/>
     </row>
-    <row r="238" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A238" t="s">
         <v>40</v>
       </c>
@@ -8269,7 +8264,7 @@
       </c>
       <c r="I238" s="1"/>
     </row>
-    <row r="239" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A239" t="s">
         <v>40</v>
       </c>
@@ -8300,7 +8295,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="240" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A240" t="s">
         <v>40</v>
       </c>
@@ -8329,7 +8324,7 @@
       </c>
       <c r="I240" s="1"/>
     </row>
-    <row r="241" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A241" t="s">
         <v>40</v>
       </c>
@@ -8358,7 +8353,7 @@
       </c>
       <c r="I241" s="1"/>
     </row>
-    <row r="242" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A242" t="s">
         <v>40</v>
       </c>
@@ -8389,7 +8384,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="243" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A243" t="s">
         <v>40</v>
       </c>
@@ -8420,7 +8415,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="244" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A244" t="s">
         <v>40</v>
       </c>
@@ -8451,7 +8446,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="245" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A245" t="s">
         <v>40</v>
       </c>
@@ -8482,7 +8477,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="246" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A246" t="s">
         <v>40</v>
       </c>
@@ -8510,7 +8505,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="247" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A247" t="s">
         <v>40</v>
       </c>
@@ -8538,7 +8533,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="248" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A248" t="s">
         <v>40</v>
       </c>
@@ -8569,7 +8564,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="249" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A249" t="s">
         <v>40</v>
       </c>
@@ -8597,7 +8592,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="250" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A250" t="s">
         <v>40</v>
       </c>
@@ -8628,7 +8623,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="251" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A251" t="s">
         <v>40</v>
       </c>
@@ -8659,7 +8654,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="252" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A252" t="s">
         <v>40</v>
       </c>
@@ -8687,7 +8682,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="253" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A253" t="s">
         <v>40</v>
       </c>
@@ -8715,7 +8710,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="254" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A254" t="s">
         <v>40</v>
       </c>
@@ -8746,7 +8741,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="255" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A255" t="s">
         <v>40</v>
       </c>
@@ -8777,7 +8772,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="256" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A256" t="s">
         <v>40</v>
       </c>
@@ -8805,7 +8800,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="257" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A257" t="s">
         <v>41</v>
       </c>
@@ -8833,7 +8828,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="258" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A258" t="s">
         <v>41</v>
       </c>
@@ -8861,7 +8856,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="259" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A259" t="s">
         <v>41</v>
       </c>
@@ -8889,7 +8884,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="260" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A260" t="s">
         <v>41</v>
       </c>
@@ -8917,7 +8912,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="261" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A261" t="s">
         <v>41</v>
       </c>
@@ -8945,7 +8940,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="262" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A262" t="s">
         <v>41</v>
       </c>
@@ -8976,7 +8971,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="263" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A263" t="s">
         <v>41</v>
       </c>
@@ -9004,7 +8999,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="264" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A264" t="s">
         <v>41</v>
       </c>
@@ -9032,7 +9027,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="265" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="265" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A265" t="s">
         <v>41</v>
       </c>
@@ -9060,7 +9055,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="266" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="266" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A266" t="s">
         <v>41</v>
       </c>
@@ -9088,7 +9083,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="267" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="267" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A267" t="s">
         <v>41</v>
       </c>
@@ -9116,7 +9111,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="268" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="268" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A268" t="s">
         <v>41</v>
       </c>
@@ -9144,7 +9139,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="269" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="269" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A269" t="s">
         <v>41</v>
       </c>
@@ -9172,7 +9167,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="270" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="270" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A270" t="s">
         <v>41</v>
       </c>
@@ -9200,7 +9195,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="271" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="271" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A271" t="s">
         <v>41</v>
       </c>
@@ -9228,7 +9223,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="272" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="272" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A272" t="s">
         <v>41</v>
       </c>
@@ -9259,7 +9254,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="273" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A273" t="s">
         <v>41</v>
       </c>
@@ -9290,7 +9285,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="274" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="274" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A274" t="s">
         <v>41</v>
       </c>
@@ -9321,7 +9316,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="275" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A275" t="s">
         <v>41</v>
       </c>
@@ -9352,7 +9347,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="276" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="276" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A276" t="s">
         <v>41</v>
       </c>
@@ -9383,7 +9378,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="277" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A277" t="s">
         <v>41</v>
       </c>
@@ -9411,7 +9406,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="278" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A278" t="s">
         <v>41</v>
       </c>
@@ -9442,7 +9437,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="279" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="279" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A279" t="s">
         <v>41</v>
       </c>
@@ -9473,7 +9468,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="280" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A280" t="s">
         <v>41</v>
       </c>
@@ -9504,7 +9499,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="281" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="281" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A281" t="s">
         <v>41</v>
       </c>
@@ -9532,7 +9527,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="282" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="282" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A282" t="s">
         <v>41</v>
       </c>
@@ -9560,7 +9555,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="283" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="283" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A283" t="s">
         <v>41</v>
       </c>
@@ -9588,7 +9583,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="284" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="284" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A284" t="s">
         <v>41</v>
       </c>
@@ -9619,7 +9614,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="285" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="285" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A285" t="s">
         <v>41</v>
       </c>
@@ -9650,7 +9645,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="286" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="286" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A286" t="s">
         <v>41</v>
       </c>
@@ -9681,7 +9676,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="287" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="287" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A287" t="s">
         <v>41</v>
       </c>
@@ -9709,7 +9704,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="288" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="288" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A288" t="s">
         <v>41</v>
       </c>
@@ -9737,7 +9732,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="289" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="289" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A289" t="s">
         <v>41</v>
       </c>
@@ -9765,7 +9760,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="290" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="290" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A290" t="s">
         <v>41</v>
       </c>
@@ -9793,7 +9788,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="291" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="291" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A291" t="s">
         <v>41</v>
       </c>
@@ -9824,7 +9819,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="292" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="292" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A292" t="s">
         <v>41</v>
       </c>
@@ -9852,7 +9847,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="293" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="293" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A293" t="s">
         <v>41</v>
       </c>
@@ -9883,7 +9878,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="294" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="294" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A294" t="s">
         <v>41</v>
       </c>
@@ -9914,7 +9909,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="295" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="295" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A295" t="s">
         <v>41</v>
       </c>
@@ -9945,7 +9940,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="296" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="296" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A296" t="s">
         <v>41</v>
       </c>
@@ -9973,7 +9968,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="297" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="297" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A297" t="s">
         <v>41</v>
       </c>
@@ -10001,7 +9996,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="298" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="298" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A298" t="s">
         <v>41</v>
       </c>
@@ -10032,7 +10027,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="299" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="299" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A299" t="s">
         <v>41</v>
       </c>
@@ -10063,7 +10058,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="300" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="300" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A300" t="s">
         <v>41</v>
       </c>
@@ -10094,7 +10089,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="301" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="301" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A301" t="s">
         <v>41</v>
       </c>
@@ -10125,7 +10120,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="302" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="302" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A302" t="s">
         <v>41</v>
       </c>
@@ -10153,7 +10148,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="303" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="303" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A303" t="s">
         <v>41</v>
       </c>
@@ -10184,7 +10179,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="304" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="304" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A304" t="s">
         <v>41</v>
       </c>
@@ -10215,7 +10210,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="305" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="305" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A305" t="s">
         <v>41</v>
       </c>
@@ -10246,7 +10241,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="306" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="306" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A306" t="s">
         <v>41</v>
       </c>
@@ -10277,7 +10272,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="307" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="307" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A307" t="s">
         <v>41</v>
       </c>
@@ -10305,7 +10300,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="308" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="308" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A308" t="s">
         <v>41</v>
       </c>
@@ -10333,7 +10328,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="309" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="309" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A309" t="s">
         <v>41</v>
       </c>
@@ -10364,7 +10359,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="310" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="310" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A310" t="s">
         <v>41</v>
       </c>
@@ -10395,7 +10390,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="311" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="311" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A311" t="s">
         <v>41</v>
       </c>
@@ -10423,7 +10418,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="312" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="312" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A312" t="s">
         <v>41</v>
       </c>
@@ -10451,7 +10446,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="313" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="313" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A313" t="s">
         <v>41</v>
       </c>
@@ -10479,7 +10474,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="314" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="314" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A314" t="s">
         <v>41</v>
       </c>
@@ -10510,7 +10505,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="315" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="315" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A315" t="s">
         <v>41</v>
       </c>
@@ -10541,7 +10536,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="316" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="316" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A316" t="s">
         <v>41</v>
       </c>
@@ -10569,7 +10564,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="317" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="317" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A317" t="s">
         <v>41</v>
       </c>
@@ -10600,7 +10595,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="318" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="318" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A318" t="s">
         <v>41</v>
       </c>
@@ -10631,7 +10626,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="319" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="319" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A319" t="s">
         <v>41</v>
       </c>
@@ -10662,7 +10657,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="320" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="320" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A320" t="s">
         <v>41</v>
       </c>
@@ -10693,7 +10688,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="321" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="321" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A321" t="s">
         <v>41</v>
       </c>
@@ -10724,7 +10719,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="322" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="322" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A322" t="s">
         <v>41</v>
       </c>
@@ -10752,7 +10747,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="323" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="323" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A323" t="s">
         <v>41</v>
       </c>
@@ -10780,7 +10775,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="324" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="324" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A324" t="s">
         <v>41</v>
       </c>
@@ -10811,7 +10806,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="325" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="325" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A325" t="s">
         <v>41</v>
       </c>
@@ -10842,7 +10837,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="326" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="326" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A326" t="s">
         <v>41</v>
       </c>
@@ -10870,7 +10865,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="327" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="327" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A327" t="s">
         <v>41</v>
       </c>
@@ -10898,7 +10893,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="328" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="328" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A328" t="s">
         <v>41</v>
       </c>
@@ -10929,7 +10924,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="329" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="329" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A329" t="s">
         <v>41</v>
       </c>
@@ -10960,7 +10955,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="330" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="330" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A330" t="s">
         <v>41</v>
       </c>
@@ -10991,7 +10986,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="331" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="331" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A331" t="s">
         <v>41</v>
       </c>
@@ -11022,7 +11017,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="332" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="332" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A332" t="s">
         <v>41</v>
       </c>
@@ -11050,7 +11045,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="333" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="333" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A333" t="s">
         <v>41</v>
       </c>
@@ -11081,7 +11076,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="334" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="334" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A334" t="s">
         <v>41</v>
       </c>
@@ -11109,7 +11104,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="335" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="335" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A335" t="s">
         <v>41</v>
       </c>
@@ -11137,7 +11132,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="336" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="336" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A336" t="s">
         <v>41</v>
       </c>
@@ -11168,7 +11163,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="337" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="337" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A337" t="s">
         <v>41</v>
       </c>
@@ -11196,7 +11191,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="338" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="338" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A338" t="s">
         <v>41</v>
       </c>
@@ -11227,7 +11222,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="339" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="339" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A339" t="s">
         <v>41</v>
       </c>
@@ -11258,7 +11253,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="340" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="340" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A340" t="s">
         <v>41</v>
       </c>
@@ -11289,7 +11284,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="341" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="341" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A341" t="s">
         <v>41</v>
       </c>
@@ -11317,7 +11312,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="342" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="342" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A342" t="s">
         <v>41</v>
       </c>
@@ -11345,7 +11340,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="343" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="343" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A343" t="s">
         <v>41</v>
       </c>
@@ -11376,7 +11371,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="344" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="344" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A344" t="s">
         <v>41</v>
       </c>
@@ -11407,7 +11402,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="345" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="345" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A345" t="s">
         <v>41</v>
       </c>
@@ -11438,7 +11433,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="346" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="346" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A346" t="s">
         <v>41</v>
       </c>
@@ -11466,7 +11461,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="347" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="347" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A347" t="s">
         <v>41</v>
       </c>
@@ -11497,7 +11492,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="348" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="348" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A348" t="s">
         <v>41</v>
       </c>
@@ -11528,7 +11523,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="349" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="349" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A349" t="s">
         <v>41</v>
       </c>
@@ -11559,7 +11554,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="350" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="350" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A350" t="s">
         <v>41</v>
       </c>
@@ -11590,7 +11585,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="351" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="351" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A351" t="s">
         <v>41</v>
       </c>
@@ -11621,7 +11616,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="352" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="352" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A352" t="s">
         <v>41</v>
       </c>
@@ -11652,7 +11647,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="353" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="353" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A353" t="s">
         <v>41</v>
       </c>
@@ -11683,7 +11678,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="354" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="354" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A354" t="s">
         <v>41</v>
       </c>
@@ -11714,7 +11709,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="355" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="355" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A355" t="s">
         <v>41</v>
       </c>
@@ -11745,7 +11740,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="356" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="356" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A356" t="s">
         <v>41</v>
       </c>
@@ -11773,7 +11768,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="357" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="357" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A357" t="s">
         <v>41</v>
       </c>
@@ -11804,7 +11799,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="358" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="358" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A358" t="s">
         <v>41</v>
       </c>
@@ -11835,7 +11830,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="359" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="359" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A359" t="s">
         <v>41</v>
       </c>
@@ -11866,7 +11861,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="360" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="360" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A360" t="s">
         <v>41</v>
       </c>
@@ -11897,7 +11892,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="361" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="361" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A361" t="s">
         <v>41</v>
       </c>
@@ -11925,7 +11920,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="362" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="362" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A362" t="s">
         <v>41</v>
       </c>
@@ -11953,7 +11948,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="363" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="363" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A363" t="s">
         <v>41</v>
       </c>
@@ -11984,7 +11979,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="364" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="364" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A364" t="s">
         <v>41</v>
       </c>
@@ -12015,7 +12010,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="365" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="365" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A365" t="s">
         <v>41</v>
       </c>
@@ -12046,7 +12041,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="366" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="366" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A366" t="s">
         <v>41</v>
       </c>
@@ -12077,7 +12072,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="367" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="367" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A367" t="s">
         <v>41</v>
       </c>
@@ -12105,7 +12100,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="368" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="368" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A368" t="s">
         <v>41</v>
       </c>
@@ -12136,7 +12131,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="369" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="369" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A369" t="s">
         <v>41</v>
       </c>
@@ -12167,7 +12162,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="370" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="370" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A370" t="s">
         <v>41</v>
       </c>
@@ -12198,7 +12193,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="371" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="371" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A371" t="s">
         <v>41</v>
       </c>
@@ -12229,7 +12224,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="372" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="372" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A372" t="s">
         <v>41</v>
       </c>
@@ -12260,7 +12255,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="373" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="373" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A373" t="s">
         <v>41</v>
       </c>
@@ -12291,7 +12286,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="374" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="374" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A374" t="s">
         <v>41</v>
       </c>
@@ -12322,7 +12317,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="375" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="375" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A375" t="s">
         <v>41</v>
       </c>
@@ -12353,7 +12348,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="376" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="376" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A376" t="s">
         <v>41</v>
       </c>
@@ -12381,7 +12376,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="377" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="377" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A377" t="s">
         <v>41</v>
       </c>
@@ -12412,7 +12407,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="378" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="378" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A378" t="s">
         <v>41</v>
       </c>
@@ -12443,7 +12438,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="379" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="379" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A379" t="s">
         <v>41</v>
       </c>
@@ -12474,7 +12469,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="380" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="380" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A380" t="s">
         <v>41</v>
       </c>
@@ -12505,7 +12500,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="381" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="381" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A381" t="s">
         <v>41</v>
       </c>
@@ -12536,7 +12531,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="382" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="382" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A382" t="s">
         <v>41</v>
       </c>
@@ -12564,7 +12559,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="383" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="383" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A383" t="s">
         <v>41</v>
       </c>
@@ -12595,7 +12590,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="384" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="384" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A384" t="s">
         <v>41</v>
       </c>
@@ -12626,7 +12621,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="385" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="385" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A385" t="s">
         <v>41</v>
       </c>
@@ -12657,7 +12652,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="386" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="386" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A386" t="s">
         <v>41</v>
       </c>
@@ -12685,7 +12680,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="387" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="387" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A387" t="s">
         <v>41</v>
       </c>
@@ -12716,7 +12711,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="388" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="388" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A388" t="s">
         <v>41</v>
       </c>
@@ -12747,7 +12742,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="389" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="389" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A389" t="s">
         <v>41</v>
       </c>
@@ -12778,7 +12773,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="390" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="390" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A390" t="s">
         <v>41</v>
       </c>
@@ -12809,7 +12804,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="391" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="391" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A391" t="s">
         <v>41</v>
       </c>
@@ -12840,7 +12835,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="392" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="392" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A392" t="s">
         <v>41</v>
       </c>
@@ -12868,7 +12863,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="393" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="393" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A393" t="s">
         <v>41</v>
       </c>
@@ -12896,7 +12891,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="394" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="394" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A394" t="s">
         <v>41</v>
       </c>
@@ -12924,7 +12919,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="395" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="395" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A395" t="s">
         <v>41</v>
       </c>
@@ -12952,7 +12947,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="396" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="396" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A396" t="s">
         <v>41</v>
       </c>
@@ -12983,7 +12978,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="397" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="397" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A397" t="s">
         <v>41</v>
       </c>
@@ -13011,7 +13006,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="398" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="398" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A398" t="s">
         <v>41</v>
       </c>
@@ -13042,7 +13037,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="399" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="399" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A399" t="s">
         <v>41</v>
       </c>
@@ -13073,7 +13068,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="400" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="400" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A400" t="s">
         <v>41</v>
       </c>
@@ -13104,7 +13099,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="401" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="401" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A401" t="s">
         <v>41</v>
       </c>
@@ -13132,7 +13127,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="402" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="402" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A402" t="s">
         <v>41</v>
       </c>
@@ -13160,7 +13155,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="403" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="403" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A403" t="s">
         <v>41</v>
       </c>
@@ -13188,7 +13183,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="404" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="404" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A404" t="s">
         <v>41</v>
       </c>
@@ -13219,7 +13214,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="405" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="405" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A405" t="s">
         <v>41</v>
       </c>
@@ -13250,7 +13245,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="406" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="406" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A406" t="s">
         <v>41</v>
       </c>
@@ -13278,7 +13273,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="407" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="407" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A407" t="s">
         <v>41</v>
       </c>
@@ -13306,7 +13301,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="408" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="408" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A408" t="s">
         <v>41</v>
       </c>
@@ -13337,7 +13332,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="409" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="409" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A409" t="s">
         <v>41</v>
       </c>
@@ -13368,7 +13363,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="410" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="410" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A410" t="s">
         <v>41</v>
       </c>
@@ -13399,7 +13394,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="411" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="411" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A411" t="s">
         <v>41</v>
       </c>
@@ -13430,7 +13425,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="412" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="412" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A412" t="s">
         <v>41</v>
       </c>
@@ -13458,7 +13453,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="413" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="413" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A413" t="s">
         <v>41</v>
       </c>
@@ -13486,7 +13481,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="414" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="414" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A414" t="s">
         <v>41</v>
       </c>
@@ -13517,7 +13512,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="415" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="415" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A415" t="s">
         <v>41</v>
       </c>
@@ -13548,7 +13543,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="416" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="416" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A416" t="s">
         <v>41</v>
       </c>
@@ -13579,7 +13574,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="417" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="417" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A417" t="s">
         <v>41</v>
       </c>
@@ -13610,7 +13605,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="418" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="418" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A418" t="s">
         <v>41</v>
       </c>
@@ -13638,7 +13633,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="419" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="419" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A419" t="s">
         <v>41</v>
       </c>
@@ -13669,7 +13664,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="420" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="420" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A420" t="s">
         <v>41</v>
       </c>
@@ -13700,7 +13695,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="421" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="421" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A421" t="s">
         <v>41</v>
       </c>
@@ -13731,7 +13726,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="422" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="422" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A422" t="s">
         <v>41</v>
       </c>
@@ -13759,7 +13754,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="423" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="423" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A423" t="s">
         <v>41</v>
       </c>
@@ -13790,7 +13785,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="424" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="424" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A424" t="s">
         <v>41</v>
       </c>
@@ -13821,7 +13816,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="425" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="425" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A425" t="s">
         <v>41</v>
       </c>
@@ -13852,7 +13847,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="426" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="426" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A426" t="s">
         <v>41</v>
       </c>
@@ -13883,7 +13878,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="427" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="427" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A427" t="s">
         <v>41</v>
       </c>
@@ -13911,7 +13906,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="428" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="428" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A428" t="s">
         <v>41</v>
       </c>
@@ -13939,7 +13934,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="429" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="429" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A429" t="s">
         <v>41</v>
       </c>
@@ -13970,7 +13965,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="430" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="430" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A430" t="s">
         <v>41</v>
       </c>
@@ -14001,7 +13996,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="431" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="431" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A431" t="s">
         <v>41</v>
       </c>
@@ -14029,7 +14024,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="432" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="432" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A432" t="s">
         <v>41</v>
       </c>
@@ -14060,7 +14055,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="433" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="433" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A433" t="s">
         <v>41</v>
       </c>
@@ -14088,7 +14083,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="434" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="434" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A434" t="s">
         <v>41</v>
       </c>
@@ -14119,7 +14114,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="435" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="435" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A435" t="s">
         <v>41</v>
       </c>
@@ -14150,7 +14145,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="436" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="436" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A436" t="s">
         <v>41</v>
       </c>
@@ -14178,7 +14173,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="437" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="437" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A437" t="s">
         <v>41</v>
       </c>
@@ -14209,7 +14204,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="438" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="438" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A438" t="s">
         <v>41</v>
       </c>
@@ -14237,7 +14232,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="439" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="439" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A439" t="s">
         <v>41</v>
       </c>
@@ -14268,7 +14263,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="440" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="440" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A440" t="s">
         <v>41</v>
       </c>
@@ -14299,7 +14294,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="441" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="441" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A441" t="s">
         <v>41</v>
       </c>
@@ -14327,7 +14322,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="442" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="442" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A442" t="s">
         <v>41</v>
       </c>
@@ -14355,7 +14350,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="443" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="443" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A443" t="s">
         <v>41</v>
       </c>
@@ -14383,7 +14378,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="444" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="444" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A444" t="s">
         <v>41</v>
       </c>
@@ -14414,7 +14409,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="445" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="445" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A445" t="s">
         <v>41</v>
       </c>
@@ -14445,7 +14440,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="446" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="446" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A446" t="s">
         <v>41</v>
       </c>
@@ -14473,7 +14468,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="447" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="447" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A447" t="s">
         <v>41</v>
       </c>
@@ -14504,7 +14499,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="448" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="448" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A448" t="s">
         <v>41</v>
       </c>
@@ -14532,7 +14527,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="449" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="449" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A449" t="s">
         <v>41</v>
       </c>
@@ -14560,7 +14555,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="450" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="450" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A450" t="s">
         <v>41</v>
       </c>
@@ -14591,7 +14586,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="451" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="451" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A451" t="s">
         <v>41</v>
       </c>
@@ -14619,7 +14614,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="452" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="452" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A452" t="s">
         <v>40</v>
       </c>
@@ -14650,7 +14645,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="453" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="453" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A453" t="s">
         <v>40</v>
       </c>
@@ -14679,7 +14674,7 @@
       </c>
       <c r="I453" s="6"/>
     </row>
-    <row r="454" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="454" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A454" t="s">
         <v>40</v>
       </c>
@@ -14710,7 +14705,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="455" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="455" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A455" t="s">
         <v>40</v>
       </c>
@@ -14741,7 +14736,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="456" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="456" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A456" t="s">
         <v>40</v>
       </c>
@@ -14772,7 +14767,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="457" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="457" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A457" t="s">
         <v>40</v>
       </c>
@@ -14801,7 +14796,7 @@
       </c>
       <c r="I457" s="6"/>
     </row>
-    <row r="458" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="458" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A458" t="s">
         <v>40</v>
       </c>
@@ -14830,7 +14825,7 @@
       </c>
       <c r="I458" s="6"/>
     </row>
-    <row r="459" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="459" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A459" t="s">
         <v>40</v>
       </c>
@@ -14861,7 +14856,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="460" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="460" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A460" t="s">
         <v>40</v>
       </c>
@@ -14890,7 +14885,7 @@
       </c>
       <c r="I460" s="6"/>
     </row>
-    <row r="461" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="461" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A461" t="s">
         <v>40</v>
       </c>
@@ -14919,7 +14914,7 @@
       </c>
       <c r="I461" s="6"/>
     </row>
-    <row r="462" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="462" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A462" t="s">
         <v>40</v>
       </c>
@@ -14950,7 +14945,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="463" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="463" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A463" t="s">
         <v>40</v>
       </c>
@@ -14981,7 +14976,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="464" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="464" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A464" t="s">
         <v>40</v>
       </c>
@@ -15010,7 +15005,7 @@
       </c>
       <c r="I464" s="6"/>
     </row>
-    <row r="465" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="465" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A465" t="s">
         <v>40</v>
       </c>
@@ -15039,7 +15034,7 @@
       </c>
       <c r="I465" s="6"/>
     </row>
-    <row r="466" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="466" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A466" t="s">
         <v>40</v>
       </c>
@@ -15070,7 +15065,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="467" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="467" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A467" t="s">
         <v>40</v>
       </c>
@@ -15101,7 +15096,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="468" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="468" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A468" t="s">
         <v>40</v>
       </c>
@@ -15132,7 +15127,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="469" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="469" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A469" t="s">
         <v>40</v>
       </c>
@@ -15163,7 +15158,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="470" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="470" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A470" t="s">
         <v>40</v>
       </c>
@@ -15194,7 +15189,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="471" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="471" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A471" t="s">
         <v>40</v>
       </c>
@@ -15223,7 +15218,7 @@
       </c>
       <c r="I471" s="6"/>
     </row>
-    <row r="472" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="472" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A472" t="s">
         <v>40</v>
       </c>
@@ -15252,7 +15247,7 @@
       </c>
       <c r="I472" s="6"/>
     </row>
-    <row r="473" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="473" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A473" t="s">
         <v>40</v>
       </c>
@@ -15283,7 +15278,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="474" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="474" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A474" t="s">
         <v>40</v>
       </c>
@@ -15312,7 +15307,7 @@
       </c>
       <c r="I474" s="6"/>
     </row>
-    <row r="475" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="475" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A475" t="s">
         <v>40</v>
       </c>
@@ -15341,7 +15336,7 @@
       </c>
       <c r="I475" s="6"/>
     </row>
-    <row r="476" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="476" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A476" t="s">
         <v>40</v>
       </c>
@@ -15372,7 +15367,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="477" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="477" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A477" t="s">
         <v>40</v>
       </c>
@@ -15401,7 +15396,7 @@
       </c>
       <c r="I477" s="6"/>
     </row>
-    <row r="478" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="478" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A478" t="s">
         <v>40</v>
       </c>
@@ -15432,7 +15427,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="479" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="479" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A479" t="s">
         <v>40</v>
       </c>
@@ -15461,7 +15456,7 @@
       </c>
       <c r="I479" s="6"/>
     </row>
-    <row r="480" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="480" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A480" t="s">
         <v>40</v>
       </c>
@@ -15492,7 +15487,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="481" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="481" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A481" t="s">
         <v>40</v>
       </c>
@@ -15523,7 +15518,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="482" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="482" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A482" t="s">
         <v>40</v>
       </c>
@@ -15554,7 +15549,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="483" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="483" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A483" t="s">
         <v>40</v>
       </c>
@@ -15585,7 +15580,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="484" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="484" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A484" t="s">
         <v>40</v>
       </c>
@@ -15616,7 +15611,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="485" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="485" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A485" t="s">
         <v>40</v>
       </c>
@@ -15645,7 +15640,7 @@
       </c>
       <c r="I485" s="6"/>
     </row>
-    <row r="486" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="486" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A486" t="s">
         <v>40</v>
       </c>
@@ -15676,7 +15671,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="487" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="487" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A487" t="s">
         <v>40</v>
       </c>
@@ -15707,7 +15702,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="488" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="488" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A488" t="s">
         <v>40</v>
       </c>
@@ -15736,7 +15731,7 @@
       </c>
       <c r="I488" s="6"/>
     </row>
-    <row r="489" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="489" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A489" t="s">
         <v>40</v>
       </c>
@@ -15767,7 +15762,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="490" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="490" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A490" t="s">
         <v>40</v>
       </c>
@@ -15798,7 +15793,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="491" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="491" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A491" t="s">
         <v>40</v>
       </c>
@@ -15829,7 +15824,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="492" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="492" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A492" t="s">
         <v>40</v>
       </c>
@@ -15858,7 +15853,7 @@
       </c>
       <c r="I492" s="6"/>
     </row>
-    <row r="493" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="493" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A493" t="s">
         <v>40</v>
       </c>
@@ -15887,7 +15882,7 @@
       </c>
       <c r="I493" s="6"/>
     </row>
-    <row r="494" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="494" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A494" t="s">
         <v>40</v>
       </c>
@@ -15918,7 +15913,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="495" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="495" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A495" t="s">
         <v>40</v>
       </c>
@@ -15949,7 +15944,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="496" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="496" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A496" t="s">
         <v>40</v>
       </c>
@@ -15980,7 +15975,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="497" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="497" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A497" t="s">
         <v>40</v>
       </c>
@@ -16011,7 +16006,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="498" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="498" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A498" t="s">
         <v>40</v>
       </c>
@@ -16040,7 +16035,7 @@
       </c>
       <c r="I498" s="6"/>
     </row>
-    <row r="499" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="499" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A499" t="s">
         <v>40</v>
       </c>
@@ -16069,7 +16064,7 @@
       </c>
       <c r="I499" s="6"/>
     </row>
-    <row r="500" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="500" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A500" t="s">
         <v>40</v>
       </c>
@@ -16100,7 +16095,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="501" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="501" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A501" t="s">
         <v>40</v>
       </c>
@@ -16131,7 +16126,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="502" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="502" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A502" t="s">
         <v>40</v>
       </c>
@@ -16162,7 +16157,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="503" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="503" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A503" t="s">
         <v>40</v>
       </c>
@@ -16193,7 +16188,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="504" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="504" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A504" t="s">
         <v>40</v>
       </c>
@@ -16222,7 +16217,7 @@
       </c>
       <c r="I504" s="6"/>
     </row>
-    <row r="505" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="505" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A505" t="s">
         <v>40</v>
       </c>
@@ -16253,7 +16248,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="506" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="506" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A506" t="s">
         <v>40</v>
       </c>
@@ -16284,7 +16279,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="507" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="507" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A507" t="s">
         <v>40</v>
       </c>
@@ -16313,7 +16308,7 @@
       </c>
       <c r="I507" s="6"/>
     </row>
-    <row r="508" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="508" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A508" t="s">
         <v>40</v>
       </c>
@@ -16344,7 +16339,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="509" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="509" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A509" t="s">
         <v>40</v>
       </c>
@@ -16373,7 +16368,7 @@
       </c>
       <c r="I509" s="6"/>
     </row>
-    <row r="510" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="510" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A510" t="s">
         <v>40</v>
       </c>
@@ -16404,7 +16399,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="511" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="511" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A511" t="s">
         <v>40</v>
       </c>
@@ -16435,7 +16430,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="512" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="512" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A512" t="s">
         <v>40</v>
       </c>
@@ -16466,7 +16461,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="513" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="513" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A513" t="s">
         <v>40</v>
       </c>
@@ -16495,7 +16490,7 @@
       </c>
       <c r="I513" s="6"/>
     </row>
-    <row r="514" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="514" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A514" t="s">
         <v>40</v>
       </c>
@@ -16526,7 +16521,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="515" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="515" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A515" t="s">
         <v>40</v>
       </c>
@@ -16557,7 +16552,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="516" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="516" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A516" t="s">
         <v>40</v>
       </c>
@@ -16586,7 +16581,7 @@
       </c>
       <c r="I516" s="6"/>
     </row>
-    <row r="517" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="517" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A517" t="s">
         <v>40</v>
       </c>
@@ -16617,7 +16612,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="518" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="518" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A518" t="s">
         <v>40</v>
       </c>
@@ -16648,7 +16643,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="519" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="519" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A519" t="s">
         <v>40</v>
       </c>
@@ -16679,7 +16674,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="520" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="520" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A520" t="s">
         <v>40</v>
       </c>
@@ -16710,7 +16705,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="521" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="521" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A521" t="s">
         <v>40</v>
       </c>
@@ -16741,7 +16736,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="522" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="522" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A522" t="s">
         <v>40</v>
       </c>
@@ -16772,7 +16767,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="523" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="523" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A523" t="s">
         <v>40</v>
       </c>
@@ -16803,7 +16798,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="524" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="524" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A524" t="s">
         <v>40</v>
       </c>
@@ -16834,7 +16829,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="525" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="525" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A525" t="s">
         <v>40</v>
       </c>
@@ -16865,7 +16860,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="526" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="526" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A526" t="s">
         <v>40</v>
       </c>
@@ -16896,7 +16891,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="527" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="527" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A527" t="s">
         <v>40</v>
       </c>
@@ -16925,7 +16920,7 @@
       </c>
       <c r="I527" s="6"/>
     </row>
-    <row r="528" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="528" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A528" t="s">
         <v>40</v>
       </c>
@@ -16954,7 +16949,7 @@
       </c>
       <c r="I528" s="6"/>
     </row>
-    <row r="529" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="529" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A529" t="s">
         <v>40</v>
       </c>
@@ -16985,7 +16980,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="530" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="530" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A530" t="s">
         <v>40</v>
       </c>
@@ -17016,7 +17011,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="531" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="531" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A531" t="s">
         <v>40</v>
       </c>
@@ -17045,7 +17040,7 @@
       </c>
       <c r="I531" s="6"/>
     </row>
-    <row r="532" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="532" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A532" t="s">
         <v>40</v>
       </c>
@@ -17074,7 +17069,7 @@
       </c>
       <c r="I532" s="6"/>
     </row>
-    <row r="533" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="533" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A533" t="s">
         <v>40</v>
       </c>
@@ -17105,7 +17100,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="534" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="534" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A534" t="s">
         <v>40</v>
       </c>
@@ -17134,7 +17129,7 @@
       </c>
       <c r="I534" s="6"/>
     </row>
-    <row r="535" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="535" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A535" t="s">
         <v>40</v>
       </c>
@@ -17163,7 +17158,7 @@
       </c>
       <c r="I535" s="6"/>
     </row>
-    <row r="536" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="536" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A536" t="s">
         <v>40</v>
       </c>
@@ -17194,7 +17189,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="537" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="537" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A537" t="s">
         <v>40</v>
       </c>
@@ -17223,7 +17218,7 @@
       </c>
       <c r="I537" s="6"/>
     </row>
-    <row r="538" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="538" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A538" t="s">
         <v>40</v>
       </c>
@@ -17254,7 +17249,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="539" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="539" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A539" t="s">
         <v>40</v>
       </c>
@@ -17285,7 +17280,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="540" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="540" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A540" t="s">
         <v>40</v>
       </c>
@@ -17316,7 +17311,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="541" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="541" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A541" t="s">
         <v>40</v>
       </c>
@@ -17345,7 +17340,7 @@
       </c>
       <c r="I541" s="6"/>
     </row>
-    <row r="542" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="542" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A542" t="s">
         <v>40</v>
       </c>
@@ -17376,7 +17371,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="543" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="543" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A543" t="s">
         <v>40</v>
       </c>
@@ -17407,7 +17402,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="544" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="544" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A544" t="s">
         <v>40</v>
       </c>
@@ -17438,7 +17433,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="545" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="545" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A545" t="s">
         <v>40</v>
       </c>
@@ -17469,7 +17464,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="546" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="546" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A546" t="s">
         <v>40</v>
       </c>
@@ -17500,7 +17495,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="547" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="547" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A547" t="s">
         <v>40</v>
       </c>
@@ -17531,7 +17526,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="548" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="548" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A548" t="s">
         <v>40</v>
       </c>
@@ -17560,7 +17555,7 @@
       </c>
       <c r="I548" s="6"/>
     </row>
-    <row r="549" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="549" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A549" t="s">
         <v>40</v>
       </c>
@@ -17591,7 +17586,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="550" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="550" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A550" t="s">
         <v>40</v>
       </c>
@@ -17622,7 +17617,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="551" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="551" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A551" t="s">
         <v>40</v>
       </c>
@@ -17651,7 +17646,7 @@
       </c>
       <c r="I551" s="6"/>
     </row>
-    <row r="552" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="552" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A552" t="s">
         <v>40</v>
       </c>
@@ -17680,7 +17675,7 @@
       </c>
       <c r="I552" s="6"/>
     </row>
-    <row r="553" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="553" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A553" t="s">
         <v>40</v>
       </c>
@@ -17709,7 +17704,7 @@
       </c>
       <c r="I553" s="6"/>
     </row>
-    <row r="554" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="554" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A554" t="s">
         <v>40</v>
       </c>
@@ -17740,7 +17735,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="555" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="555" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A555" t="s">
         <v>40</v>
       </c>
@@ -17769,7 +17764,7 @@
       </c>
       <c r="I555" s="6"/>
     </row>
-    <row r="556" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="556" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A556" t="s">
         <v>40</v>
       </c>
@@ -17798,7 +17793,7 @@
       </c>
       <c r="I556" s="6"/>
     </row>
-    <row r="557" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="557" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A557" t="s">
         <v>40</v>
       </c>
@@ -17829,7 +17824,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="558" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="558" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A558" t="s">
         <v>40</v>
       </c>
@@ -17860,7 +17855,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="559" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="559" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A559" t="s">
         <v>40</v>
       </c>
@@ -17889,7 +17884,7 @@
       </c>
       <c r="I559" s="6"/>
     </row>
-    <row r="560" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="560" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A560" t="s">
         <v>40</v>
       </c>
@@ -17920,7 +17915,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="561" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="561" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A561" t="s">
         <v>40</v>
       </c>
@@ -17951,7 +17946,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="562" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="562" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A562" t="s">
         <v>40</v>
       </c>
@@ -17980,7 +17975,7 @@
       </c>
       <c r="I562" s="6"/>
     </row>
-    <row r="563" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="563" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A563" t="s">
         <v>40</v>
       </c>
@@ -18009,7 +18004,7 @@
       </c>
       <c r="I563" s="6"/>
     </row>
-    <row r="564" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="564" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A564" t="s">
         <v>40</v>
       </c>
@@ -18038,7 +18033,7 @@
       </c>
       <c r="I564" s="6"/>
     </row>
-    <row r="565" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="565" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A565" t="s">
         <v>40</v>
       </c>
@@ -18067,7 +18062,7 @@
       </c>
       <c r="I565" s="6"/>
     </row>
-    <row r="566" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="566" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A566" t="s">
         <v>40</v>
       </c>
@@ -18096,7 +18091,7 @@
       </c>
       <c r="I566" s="6"/>
     </row>
-    <row r="567" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="567" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A567" t="s">
         <v>40</v>
       </c>
@@ -18125,7 +18120,7 @@
       </c>
       <c r="I567" s="6"/>
     </row>
-    <row r="568" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="568" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A568" t="s">
         <v>40</v>
       </c>
@@ -18156,7 +18151,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="569" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="569" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A569" t="s">
         <v>40</v>
       </c>
@@ -18185,7 +18180,7 @@
       </c>
       <c r="I569" s="6"/>
     </row>
-    <row r="570" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="570" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A570" t="s">
         <v>40</v>
       </c>
@@ -18216,7 +18211,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="571" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="571" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A571" t="s">
         <v>40</v>
       </c>
@@ -18247,7 +18242,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="572" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="572" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A572" t="s">
         <v>40</v>
       </c>
@@ -18278,7 +18273,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="573" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="573" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A573" t="s">
         <v>40</v>
       </c>
@@ -18309,7 +18304,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="574" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="574" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A574" t="s">
         <v>40</v>
       </c>
@@ -18340,7 +18335,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="575" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="575" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A575" t="s">
         <v>40</v>
       </c>
@@ -18371,7 +18366,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="576" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="576" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A576" t="s">
         <v>40</v>
       </c>
@@ -18400,7 +18395,7 @@
       </c>
       <c r="I576" s="6"/>
     </row>
-    <row r="577" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="577" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A577" t="s">
         <v>40</v>
       </c>
@@ -18429,7 +18424,7 @@
       </c>
       <c r="I577" s="6"/>
     </row>
-    <row r="578" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="578" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A578" t="s">
         <v>40</v>
       </c>
@@ -18460,7 +18455,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="579" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="579" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A579" t="s">
         <v>40</v>
       </c>
@@ -18489,7 +18484,7 @@
       </c>
       <c r="I579" s="6"/>
     </row>
-    <row r="580" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="580" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A580" t="s">
         <v>40</v>
       </c>
@@ -18520,7 +18515,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="581" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="581" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A581" t="s">
         <v>40</v>
       </c>
@@ -18549,7 +18544,7 @@
       </c>
       <c r="I581" s="6"/>
     </row>
-    <row r="582" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="582" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A582" t="s">
         <v>40</v>
       </c>
@@ -18580,7 +18575,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="583" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="583" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A583" t="s">
         <v>40</v>
       </c>
@@ -18609,7 +18604,7 @@
       </c>
       <c r="I583" s="6"/>
     </row>
-    <row r="584" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="584" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A584" t="s">
         <v>40</v>
       </c>
@@ -18640,7 +18635,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="585" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="585" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A585" t="s">
         <v>40</v>
       </c>
@@ -18671,7 +18666,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="586" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="586" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A586" t="s">
         <v>40</v>
       </c>
@@ -18702,7 +18697,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="587" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="587" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A587" t="s">
         <v>40</v>
       </c>
@@ -18733,7 +18728,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="588" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="588" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A588" t="s">
         <v>40</v>
       </c>
@@ -18764,7 +18759,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="589" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="589" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A589" t="s">
         <v>40</v>
       </c>
@@ -18795,7 +18790,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="590" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="590" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A590" t="s">
         <v>40</v>
       </c>
@@ -18824,7 +18819,7 @@
       </c>
       <c r="I590" s="6"/>
     </row>
-    <row r="591" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="591" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A591" t="s">
         <v>40</v>
       </c>
@@ -18853,7 +18848,7 @@
       </c>
       <c r="I591" s="6"/>
     </row>
-    <row r="592" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="592" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A592" t="s">
         <v>40</v>
       </c>
@@ -18881,7 +18876,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="593" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="593" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A593" t="s">
         <v>40</v>
       </c>
@@ -18909,7 +18904,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="594" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="594" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A594" t="s">
         <v>40</v>
       </c>
@@ -18937,7 +18932,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="595" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="595" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A595" t="s">
         <v>40</v>
       </c>
@@ -18965,7 +18960,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="596" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="596" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A596" t="s">
         <v>40</v>
       </c>
@@ -18993,7 +18988,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="597" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="597" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A597" t="s">
         <v>40</v>
       </c>
@@ -19024,7 +19019,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="598" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="598" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A598" t="s">
         <v>40</v>
       </c>
@@ -19052,7 +19047,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="599" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="599" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A599" t="s">
         <v>40</v>
       </c>
@@ -19080,7 +19075,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="600" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="600" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A600" t="s">
         <v>40</v>
       </c>
@@ -19108,7 +19103,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="601" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="601" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A601" t="s">
         <v>40</v>
       </c>
@@ -19136,7 +19131,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="602" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="602" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A602" t="s">
         <v>40</v>
       </c>
@@ -19164,7 +19159,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="603" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="603" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A603" t="s">
         <v>40</v>
       </c>
@@ -19192,7 +19187,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="604" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="604" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A604" t="s">
         <v>40</v>
       </c>
@@ -19220,7 +19215,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="605" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="605" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A605" t="s">
         <v>40</v>
       </c>
@@ -19248,7 +19243,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="606" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="606" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A606" t="s">
         <v>40</v>
       </c>
@@ -19279,7 +19274,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="607" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="607" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A607" t="s">
         <v>40</v>
       </c>
@@ -19308,7 +19303,7 @@
       </c>
       <c r="I607" s="6"/>
     </row>
-    <row r="608" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="608" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A608" t="s">
         <v>40</v>
       </c>
@@ -19339,7 +19334,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="609" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="609" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A609" t="s">
         <v>40</v>
       </c>
@@ -19368,7 +19363,7 @@
       </c>
       <c r="I609" s="6"/>
     </row>
-    <row r="610" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="610" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A610" t="s">
         <v>40</v>
       </c>
@@ -19399,7 +19394,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="611" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="611" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A611" t="s">
         <v>40</v>
       </c>
@@ -19428,7 +19423,7 @@
       </c>
       <c r="I611" s="6"/>
     </row>
-    <row r="612" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="612" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A612" t="s">
         <v>40</v>
       </c>
@@ -19459,7 +19454,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="613" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="613" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A613" t="s">
         <v>40</v>
       </c>
@@ -19490,7 +19485,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="614" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="614" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A614" t="s">
         <v>40</v>
       </c>
@@ -19521,7 +19516,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="615" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="615" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A615" t="s">
         <v>40</v>
       </c>
@@ -19552,7 +19547,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="616" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="616" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A616" t="s">
         <v>40</v>
       </c>
@@ -19583,7 +19578,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="617" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="617" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A617" t="s">
         <v>40</v>
       </c>
@@ -19614,7 +19609,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="618" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="618" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A618" t="s">
         <v>40</v>
       </c>
@@ -19643,7 +19638,7 @@
       </c>
       <c r="I618" s="6"/>
     </row>
-    <row r="619" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="619" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A619" t="s">
         <v>40</v>
       </c>
@@ -19672,7 +19667,7 @@
       </c>
       <c r="I619" s="6"/>
     </row>
-    <row r="620" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="620" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A620" t="s">
         <v>40</v>
       </c>
@@ -19701,7 +19696,7 @@
       </c>
       <c r="I620" s="6"/>
     </row>
-    <row r="621" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="621" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A621" t="s">
         <v>40</v>
       </c>
@@ -19732,7 +19727,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="622" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="622" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A622" t="s">
         <v>40</v>
       </c>
@@ -19761,7 +19756,7 @@
       </c>
       <c r="I622" s="6"/>
     </row>
-    <row r="623" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="623" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A623" t="s">
         <v>40</v>
       </c>
@@ -19790,7 +19785,7 @@
       </c>
       <c r="I623" s="6"/>
     </row>
-    <row r="624" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="624" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A624" t="s">
         <v>40</v>
       </c>
@@ -19821,7 +19816,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="625" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="625" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A625" t="s">
         <v>40</v>
       </c>
@@ -19850,7 +19845,7 @@
       </c>
       <c r="I625" s="6"/>
     </row>
-    <row r="626" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="626" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A626" t="s">
         <v>40</v>
       </c>
@@ -19881,7 +19876,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="627" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="627" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A627" t="s">
         <v>40</v>
       </c>
@@ -19912,7 +19907,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="628" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="628" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A628" t="s">
         <v>40</v>
       </c>
@@ -19941,7 +19936,7 @@
       </c>
       <c r="I628" s="6"/>
     </row>
-    <row r="629" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="629" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A629" t="s">
         <v>40</v>
       </c>
@@ -19972,7 +19967,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="630" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="630" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A630" t="s">
         <v>40</v>
       </c>
@@ -20003,7 +19998,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="631" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="631" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A631" t="s">
         <v>40</v>
       </c>
@@ -20034,7 +20029,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="632" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="632" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A632" t="s">
         <v>40</v>
       </c>
@@ -20063,7 +20058,7 @@
       </c>
       <c r="I632" s="6"/>
     </row>
-    <row r="633" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="633" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A633" t="s">
         <v>40</v>
       </c>
@@ -20094,7 +20089,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="634" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="634" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A634" t="s">
         <v>40</v>
       </c>
@@ -20123,7 +20118,7 @@
       </c>
       <c r="I634" s="6"/>
     </row>
-    <row r="635" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="635" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A635" t="s">
         <v>40</v>
       </c>
@@ -20154,7 +20149,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="636" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="636" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A636" t="s">
         <v>40</v>
       </c>
@@ -20183,7 +20178,7 @@
       </c>
       <c r="I636" s="6"/>
     </row>
-    <row r="637" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="637" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A637" t="s">
         <v>40</v>
       </c>
@@ -20212,7 +20207,7 @@
       </c>
       <c r="I637" s="6"/>
     </row>
-    <row r="638" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="638" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A638" t="s">
         <v>40</v>
       </c>
@@ -20243,7 +20238,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="639" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="639" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A639" t="s">
         <v>40</v>
       </c>
@@ -20272,7 +20267,7 @@
       </c>
       <c r="I639" s="6"/>
     </row>
-    <row r="640" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="640" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A640" t="s">
         <v>40</v>
       </c>
@@ -20303,7 +20298,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="641" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="641" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A641" t="s">
         <v>40</v>
       </c>
@@ -20334,7 +20329,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="642" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="642" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A642" t="s">
         <v>40</v>
       </c>
@@ -20365,7 +20360,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="643" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="643" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A643" t="s">
         <v>40</v>
       </c>
@@ -20396,7 +20391,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="644" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="644" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A644" t="s">
         <v>40</v>
       </c>
@@ -20427,7 +20422,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="645" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="645" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A645" t="s">
         <v>40</v>
       </c>
@@ -20458,7 +20453,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="646" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="646" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A646" t="s">
         <v>40</v>
       </c>
@@ -20487,7 +20482,7 @@
       </c>
       <c r="I646" s="6"/>
     </row>
-    <row r="647" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="647" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A647" t="s">
         <v>40</v>
       </c>
@@ -20518,7 +20513,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="648" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="648" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A648" t="s">
         <v>41</v>
       </c>
@@ -20549,7 +20544,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="649" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="649" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A649" t="s">
         <v>41</v>
       </c>
@@ -20578,7 +20573,7 @@
       </c>
       <c r="I649" s="6"/>
     </row>
-    <row r="650" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="650" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A650" t="s">
         <v>41</v>
       </c>
@@ -20609,7 +20604,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="651" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="651" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A651" t="s">
         <v>41</v>
       </c>
@@ -20640,7 +20635,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="652" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="652" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A652" t="s">
         <v>41</v>
       </c>
@@ -20671,7 +20666,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="653" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="653" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A653" t="s">
         <v>41</v>
       </c>
@@ -20702,7 +20697,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="654" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="654" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A654" t="s">
         <v>41</v>
       </c>
@@ -20731,7 +20726,7 @@
       </c>
       <c r="I654" s="6"/>
     </row>
-    <row r="655" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="655" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A655" t="s">
         <v>41</v>
       </c>
@@ -20762,7 +20757,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="656" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="656" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A656" t="s">
         <v>41</v>
       </c>
@@ -20793,7 +20788,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="657" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="657" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A657" t="s">
         <v>41</v>
       </c>
@@ -20822,7 +20817,7 @@
       </c>
       <c r="I657" s="6"/>
     </row>
-    <row r="658" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="658" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A658" t="s">
         <v>41</v>
       </c>
@@ -20851,7 +20846,7 @@
       </c>
       <c r="I658" s="6"/>
     </row>
-    <row r="659" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="659" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A659" t="s">
         <v>41</v>
       </c>
@@ -20882,7 +20877,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="660" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="660" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A660" t="s">
         <v>41</v>
       </c>
@@ -20913,7 +20908,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="661" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="661" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A661" t="s">
         <v>41</v>
       </c>
@@ -20944,7 +20939,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="662" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="662" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A662" t="s">
         <v>41</v>
       </c>
@@ -20975,7 +20970,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="663" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="663" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A663" t="s">
         <v>41</v>
       </c>
@@ -21004,7 +20999,7 @@
       </c>
       <c r="I663" s="6"/>
     </row>
-    <row r="664" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="664" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A664" t="s">
         <v>41</v>
       </c>
@@ -21033,7 +21028,7 @@
       </c>
       <c r="I664" s="6"/>
     </row>
-    <row r="665" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="665" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A665" t="s">
         <v>41</v>
       </c>
@@ -21064,7 +21059,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="666" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="666" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A666" t="s">
         <v>41</v>
       </c>
@@ -21095,7 +21090,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="667" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="667" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A667" t="s">
         <v>41</v>
       </c>
@@ -21126,7 +21121,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="668" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="668" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A668" t="s">
         <v>41</v>
       </c>
@@ -21155,7 +21150,7 @@
       </c>
       <c r="I668" s="6"/>
     </row>
-    <row r="669" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="669" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A669" t="s">
         <v>41</v>
       </c>
@@ -21184,7 +21179,7 @@
       </c>
       <c r="I669" s="6"/>
     </row>
-    <row r="670" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="670" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A670" t="s">
         <v>41</v>
       </c>
@@ -21215,7 +21210,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="671" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="671" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A671" t="s">
         <v>41</v>
       </c>
@@ -21246,7 +21241,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="672" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="672" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A672" t="s">
         <v>41</v>
       </c>
@@ -21277,7 +21272,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="673" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="673" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A673" t="s">
         <v>41</v>
       </c>
@@ -21308,7 +21303,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="674" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="674" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A674" t="s">
         <v>41</v>
       </c>
@@ -21339,7 +21334,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="675" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="675" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A675" t="s">
         <v>41</v>
       </c>
@@ -21370,7 +21365,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="676" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="676" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A676" t="s">
         <v>41</v>
       </c>
@@ -21401,7 +21396,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="677" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="677" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A677" t="s">
         <v>41</v>
       </c>
@@ -21432,7 +21427,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="678" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="678" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A678" t="s">
         <v>41</v>
       </c>
@@ -21461,7 +21456,7 @@
       </c>
       <c r="I678" s="6"/>
     </row>
-    <row r="679" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="679" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A679" t="s">
         <v>41</v>
       </c>
@@ -21492,7 +21487,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="680" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="680" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A680" t="s">
         <v>41</v>
       </c>
@@ -21523,7 +21518,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="681" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="681" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A681" t="s">
         <v>41</v>
       </c>
@@ -21554,7 +21549,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="682" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="682" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A682" t="s">
         <v>41</v>
       </c>
@@ -21585,7 +21580,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="683" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="683" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A683" t="s">
         <v>41</v>
       </c>
@@ -21614,7 +21609,7 @@
       </c>
       <c r="I683" s="6"/>
     </row>
-    <row r="684" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="684" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A684" t="s">
         <v>41</v>
       </c>
@@ -21643,7 +21638,7 @@
       </c>
       <c r="I684" s="6"/>
     </row>
-    <row r="685" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="685" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A685" t="s">
         <v>41</v>
       </c>
@@ -21672,7 +21667,7 @@
       </c>
       <c r="I685" s="6"/>
     </row>
-    <row r="686" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="686" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A686" t="s">
         <v>41</v>
       </c>
@@ -21703,7 +21698,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="687" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="687" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A687" t="s">
         <v>41</v>
       </c>
@@ -21732,7 +21727,7 @@
       </c>
       <c r="I687" s="6"/>
     </row>
-    <row r="688" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="688" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A688" t="s">
         <v>41</v>
       </c>
@@ -21763,7 +21758,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="689" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="689" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A689" t="s">
         <v>41</v>
       </c>
@@ -21794,7 +21789,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="690" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="690" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A690" t="s">
         <v>41</v>
       </c>
@@ -21825,7 +21820,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="691" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="691" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A691" t="s">
         <v>41</v>
       </c>
@@ -21854,7 +21849,7 @@
       </c>
       <c r="I691" s="6"/>
     </row>
-    <row r="692" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="692" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A692" t="s">
         <v>41</v>
       </c>
@@ -21885,7 +21880,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="693" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="693" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A693" t="s">
         <v>41</v>
       </c>
@@ -21916,7 +21911,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="694" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="694" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A694" t="s">
         <v>41</v>
       </c>
@@ -21947,7 +21942,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="695" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="695" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A695" t="s">
         <v>41</v>
       </c>
@@ -21978,7 +21973,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="696" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="696" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A696" t="s">
         <v>41</v>
       </c>
@@ -22009,7 +22004,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="697" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="697" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A697" t="s">
         <v>41</v>
       </c>
@@ -22040,7 +22035,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="698" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="698" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A698" t="s">
         <v>41</v>
       </c>
@@ -22069,7 +22064,7 @@
       </c>
       <c r="I698" s="6"/>
     </row>
-    <row r="699" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="699" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A699" t="s">
         <v>41</v>
       </c>
@@ -22098,7 +22093,7 @@
       </c>
       <c r="I699" s="6"/>
     </row>
-    <row r="700" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="700" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A700" t="s">
         <v>41</v>
       </c>
@@ -22129,7 +22124,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="701" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="701" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A701" t="s">
         <v>41</v>
       </c>
@@ -22160,7 +22155,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="702" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="702" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A702" t="s">
         <v>41</v>
       </c>
@@ -22191,7 +22186,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="703" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="703" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A703" t="s">
         <v>41</v>
       </c>
@@ -22222,7 +22217,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="704" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="704" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A704" t="s">
         <v>41</v>
       </c>
@@ -22253,7 +22248,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="705" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="705" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A705" t="s">
         <v>41</v>
       </c>
@@ -22284,7 +22279,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="706" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="706" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A706" t="s">
         <v>41</v>
       </c>
@@ -22313,7 +22308,7 @@
       </c>
       <c r="I706" s="6"/>
     </row>
-    <row r="707" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="707" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A707" t="s">
         <v>41</v>
       </c>
@@ -22342,7 +22337,7 @@
       </c>
       <c r="I707" s="6"/>
     </row>
-    <row r="708" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="708" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A708" t="s">
         <v>41</v>
       </c>
@@ -22373,7 +22368,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="709" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="709" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A709" t="s">
         <v>41</v>
       </c>
@@ -22402,7 +22397,7 @@
       </c>
       <c r="I709" s="6"/>
     </row>
-    <row r="710" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="710" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A710" t="s">
         <v>41</v>
       </c>
@@ -22433,7 +22428,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="711" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="711" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A711" t="s">
         <v>41</v>
       </c>
@@ -22464,7 +22459,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="712" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="712" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A712" t="s">
         <v>41</v>
       </c>
@@ -22495,7 +22490,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="713" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="713" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A713" t="s">
         <v>41</v>
       </c>
@@ -22526,7 +22521,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="714" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="714" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A714" t="s">
         <v>41</v>
       </c>
@@ -22555,7 +22550,7 @@
       </c>
       <c r="I714" s="6"/>
     </row>
-    <row r="715" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="715" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A715" t="s">
         <v>41</v>
       </c>
@@ -22586,7 +22581,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="716" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="716" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A716" t="s">
         <v>41</v>
       </c>
@@ -22617,7 +22612,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="717" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="717" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A717" t="s">
         <v>41</v>
       </c>
@@ -22648,7 +22643,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="718" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="718" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A718" t="s">
         <v>41</v>
       </c>
@@ -22677,7 +22672,7 @@
       </c>
       <c r="I718" s="6"/>
     </row>
-    <row r="719" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="719" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A719" t="s">
         <v>41</v>
       </c>
@@ -22708,7 +22703,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="720" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="720" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A720" t="s">
         <v>41</v>
       </c>
@@ -22739,7 +22734,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="721" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="721" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A721" t="s">
         <v>41</v>
       </c>
@@ -22768,7 +22763,7 @@
       </c>
       <c r="I721" s="6"/>
     </row>
-    <row r="722" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="722" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A722" t="s">
         <v>41</v>
       </c>
@@ -22799,7 +22794,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="723" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="723" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A723" t="s">
         <v>41</v>
       </c>
@@ -22828,7 +22823,7 @@
       </c>
       <c r="I723" s="6"/>
     </row>
-    <row r="724" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="724" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A724" t="s">
         <v>41</v>
       </c>
@@ -22859,7 +22854,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="725" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="725" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A725" t="s">
         <v>41</v>
       </c>
@@ -22890,7 +22885,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="726" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="726" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A726" t="s">
         <v>41</v>
       </c>
@@ -22921,7 +22916,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="727" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="727" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A727" t="s">
         <v>41</v>
       </c>
@@ -22952,7 +22947,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="728" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="728" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A728" t="s">
         <v>41</v>
       </c>
@@ -22983,7 +22978,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="729" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="729" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A729" t="s">
         <v>41</v>
       </c>
@@ -23012,7 +23007,7 @@
       </c>
       <c r="I729" s="6"/>
     </row>
-    <row r="730" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="730" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A730" t="s">
         <v>41</v>
       </c>
@@ -23043,7 +23038,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="731" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="731" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A731" t="s">
         <v>41</v>
       </c>
@@ -23074,7 +23069,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="732" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="732" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A732" t="s">
         <v>41</v>
       </c>
@@ -23105,7 +23100,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="733" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="733" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A733" t="s">
         <v>41</v>
       </c>
@@ -23136,7 +23131,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="734" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="734" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A734" t="s">
         <v>41</v>
       </c>
@@ -23167,7 +23162,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="735" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="735" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A735" t="s">
         <v>41</v>
       </c>
@@ -23198,7 +23193,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="736" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="736" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A736" t="s">
         <v>41</v>
       </c>
@@ -23227,7 +23222,7 @@
       </c>
       <c r="I736" s="6"/>
     </row>
-    <row r="737" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="737" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A737" t="s">
         <v>41</v>
       </c>
@@ -23258,7 +23253,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="738" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="738" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A738" t="s">
         <v>41</v>
       </c>
@@ -23289,7 +23284,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="739" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="739" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A739" t="s">
         <v>41</v>
       </c>
@@ -23320,7 +23315,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="740" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="740" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A740" t="s">
         <v>41</v>
       </c>
@@ -23351,7 +23346,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="741" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="741" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A741" t="s">
         <v>41</v>
       </c>
@@ -23382,7 +23377,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="742" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="742" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A742" t="s">
         <v>41</v>
       </c>
@@ -23413,7 +23408,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="743" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="743" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A743" t="s">
         <v>41</v>
       </c>
@@ -23444,7 +23439,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="744" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="744" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A744" t="s">
         <v>41</v>
       </c>
@@ -23475,7 +23470,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="745" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="745" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A745" t="s">
         <v>41</v>
       </c>
@@ -23506,7 +23501,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="746" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="746" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A746" t="s">
         <v>41</v>
       </c>
@@ -23537,7 +23532,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="747" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="747" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A747" t="s">
         <v>41</v>
       </c>
@@ -23568,7 +23563,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="748" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="748" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A748" t="s">
         <v>41</v>
       </c>
@@ -23597,7 +23592,7 @@
       </c>
       <c r="I748" s="6"/>
     </row>
-    <row r="749" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="749" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A749" t="s">
         <v>41</v>
       </c>
@@ -23628,7 +23623,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="750" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="750" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A750" t="s">
         <v>41</v>
       </c>
@@ -23659,7 +23654,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="751" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="751" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A751" t="s">
         <v>41</v>
       </c>
@@ -23688,7 +23683,7 @@
       </c>
       <c r="I751" s="6"/>
     </row>
-    <row r="752" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="752" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A752" t="s">
         <v>41</v>
       </c>
@@ -23719,7 +23714,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="753" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="753" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A753" t="s">
         <v>41</v>
       </c>
@@ -23750,7 +23745,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="754" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="754" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A754" t="s">
         <v>41</v>
       </c>
@@ -23781,7 +23776,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="755" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="755" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A755" t="s">
         <v>41</v>
       </c>
@@ -23812,7 +23807,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="756" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="756" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A756" t="s">
         <v>41</v>
       </c>
@@ -23843,7 +23838,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="757" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="757" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A757" t="s">
         <v>41</v>
       </c>
@@ -23874,7 +23869,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="758" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="758" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A758" t="s">
         <v>41</v>
       </c>
@@ -23903,7 +23898,7 @@
       </c>
       <c r="I758" s="6"/>
     </row>
-    <row r="759" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="759" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A759" t="s">
         <v>41</v>
       </c>
@@ -23932,7 +23927,7 @@
       </c>
       <c r="I759" s="6"/>
     </row>
-    <row r="760" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="760" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A760" t="s">
         <v>41</v>
       </c>
@@ -23963,7 +23958,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="761" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="761" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A761" t="s">
         <v>41</v>
       </c>
@@ -23994,7 +23989,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="762" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="762" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A762" t="s">
         <v>41</v>
       </c>
@@ -24025,7 +24020,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="763" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="763" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A763" t="s">
         <v>41</v>
       </c>
@@ -24056,7 +24051,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="764" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="764" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A764" t="s">
         <v>41</v>
       </c>
@@ -24087,7 +24082,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="765" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="765" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A765" t="s">
         <v>41</v>
       </c>
@@ -24118,7 +24113,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="766" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="766" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A766" t="s">
         <v>41</v>
       </c>
@@ -24147,7 +24142,7 @@
       </c>
       <c r="I766" s="6"/>
     </row>
-    <row r="767" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="767" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A767" t="s">
         <v>41</v>
       </c>
@@ -24178,7 +24173,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="768" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="768" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A768" t="s">
         <v>41</v>
       </c>
@@ -24209,7 +24204,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="769" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="769" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A769" t="s">
         <v>41</v>
       </c>
@@ -24240,7 +24235,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="770" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="770" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A770" t="s">
         <v>41</v>
       </c>
@@ -24271,7 +24266,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="771" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="771" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A771" t="s">
         <v>41</v>
       </c>
@@ -24302,7 +24297,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="772" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="772" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A772" t="s">
         <v>41</v>
       </c>
@@ -24333,7 +24328,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="773" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="773" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A773" t="s">
         <v>41</v>
       </c>
@@ -24364,7 +24359,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="774" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="774" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A774" t="s">
         <v>41</v>
       </c>
@@ -24395,7 +24390,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="775" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="775" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A775" t="s">
         <v>41</v>
       </c>
@@ -24426,7 +24421,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="776" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="776" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A776" t="s">
         <v>41</v>
       </c>
@@ -24457,7 +24452,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="777" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="777" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A777" t="s">
         <v>41</v>
       </c>
@@ -24488,7 +24483,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="778" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="778" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A778" t="s">
         <v>41</v>
       </c>
@@ -24517,7 +24512,7 @@
       </c>
       <c r="I778" s="6"/>
     </row>
-    <row r="779" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="779" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A779" t="s">
         <v>41</v>
       </c>
@@ -24548,7 +24543,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="780" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="780" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A780" t="s">
         <v>41</v>
       </c>
@@ -24579,7 +24574,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="781" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="781" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A781" t="s">
         <v>41</v>
       </c>
@@ -24608,7 +24603,7 @@
       </c>
       <c r="I781" s="6"/>
     </row>
-    <row r="782" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="782" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A782" t="s">
         <v>41</v>
       </c>
@@ -24637,7 +24632,7 @@
       </c>
       <c r="I782" s="6"/>
     </row>
-    <row r="783" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="783" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A783" t="s">
         <v>41</v>
       </c>
@@ -24666,7 +24661,7 @@
       </c>
       <c r="I783" s="6"/>
     </row>
-    <row r="784" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="784" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A784" t="s">
         <v>41</v>
       </c>
@@ -24695,7 +24690,7 @@
       </c>
       <c r="I784" s="6"/>
     </row>
-    <row r="785" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="785" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A785" t="s">
         <v>41</v>
       </c>
@@ -24726,7 +24721,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="786" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="786" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A786" t="s">
         <v>41</v>
       </c>
@@ -24755,7 +24750,7 @@
       </c>
       <c r="I786" s="6"/>
     </row>
-    <row r="787" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="787" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A787" t="s">
         <v>41</v>
       </c>
@@ -24786,7 +24781,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="788" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="788" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A788" t="s">
         <v>41</v>
       </c>
@@ -24815,7 +24810,7 @@
       </c>
       <c r="I788" s="6"/>
     </row>
-    <row r="789" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="789" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A789" t="s">
         <v>41</v>
       </c>
@@ -24844,7 +24839,7 @@
       </c>
       <c r="I789" s="6"/>
     </row>
-    <row r="790" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="790" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A790" t="s">
         <v>41</v>
       </c>
@@ -24873,7 +24868,7 @@
       </c>
       <c r="I790" s="6"/>
     </row>
-    <row r="791" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="791" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A791" t="s">
         <v>41</v>
       </c>
@@ -24904,7 +24899,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="792" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="792" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A792" t="s">
         <v>41</v>
       </c>
@@ -24933,7 +24928,7 @@
       </c>
       <c r="I792" s="6"/>
     </row>
-    <row r="793" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="793" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A793" t="s">
         <v>41</v>
       </c>
@@ -24962,7 +24957,7 @@
       </c>
       <c r="I793" s="6"/>
     </row>
-    <row r="794" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="794" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A794" t="s">
         <v>41</v>
       </c>
@@ -24993,7 +24988,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="795" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="795" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A795" t="s">
         <v>41</v>
       </c>
@@ -25024,7 +25019,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="796" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="796" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A796" t="s">
         <v>41</v>
       </c>
@@ -25053,7 +25048,7 @@
       </c>
       <c r="I796" s="6"/>
     </row>
-    <row r="797" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="797" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A797" t="s">
         <v>41</v>
       </c>
@@ -25082,7 +25077,7 @@
       </c>
       <c r="I797" s="6"/>
     </row>
-    <row r="798" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="798" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A798" t="s">
         <v>41</v>
       </c>
@@ -25111,7 +25106,7 @@
       </c>
       <c r="I798" s="6"/>
     </row>
-    <row r="799" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="799" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A799" t="s">
         <v>41</v>
       </c>
@@ -25140,7 +25135,7 @@
       </c>
       <c r="I799" s="6"/>
     </row>
-    <row r="800" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="800" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A800" t="s">
         <v>41</v>
       </c>
@@ -25169,7 +25164,7 @@
       </c>
       <c r="I800" s="6"/>
     </row>
-    <row r="801" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="801" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A801" t="s">
         <v>41</v>
       </c>
@@ -25198,7 +25193,7 @@
       </c>
       <c r="I801" s="6"/>
     </row>
-    <row r="802" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="802" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A802" t="s">
         <v>41</v>
       </c>
@@ -25229,7 +25224,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="803" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="803" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A803" t="s">
         <v>41</v>
       </c>
@@ -25258,7 +25253,7 @@
       </c>
       <c r="I803" s="6"/>
     </row>
-    <row r="804" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="804" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A804" t="s">
         <v>41</v>
       </c>
@@ -25287,7 +25282,7 @@
       </c>
       <c r="I804" s="6"/>
     </row>
-    <row r="805" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="805" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A805" t="s">
         <v>41</v>
       </c>
@@ -25318,7 +25313,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="806" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="806" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A806" t="s">
         <v>41</v>
       </c>
@@ -25349,7 +25344,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="807" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="807" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A807" t="s">
         <v>41</v>
       </c>
@@ -25378,7 +25373,7 @@
       </c>
       <c r="I807" s="6"/>
     </row>
-    <row r="808" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="808" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A808" t="s">
         <v>41</v>
       </c>
@@ -25409,7 +25404,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="809" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="809" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A809" t="s">
         <v>41</v>
       </c>
@@ -25440,7 +25435,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="810" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="810" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A810" t="s">
         <v>41</v>
       </c>
@@ -25471,7 +25466,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="811" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="811" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A811" t="s">
         <v>41</v>
       </c>
@@ -25500,7 +25495,7 @@
       </c>
       <c r="I811" s="6"/>
     </row>
-    <row r="812" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="812" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A812" t="s">
         <v>41</v>
       </c>
@@ -25531,7 +25526,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="813" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="813" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A813" t="s">
         <v>41</v>
       </c>
@@ -25560,7 +25555,7 @@
       </c>
       <c r="I813" s="6"/>
     </row>
-    <row r="814" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="814" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A814" t="s">
         <v>41</v>
       </c>
@@ -25591,7 +25586,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="815" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="815" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A815" t="s">
         <v>41</v>
       </c>
@@ -25622,7 +25617,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="816" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="816" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A816" t="s">
         <v>41</v>
       </c>
@@ -25651,7 +25646,7 @@
       </c>
       <c r="I816" s="6"/>
     </row>
-    <row r="817" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="817" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A817" t="s">
         <v>41</v>
       </c>
@@ -25682,7 +25677,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="818" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="818" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A818" t="s">
         <v>41</v>
       </c>
@@ -25711,7 +25706,7 @@
       </c>
       <c r="I818" s="6"/>
     </row>
-    <row r="819" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="819" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A819" t="s">
         <v>41</v>
       </c>
@@ -25740,7 +25735,7 @@
       </c>
       <c r="I819" s="6"/>
     </row>
-    <row r="820" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="820" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A820" t="s">
         <v>41</v>
       </c>
@@ -25771,7 +25766,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="821" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="821" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A821" t="s">
         <v>41</v>
       </c>
@@ -25802,7 +25797,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="822" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="822" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A822" t="s">
         <v>41</v>
       </c>
@@ -25831,7 +25826,7 @@
       </c>
       <c r="I822" s="6"/>
     </row>
-    <row r="823" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="823" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A823" t="s">
         <v>41</v>
       </c>
@@ -25862,7 +25857,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="824" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="824" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A824" t="s">
         <v>41</v>
       </c>
@@ -25893,7 +25888,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="825" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="825" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A825" t="s">
         <v>41</v>
       </c>
@@ -25924,7 +25919,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="826" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="826" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A826" t="s">
         <v>41</v>
       </c>
@@ -25953,7 +25948,7 @@
       </c>
       <c r="I826" s="6"/>
     </row>
-    <row r="827" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="827" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A827" t="s">
         <v>41</v>
       </c>
@@ -25984,7 +25979,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="828" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="828" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A828" t="s">
         <v>40</v>
       </c>
@@ -26012,7 +26007,7 @@
       </c>
       <c r="I828" s="1"/>
     </row>
-    <row r="829" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="829" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A829" t="s">
         <v>40</v>
       </c>
@@ -26040,7 +26035,7 @@
       </c>
       <c r="I829" s="1"/>
     </row>
-    <row r="830" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="830" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A830" t="s">
         <v>40</v>
       </c>
@@ -26068,7 +26063,7 @@
       </c>
       <c r="I830" s="1"/>
     </row>
-    <row r="831" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="831" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A831" t="s">
         <v>40</v>
       </c>
@@ -26096,7 +26091,7 @@
       </c>
       <c r="I831" s="1"/>
     </row>
-    <row r="832" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="832" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A832" t="s">
         <v>40</v>
       </c>
@@ -26126,7 +26121,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="833" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="833" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A833" t="s">
         <v>40</v>
       </c>
@@ -26154,7 +26149,7 @@
       </c>
       <c r="I833" s="1"/>
     </row>
-    <row r="834" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="834" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A834" t="s">
         <v>40</v>
       </c>
@@ -26184,7 +26179,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="835" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="835" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A835" t="s">
         <v>40</v>
       </c>
@@ -26214,7 +26209,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="836" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="836" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A836" t="s">
         <v>40</v>
       </c>
@@ -26244,7 +26239,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="837" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="837" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A837" t="s">
         <v>40</v>
       </c>
@@ -26272,7 +26267,7 @@
       </c>
       <c r="I837" s="1"/>
     </row>
-    <row r="838" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="838" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A838" t="s">
         <v>40</v>
       </c>
@@ -26302,7 +26297,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="839" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="839" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A839" t="s">
         <v>40</v>
       </c>
@@ -26332,7 +26327,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="840" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="840" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A840" t="s">
         <v>40</v>
       </c>
@@ -26362,7 +26357,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="841" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="841" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A841" t="s">
         <v>40</v>
       </c>
@@ -26390,7 +26385,7 @@
       </c>
       <c r="I841" s="1"/>
     </row>
-    <row r="842" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="842" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A842" t="s">
         <v>40</v>
       </c>
@@ -26420,7 +26415,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="843" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="843" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A843" t="s">
         <v>40</v>
       </c>
@@ -26447,7 +26442,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="844" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="844" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A844" t="s">
         <v>40</v>
       </c>
@@ -26474,7 +26469,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="845" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="845" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A845" t="s">
         <v>40</v>
       </c>
@@ -26501,7 +26496,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="846" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="846" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A846" t="s">
         <v>40</v>
       </c>
@@ -26528,7 +26523,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="847" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="847" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A847" t="s">
         <v>40</v>
       </c>
@@ -26555,7 +26550,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="848" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="848" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A848" t="s">
         <v>40</v>
       </c>
@@ -26585,7 +26580,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="849" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="849" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A849" t="s">
         <v>40</v>
       </c>
@@ -26612,7 +26607,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="850" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="850" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A850" t="s">
         <v>40</v>
       </c>
@@ -26639,7 +26634,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="851" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="851" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A851" t="s">
         <v>40</v>
       </c>
@@ -26666,7 +26661,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="852" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="852" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A852" t="s">
         <v>40</v>
       </c>
@@ -26693,7 +26688,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="853" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="853" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A853" t="s">
         <v>40</v>
       </c>
@@ -26720,7 +26715,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="854" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="854" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A854" t="s">
         <v>40</v>
       </c>
@@ -26747,7 +26742,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="855" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="855" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A855" t="s">
         <v>40</v>
       </c>
@@ -26774,7 +26769,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="856" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="856" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A856" t="s">
         <v>40</v>
       </c>
@@ -26801,7 +26796,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="857" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="857" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A857" t="s">
         <v>40</v>
       </c>
@@ -26828,7 +26823,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="858" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="858" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A858" t="s">
         <v>41</v>
       </c>
@@ -26858,7 +26853,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="859" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="859" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A859" t="s">
         <v>41</v>
       </c>
@@ -26888,7 +26883,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="860" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="860" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A860" t="s">
         <v>41</v>
       </c>
@@ -26918,7 +26913,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="861" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="861" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A861" t="s">
         <v>41</v>
       </c>
@@ -26948,7 +26943,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="862" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="862" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A862" t="s">
         <v>41</v>
       </c>
@@ -26978,7 +26973,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="863" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="863" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A863" t="s">
         <v>41</v>
       </c>
@@ -27008,7 +27003,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="864" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="864" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A864" t="s">
         <v>41</v>
       </c>
@@ -27038,7 +27033,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="865" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="865" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A865" t="s">
         <v>41</v>
       </c>
@@ -27068,7 +27063,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="866" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="866" spans="1:9" hidden="1" x14ac:dyDescent="0.2">
       <c r="A866" t="s">
         <v>41</v>
       </c>
@@ -27099,7 +27094,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I866" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:I866" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="4">
+      <filters>
+        <filter val="B-SCT13"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
